--- a/Zinc/4. Exploratory data analysis/Summary_stats.xlsx
+++ b/Zinc/4. Exploratory data analysis/Summary_stats.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -181,6 +181,9 @@
     <t xml:space="preserve">Developed_lulc</t>
   </si>
   <si>
+    <t xml:space="preserve">Elevation_m</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free_Zn_M</t>
   </si>
   <si>
@@ -584,6 +587,9 @@
   </si>
   <si>
     <t xml:space="preserve">log_DOC_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Elevation_m</t>
   </si>
   <si>
     <t xml:space="preserve">log_Free_Zn_M</t>
@@ -2184,19 +2190,19 @@
         <v>55</v>
       </c>
       <c r="B51" t="n">
-        <v>0.0000000233587071393831</v>
+        <v>252.994430051813</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0000000202816536898353</v>
+        <v>257.04</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0000000119272254295311</v>
+        <v>258.19</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000000000000000298526627304055</v>
+        <v>197.832779024965</v>
       </c>
       <c r="F51" t="n">
-        <v>0.000000000879423131847894</v>
+        <v>0.715905128431426</v>
       </c>
     </row>
     <row r="52">
@@ -2204,19 +2210,19 @@
         <v>56</v>
       </c>
       <c r="B52" t="n">
-        <v>23.3587071393831</v>
+        <v>0.0000000233587071393831</v>
       </c>
       <c r="C52" t="n">
-        <v>20.2816536898354</v>
+        <v>0.0000000202816536898353</v>
       </c>
       <c r="D52" t="n">
-        <v>11.9272254295311</v>
+        <v>0.0000000119272254295311</v>
       </c>
       <c r="E52" t="n">
-        <v>298.526627304055</v>
+        <v>0.000000000000000298526627304055</v>
       </c>
       <c r="F52" t="n">
-        <v>0.879423131847894</v>
+        <v>0.000000000879423131847894</v>
       </c>
     </row>
     <row r="53">
@@ -2224,19 +2230,19 @@
         <v>57</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0233587071393831</v>
+        <v>23.3587071393831</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0202816536898354</v>
+        <v>20.2816536898354</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0119272254295311</v>
+        <v>11.9272254295311</v>
       </c>
       <c r="E53" t="n">
-        <v>0.000298526627304055</v>
+        <v>298.526627304055</v>
       </c>
       <c r="F53" t="n">
-        <v>0.000879423131847894</v>
+        <v>0.879423131847894</v>
       </c>
     </row>
     <row r="54">
@@ -2244,19 +2250,19 @@
         <v>58</v>
       </c>
       <c r="B54" t="n">
-        <v>0.00000000000000000000918938722882253</v>
+        <v>0.0233587071393831</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0000000000000000000015806770727196</v>
+        <v>0.0202816536898354</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0000000000000000000176801567971213</v>
+        <v>0.0119272254295311</v>
       </c>
       <c r="E54" t="n">
-        <v>0.00000000000000000000000000000000000000206615118414674</v>
+        <v>0.000298526627304055</v>
       </c>
       <c r="F54" t="n">
-        <v>0.000000000000000000002313595313574</v>
+        <v>0.000879423131847894</v>
       </c>
     </row>
     <row r="55">
@@ -2264,19 +2270,19 @@
         <v>59</v>
       </c>
       <c r="B55" t="n">
-        <v>0.00000000000918938722882253</v>
+        <v>0.00000000000000000000918938722882253</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0000000000015806770727196</v>
+        <v>0.0000000000000000000015806770727196</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0000000000176801567971213</v>
+        <v>0.0000000000000000000176801567971213</v>
       </c>
       <c r="E55" t="n">
-        <v>0.00000000000000000000206615118414674</v>
+        <v>0.00000000000000000000000000000000000000206615118414674</v>
       </c>
       <c r="F55" t="n">
-        <v>0.000000000002313595313574</v>
+        <v>0.000000000000000000002313595313574</v>
       </c>
     </row>
     <row r="56">
@@ -2284,19 +2290,19 @@
         <v>60</v>
       </c>
       <c r="B56" t="n">
-        <v>0.00000000000000918938722882253</v>
+        <v>0.00000000000918938722882253</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0000000000000015806770727196</v>
+        <v>0.0000000000015806770727196</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0000000000000176801567971213</v>
+        <v>0.0000000000176801567971213</v>
       </c>
       <c r="E56" t="n">
-        <v>0.00000000000000000000000000206615118414674</v>
+        <v>0.00000000000000000000206615118414674</v>
       </c>
       <c r="F56" t="n">
-        <v>0.000000000000002313595313574</v>
+        <v>0.000000000002313595313574</v>
       </c>
     </row>
     <row r="57">
@@ -2304,19 +2310,19 @@
         <v>61</v>
       </c>
       <c r="B57" t="n">
-        <v>0.000192351560484626</v>
+        <v>0.00000000000000918938722882253</v>
       </c>
       <c r="C57" t="n">
-        <v>0.000123645004350692</v>
+        <v>0.0000000000000015806770727196</v>
       </c>
       <c r="D57" t="n">
-        <v>0.000534763559699059</v>
+        <v>0.0000000000000176801567971213</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0000000402508687146174</v>
+        <v>0.00000000000000000000000000206615118414674</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0000102116042791996</v>
+        <v>0.000000000000002313595313574</v>
       </c>
     </row>
     <row r="58">
@@ -2324,19 +2330,19 @@
         <v>62</v>
       </c>
       <c r="B58" t="n">
-        <v>192351.560484626</v>
+        <v>0.000192351560484626</v>
       </c>
       <c r="C58" t="n">
-        <v>123645.004350692</v>
+        <v>0.000123645004350692</v>
       </c>
       <c r="D58" t="n">
-        <v>534763.559699059</v>
+        <v>0.000534763559699059</v>
       </c>
       <c r="E58" t="n">
-        <v>40250868714.6174</v>
+        <v>0.0000000402508687146174</v>
       </c>
       <c r="F58" t="n">
-        <v>10211.6042791996</v>
+        <v>0.0000102116042791996</v>
       </c>
     </row>
     <row r="59">
@@ -2344,19 +2350,19 @@
         <v>63</v>
       </c>
       <c r="B59" t="n">
-        <v>192.351560484626</v>
+        <v>192351.560484626</v>
       </c>
       <c r="C59" t="n">
-        <v>123.645004350692</v>
+        <v>123645.004350692</v>
       </c>
       <c r="D59" t="n">
-        <v>534.763559699059</v>
+        <v>534763.559699059</v>
       </c>
       <c r="E59" t="n">
-        <v>40250.8687146174</v>
+        <v>40250868714.6174</v>
       </c>
       <c r="F59" t="n">
-        <v>10.2116042791996</v>
+        <v>10211.6042791996</v>
       </c>
     </row>
     <row r="60">
@@ -2364,19 +2370,19 @@
         <v>64</v>
       </c>
       <c r="B60" t="n">
-        <v>0.00242130719722993</v>
+        <v>192.351560484626</v>
       </c>
       <c r="C60" t="n">
-        <v>0.00258737104013563</v>
+        <v>123.645004350692</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0037507344968617</v>
+        <v>534.763559699059</v>
       </c>
       <c r="E60" t="n">
-        <v>0.000000669167863595133</v>
+        <v>40250.8687146174</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0000416364684086174</v>
+        <v>10.2116042791996</v>
       </c>
     </row>
     <row r="61">
@@ -2384,19 +2390,19 @@
         <v>65</v>
       </c>
       <c r="B61" t="n">
-        <v>2421307.19722993</v>
+        <v>0.00242130719722993</v>
       </c>
       <c r="C61" t="n">
-        <v>2587371.04013562</v>
+        <v>0.00258737104013563</v>
       </c>
       <c r="D61" t="n">
-        <v>3750734.4968617</v>
+        <v>0.0037507344968617</v>
       </c>
       <c r="E61" t="n">
-        <v>669167863595.133</v>
+        <v>0.000000669167863595133</v>
       </c>
       <c r="F61" t="n">
-        <v>41636.4684086174</v>
+        <v>0.0000416364684086174</v>
       </c>
     </row>
     <row r="62">
@@ -2404,19 +2410,19 @@
         <v>66</v>
       </c>
       <c r="B62" t="n">
-        <v>2421.30719722993</v>
+        <v>2421307.19722993</v>
       </c>
       <c r="C62" t="n">
-        <v>2587.37104013562</v>
+        <v>2587371.04013562</v>
       </c>
       <c r="D62" t="n">
-        <v>3750.7344968617</v>
+        <v>3750734.4968617</v>
       </c>
       <c r="E62" t="n">
-        <v>669167.863595133</v>
+        <v>669167863595.133</v>
       </c>
       <c r="F62" t="n">
-        <v>41.6364684086174</v>
+        <v>41636.4684086174</v>
       </c>
     </row>
     <row r="63">
@@ -2424,19 +2430,19 @@
         <v>67</v>
       </c>
       <c r="B63" t="n">
-        <v>0.000000000000000000013282128503575</v>
+        <v>2421.30719722993</v>
       </c>
       <c r="C63" t="n">
-        <v>0.00000000000000000000764348207483634</v>
+        <v>2587.37104013562</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0000000000000000000311489270694077</v>
+        <v>3750.7344968617</v>
       </c>
       <c r="E63" t="n">
-        <v>0.00000000000000000000000000000000000000167646198580043</v>
+        <v>669167.863595133</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00000000000000000000208402633532361</v>
+        <v>41.6364684086174</v>
       </c>
     </row>
     <row r="64">
@@ -2444,19 +2450,19 @@
         <v>68</v>
       </c>
       <c r="B64" t="n">
-        <v>0.000000000013282128503575</v>
+        <v>0.000000000000000000013282128503575</v>
       </c>
       <c r="C64" t="n">
-        <v>0.00000000000764348207483634</v>
+        <v>0.00000000000000000000764348207483634</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0000000000311489270694077</v>
+        <v>0.0000000000000000000311489270694077</v>
       </c>
       <c r="E64" t="n">
-        <v>0.00000000000000000000167646198580043</v>
+        <v>0.00000000000000000000000000000000000000167646198580043</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00000000000208402633532361</v>
+        <v>0.00000000000000000000208402633532361</v>
       </c>
     </row>
     <row r="65">
@@ -2464,19 +2470,19 @@
         <v>69</v>
       </c>
       <c r="B65" t="n">
-        <v>0.000000000000013282128503575</v>
+        <v>0.000000000013282128503575</v>
       </c>
       <c r="C65" t="n">
-        <v>0.00000000000000764348207483634</v>
+        <v>0.00000000000764348207483634</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0000000000000311489270694077</v>
+        <v>0.0000000000311489270694077</v>
       </c>
       <c r="E65" t="n">
-        <v>0.00000000000000000000000000167646198580043</v>
+        <v>0.00000000000000000000167646198580043</v>
       </c>
       <c r="F65" t="n">
-        <v>0.00000000000000208402633532361</v>
+        <v>0.00000000000208402633532361</v>
       </c>
     </row>
     <row r="66">
@@ -2484,19 +2490,19 @@
         <v>70</v>
       </c>
       <c r="B66" t="n">
-        <v>0.0000475295336787565</v>
+        <v>0.000000000000013282128503575</v>
       </c>
       <c r="C66" t="n">
-        <v>0.00003885</v>
+        <v>0.00000000000000764348207483634</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0000313</v>
+        <v>0.0000000000000311489270694077</v>
       </c>
       <c r="E66" t="n">
-        <v>0.000000000920467541080681</v>
+        <v>0.00000000000000000000000000167646198580043</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0000015442250274627</v>
+        <v>0.00000000000000208402633532361</v>
       </c>
     </row>
     <row r="67">
@@ -2504,19 +2510,19 @@
         <v>71</v>
       </c>
       <c r="B67" t="n">
-        <v>47529.5336787565</v>
+        <v>0.0000475295336787565</v>
       </c>
       <c r="C67" t="n">
-        <v>38850</v>
+        <v>0.00003885</v>
       </c>
       <c r="D67" t="n">
-        <v>31300</v>
+        <v>0.0000313</v>
       </c>
       <c r="E67" t="n">
-        <v>920467541.080681</v>
+        <v>0.000000000920467541080681</v>
       </c>
       <c r="F67" t="n">
-        <v>1544.2250274627</v>
+        <v>0.0000015442250274627</v>
       </c>
     </row>
     <row r="68">
@@ -2524,19 +2530,19 @@
         <v>72</v>
       </c>
       <c r="B68" t="n">
-        <v>47.5295336787565</v>
+        <v>47529.5336787565</v>
       </c>
       <c r="C68" t="n">
-        <v>38.85</v>
+        <v>38850</v>
       </c>
       <c r="D68" t="n">
-        <v>31.3</v>
+        <v>31300</v>
       </c>
       <c r="E68" t="n">
-        <v>920.467541080681</v>
+        <v>920467541.080681</v>
       </c>
       <c r="F68" t="n">
-        <v>1.5442250274627</v>
+        <v>1544.2250274627</v>
       </c>
     </row>
     <row r="69">
@@ -2544,19 +2550,19 @@
         <v>73</v>
       </c>
       <c r="B69" t="n">
-        <v>0.00000209040341012345</v>
+        <v>47.5295336787565</v>
       </c>
       <c r="C69" t="n">
-        <v>0.00000101629274240622</v>
+        <v>38.85</v>
       </c>
       <c r="D69" t="n">
-        <v>0.000000590661898058897</v>
+        <v>31.3</v>
       </c>
       <c r="E69" t="n">
-        <v>0.000000000027677618886188</v>
+        <v>920.467541080681</v>
       </c>
       <c r="F69" t="n">
-        <v>0.000000267775420587763</v>
+        <v>1.5442250274627</v>
       </c>
     </row>
     <row r="70">
@@ -2564,19 +2570,19 @@
         <v>74</v>
       </c>
       <c r="B70" t="n">
-        <v>2090.40341012345</v>
+        <v>0.00000209040341012345</v>
       </c>
       <c r="C70" t="n">
-        <v>1016.29274240622</v>
+        <v>0.00000101629274240622</v>
       </c>
       <c r="D70" t="n">
-        <v>590.661898058897</v>
+        <v>0.000000590661898058897</v>
       </c>
       <c r="E70" t="n">
-        <v>27677618.886188</v>
+        <v>0.000000000027677618886188</v>
       </c>
       <c r="F70" t="n">
-        <v>267.775420587763</v>
+        <v>0.000000267775420587763</v>
       </c>
     </row>
     <row r="71">
@@ -2584,19 +2590,19 @@
         <v>75</v>
       </c>
       <c r="B71" t="n">
-        <v>2.09040341012345</v>
+        <v>2090.40341012345</v>
       </c>
       <c r="C71" t="n">
-        <v>1.01629274240622</v>
+        <v>1016.29274240622</v>
       </c>
       <c r="D71" t="n">
-        <v>0.590661898058897</v>
+        <v>590.661898058897</v>
       </c>
       <c r="E71" t="n">
-        <v>27.677618886188</v>
+        <v>27677618.886188</v>
       </c>
       <c r="F71" t="n">
-        <v>0.267775420587763</v>
+        <v>267.775420587763</v>
       </c>
     </row>
     <row r="72">
@@ -2604,19 +2610,19 @@
         <v>76</v>
       </c>
       <c r="B72" t="n">
-        <v>0.00000938044789122566</v>
+        <v>2.09040341012345</v>
       </c>
       <c r="C72" t="n">
-        <v>0.00000960935403782059</v>
+        <v>1.01629274240622</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0000137447086672182</v>
+        <v>0.590661898058897</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0000000000251579879894806</v>
+        <v>27.677618886188</v>
       </c>
       <c r="F72" t="n">
-        <v>0.000000255296170530961</v>
+        <v>0.267775420587763</v>
       </c>
     </row>
     <row r="73">
@@ -2624,19 +2630,19 @@
         <v>77</v>
       </c>
       <c r="B73" t="n">
-        <v>9380.44789122566</v>
+        <v>0.00000938044789122566</v>
       </c>
       <c r="C73" t="n">
-        <v>9609.35403782059</v>
+        <v>0.00000960935403782059</v>
       </c>
       <c r="D73" t="n">
-        <v>13744.7086672182</v>
+        <v>0.0000137447086672182</v>
       </c>
       <c r="E73" t="n">
-        <v>25157987.9894806</v>
+        <v>0.0000000000251579879894806</v>
       </c>
       <c r="F73" t="n">
-        <v>255.296170530961</v>
+        <v>0.000000255296170530961</v>
       </c>
     </row>
     <row r="74">
@@ -2644,19 +2650,19 @@
         <v>78</v>
       </c>
       <c r="B74" t="n">
-        <v>9.38044789122566</v>
+        <v>9380.44789122566</v>
       </c>
       <c r="C74" t="n">
-        <v>9.60935403782059</v>
+        <v>9609.35403782059</v>
       </c>
       <c r="D74" t="n">
-        <v>13.7447086672182</v>
+        <v>13744.7086672182</v>
       </c>
       <c r="E74" t="n">
-        <v>25.1579879894806</v>
+        <v>25157987.9894806</v>
       </c>
       <c r="F74" t="n">
-        <v>0.255296170530961</v>
+        <v>255.296170530961</v>
       </c>
     </row>
     <row r="75">
@@ -2664,19 +2670,19 @@
         <v>79</v>
       </c>
       <c r="B75" t="n">
-        <v>0.00000467885981919574</v>
+        <v>9.38044789122566</v>
       </c>
       <c r="C75" t="n">
-        <v>0.00000276414084510179</v>
+        <v>9.60935403782059</v>
       </c>
       <c r="D75" t="n">
-        <v>0.00000142420356041839</v>
+        <v>13.7447086672182</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0000000000227672899017921</v>
+        <v>25.1579879894806</v>
       </c>
       <c r="F75" t="n">
-        <v>0.000000242863369666746</v>
+        <v>0.255296170530961</v>
       </c>
     </row>
     <row r="76">
@@ -2684,19 +2690,19 @@
         <v>80</v>
       </c>
       <c r="B76" t="n">
-        <v>4678.85981919574</v>
+        <v>0.00000467885981919574</v>
       </c>
       <c r="C76" t="n">
-        <v>2764.1408451018</v>
+        <v>0.00000276414084510179</v>
       </c>
       <c r="D76" t="n">
-        <v>1424.20356041839</v>
+        <v>0.00000142420356041839</v>
       </c>
       <c r="E76" t="n">
-        <v>22767289.9017921</v>
+        <v>0.0000000000227672899017921</v>
       </c>
       <c r="F76" t="n">
-        <v>242.863369666746</v>
+        <v>0.000000242863369666746</v>
       </c>
     </row>
     <row r="77">
@@ -2704,19 +2710,19 @@
         <v>81</v>
       </c>
       <c r="B77" t="n">
-        <v>4.67885981919574</v>
+        <v>4678.85981919574</v>
       </c>
       <c r="C77" t="n">
-        <v>2.7641408451018</v>
+        <v>2764.1408451018</v>
       </c>
       <c r="D77" t="n">
-        <v>1.42420356041839</v>
+        <v>1424.20356041839</v>
       </c>
       <c r="E77" t="n">
-        <v>22.7672899017921</v>
+        <v>22767289.9017921</v>
       </c>
       <c r="F77" t="n">
-        <v>0.242863369666746</v>
+        <v>242.863369666746</v>
       </c>
     </row>
     <row r="78">
@@ -2724,19 +2730,19 @@
         <v>82</v>
       </c>
       <c r="B78" t="n">
-        <v>0.000445417616580311</v>
+        <v>4.67885981919574</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0004685</v>
+        <v>2.7641408451018</v>
       </c>
       <c r="D78" t="n">
-        <v>0.000545</v>
+        <v>1.42420356041839</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0000000278731764161227</v>
+        <v>22.7672899017921</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0000084976644789126</v>
+        <v>0.242863369666746</v>
       </c>
     </row>
     <row r="79">
@@ -2744,19 +2750,19 @@
         <v>83</v>
       </c>
       <c r="B79" t="n">
-        <v>445417.616580311</v>
+        <v>0.000445417616580311</v>
       </c>
       <c r="C79" t="n">
-        <v>468500</v>
+        <v>0.0004685</v>
       </c>
       <c r="D79" t="n">
-        <v>545000</v>
+        <v>0.000545</v>
       </c>
       <c r="E79" t="n">
-        <v>27873176416.1227</v>
+        <v>0.0000000278731764161227</v>
       </c>
       <c r="F79" t="n">
-        <v>8497.6644789126</v>
+        <v>0.0000084976644789126</v>
       </c>
     </row>
     <row r="80">
@@ -2764,19 +2770,19 @@
         <v>84</v>
       </c>
       <c r="B80" t="n">
-        <v>445.417616580311</v>
+        <v>445417.616580311</v>
       </c>
       <c r="C80" t="n">
-        <v>468.5</v>
+        <v>468500</v>
       </c>
       <c r="D80" t="n">
-        <v>545</v>
+        <v>545000</v>
       </c>
       <c r="E80" t="n">
-        <v>27873.1764161227</v>
+        <v>27873176416.1227</v>
       </c>
       <c r="F80" t="n">
-        <v>8.4976644789126</v>
+        <v>8497.6644789126</v>
       </c>
     </row>
     <row r="81">
@@ -2784,19 +2790,19 @@
         <v>85</v>
       </c>
       <c r="B81" t="n">
-        <v>0.000316880829015544</v>
+        <v>445.417616580311</v>
       </c>
       <c r="C81" t="n">
-        <v>0.000207</v>
+        <v>468.5</v>
       </c>
       <c r="D81" t="n">
-        <v>0.000168</v>
+        <v>545</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0000000775443805665837</v>
+        <v>27873.1764161227</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0000141736437669936</v>
+        <v>8.4976644789126</v>
       </c>
     </row>
     <row r="82">
@@ -2804,19 +2810,19 @@
         <v>86</v>
       </c>
       <c r="B82" t="n">
-        <v>316880.829015544</v>
+        <v>0.000316880829015544</v>
       </c>
       <c r="C82" t="n">
-        <v>207000</v>
+        <v>0.000207</v>
       </c>
       <c r="D82" t="n">
-        <v>168000</v>
+        <v>0.000168</v>
       </c>
       <c r="E82" t="n">
-        <v>77544380566.5837</v>
+        <v>0.0000000775443805665837</v>
       </c>
       <c r="F82" t="n">
-        <v>14173.6437669936</v>
+        <v>0.0000141736437669936</v>
       </c>
     </row>
     <row r="83">
@@ -2824,19 +2830,19 @@
         <v>87</v>
       </c>
       <c r="B83" t="n">
-        <v>316.880829015544</v>
+        <v>316880.829015544</v>
       </c>
       <c r="C83" t="n">
-        <v>207</v>
+        <v>207000</v>
       </c>
       <c r="D83" t="n">
-        <v>168</v>
+        <v>168000</v>
       </c>
       <c r="E83" t="n">
-        <v>77544.3805665837</v>
+        <v>77544380566.5837</v>
       </c>
       <c r="F83" t="n">
-        <v>14.1736437669936</v>
+        <v>14173.6437669936</v>
       </c>
     </row>
     <row r="84">
@@ -2844,19 +2850,19 @@
         <v>88</v>
       </c>
       <c r="B84" t="n">
-        <v>5.38370466321244</v>
+        <v>316.880829015544</v>
       </c>
       <c r="C84" t="n">
-        <v>3.192</v>
+        <v>207</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="E84" t="n">
-        <v>58.8082307333288</v>
+        <v>77544.3805665837</v>
       </c>
       <c r="F84" t="n">
-        <v>0.390324133715756</v>
+        <v>14.1736437669936</v>
       </c>
     </row>
     <row r="85">
@@ -2864,19 +2870,19 @@
         <v>89</v>
       </c>
       <c r="B85" t="n">
-        <v>0.000119058497409326</v>
+        <v>5.38370466321244</v>
       </c>
       <c r="C85" t="n">
-        <v>0.00007835</v>
+        <v>3.192</v>
       </c>
       <c r="D85" t="n">
-        <v>0.000139</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00000000991151759565843</v>
+        <v>58.8082307333288</v>
       </c>
       <c r="F85" t="n">
-        <v>0.00000506729777341965</v>
+        <v>0.390324133715756</v>
       </c>
     </row>
     <row r="86">
@@ -2884,19 +2890,19 @@
         <v>90</v>
       </c>
       <c r="B86" t="n">
-        <v>119058.497409326</v>
+        <v>0.000119058497409326</v>
       </c>
       <c r="C86" t="n">
-        <v>78350</v>
+        <v>0.00007835</v>
       </c>
       <c r="D86" t="n">
-        <v>139000</v>
+        <v>0.000139</v>
       </c>
       <c r="E86" t="n">
-        <v>9911517595.65843</v>
+        <v>0.00000000991151759565843</v>
       </c>
       <c r="F86" t="n">
-        <v>5067.29777341965</v>
+        <v>0.00000506729777341965</v>
       </c>
     </row>
     <row r="87">
@@ -2904,19 +2910,19 @@
         <v>91</v>
       </c>
       <c r="B87" t="n">
-        <v>119.058497409326</v>
+        <v>119058.497409326</v>
       </c>
       <c r="C87" t="n">
-        <v>78.35</v>
+        <v>78350</v>
       </c>
       <c r="D87" t="n">
-        <v>139</v>
+        <v>139000</v>
       </c>
       <c r="E87" t="n">
-        <v>9911.51759565844</v>
+        <v>9911517595.65843</v>
       </c>
       <c r="F87" t="n">
-        <v>5.06729777341965</v>
+        <v>5067.29777341965</v>
       </c>
     </row>
     <row r="88">
@@ -2924,19 +2930,19 @@
         <v>92</v>
       </c>
       <c r="B88" t="n">
-        <v>0.000000000000649330917553544</v>
+        <v>119.058497409326</v>
       </c>
       <c r="C88" t="n">
-        <v>0.000000000000473992050408704</v>
+        <v>78.35</v>
       </c>
       <c r="D88" t="n">
-        <v>0.000000000000167530301195192</v>
+        <v>139</v>
       </c>
       <c r="E88" t="n">
-        <v>0.000000000000000000000000466522499852699</v>
+        <v>9911.51759565844</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0000000000000347650329004844</v>
+        <v>5.06729777341965</v>
       </c>
     </row>
     <row r="89">
@@ -2944,19 +2950,19 @@
         <v>93</v>
       </c>
       <c r="B89" t="n">
-        <v>0.000000649330917553544</v>
+        <v>0.000000000000649330917553544</v>
       </c>
       <c r="C89" t="n">
-        <v>0.000000473992050408704</v>
+        <v>0.000000000000473992050408704</v>
       </c>
       <c r="D89" t="n">
-        <v>0.000000167530301195192</v>
+        <v>0.000000000000167530301195192</v>
       </c>
       <c r="E89" t="n">
-        <v>0.0000000000004665224998527</v>
+        <v>0.000000000000000000000000466522499852699</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0000000347650329004844</v>
+        <v>0.0000000000000347650329004844</v>
       </c>
     </row>
     <row r="90">
@@ -2964,19 +2970,19 @@
         <v>94</v>
       </c>
       <c r="B90" t="n">
-        <v>0.000000000649330917553545</v>
+        <v>0.000000649330917553544</v>
       </c>
       <c r="C90" t="n">
-        <v>0.000000000473992050408704</v>
+        <v>0.000000473992050408704</v>
       </c>
       <c r="D90" t="n">
-        <v>0.000000000167530301195192</v>
+        <v>0.000000167530301195192</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0000000000000000004665224998527</v>
+        <v>0.0000000000004665224998527</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0000000000347650329004844</v>
+        <v>0.0000000347650329004844</v>
       </c>
     </row>
     <row r="91">
@@ -2984,19 +2990,19 @@
         <v>95</v>
       </c>
       <c r="B91" t="n">
-        <v>0.00000794268258312364</v>
+        <v>0.000000000649330917553545</v>
       </c>
       <c r="C91" t="n">
-        <v>0.00000588709151283506</v>
+        <v>0.000000000473992050408704</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0000033540083254624</v>
+        <v>0.000000000167530301195192</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0000000000553358738464153</v>
+        <v>0.0000000000000000004665224998527</v>
       </c>
       <c r="F91" t="n">
-        <v>0.000000378625390235005</v>
+        <v>0.0000000000347650329004844</v>
       </c>
     </row>
     <row r="92">
@@ -3004,19 +3010,19 @@
         <v>96</v>
       </c>
       <c r="B92" t="n">
-        <v>7942.68258312364</v>
+        <v>0.00000794268258312364</v>
       </c>
       <c r="C92" t="n">
-        <v>5887.09151283506</v>
+        <v>0.00000588709151283506</v>
       </c>
       <c r="D92" t="n">
-        <v>3354.0083254624</v>
+        <v>0.0000033540083254624</v>
       </c>
       <c r="E92" t="n">
-        <v>55335873.8464153</v>
+        <v>0.0000000000553358738464153</v>
       </c>
       <c r="F92" t="n">
-        <v>378.625390235005</v>
+        <v>0.000000378625390235005</v>
       </c>
     </row>
     <row r="93">
@@ -3024,19 +3030,19 @@
         <v>97</v>
       </c>
       <c r="B93" t="n">
-        <v>7.94268258312364</v>
+        <v>7942.68258312364</v>
       </c>
       <c r="C93" t="n">
-        <v>5.88709151283506</v>
+        <v>5887.09151283506</v>
       </c>
       <c r="D93" t="n">
-        <v>3.3540083254624</v>
+        <v>3354.0083254624</v>
       </c>
       <c r="E93" t="n">
-        <v>55.3358738464153</v>
+        <v>55335873.8464153</v>
       </c>
       <c r="F93" t="n">
-        <v>0.378625390235005</v>
+        <v>378.625390235005</v>
       </c>
     </row>
     <row r="94">
@@ -3044,19 +3050,19 @@
         <v>98</v>
       </c>
       <c r="B94" t="n">
-        <v>0.000000341822637193483</v>
+        <v>7.94268258312364</v>
       </c>
       <c r="C94" t="n">
-        <v>0.000000177363523669142</v>
+        <v>5.88709151283506</v>
       </c>
       <c r="D94" t="n">
-        <v>0.000000255222963378883</v>
+        <v>3.3540083254624</v>
       </c>
       <c r="E94" t="n">
-        <v>0.000000000000263275877032095</v>
+        <v>55.3358738464153</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0000000261163140124348</v>
+        <v>0.378625390235005</v>
       </c>
     </row>
     <row r="95">
@@ -3064,19 +3070,19 @@
         <v>99</v>
       </c>
       <c r="B95" t="n">
-        <v>341.822637193483</v>
+        <v>0.000000341822637193483</v>
       </c>
       <c r="C95" t="n">
-        <v>177.363523669143</v>
+        <v>0.000000177363523669142</v>
       </c>
       <c r="D95" t="n">
-        <v>255.222963378883</v>
+        <v>0.000000255222963378883</v>
       </c>
       <c r="E95" t="n">
-        <v>263275.877032095</v>
+        <v>0.000000000000263275877032095</v>
       </c>
       <c r="F95" t="n">
-        <v>26.1163140124348</v>
+        <v>0.0000000261163140124348</v>
       </c>
     </row>
     <row r="96">
@@ -3084,19 +3090,19 @@
         <v>100</v>
       </c>
       <c r="B96" t="n">
-        <v>0.341822637193483</v>
+        <v>341.822637193483</v>
       </c>
       <c r="C96" t="n">
-        <v>0.177363523669142</v>
+        <v>177.363523669143</v>
       </c>
       <c r="D96" t="n">
-        <v>0.255222963378883</v>
+        <v>255.222963378883</v>
       </c>
       <c r="E96" t="n">
-        <v>0.263275877032095</v>
+        <v>263275.877032095</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0261163140124348</v>
+        <v>26.1163140124348</v>
       </c>
     </row>
     <row r="97">
@@ -3104,19 +3110,19 @@
         <v>101</v>
       </c>
       <c r="B97" t="n">
-        <v>0.000000133864061126652</v>
+        <v>0.341822637193483</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0000000500167711692256</v>
+        <v>0.177363523669142</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0000000179935248922902</v>
+        <v>0.255222963378883</v>
       </c>
       <c r="E97" t="n">
-        <v>0.000000000000365142881890716</v>
+        <v>0.263275877032095</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0000000307565605239098</v>
+        <v>0.0261163140124348</v>
       </c>
     </row>
     <row r="98">
@@ -3124,19 +3130,19 @@
         <v>102</v>
       </c>
       <c r="B98" t="n">
-        <v>133.864061126652</v>
+        <v>0.000000133864061126652</v>
       </c>
       <c r="C98" t="n">
-        <v>50.0167711692256</v>
+        <v>0.0000000500167711692256</v>
       </c>
       <c r="D98" t="n">
-        <v>17.9935248922902</v>
+        <v>0.0000000179935248922902</v>
       </c>
       <c r="E98" t="n">
-        <v>365142.881890716</v>
+        <v>0.000000000000365142881890716</v>
       </c>
       <c r="F98" t="n">
-        <v>30.7565605239098</v>
+        <v>0.0000000307565605239098</v>
       </c>
     </row>
     <row r="99">
@@ -3144,19 +3150,19 @@
         <v>103</v>
       </c>
       <c r="B99" t="n">
-        <v>0.133864061126652</v>
+        <v>133.864061126652</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0500167711692256</v>
+        <v>50.0167711692256</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0179935248922902</v>
+        <v>17.9935248922902</v>
       </c>
       <c r="E99" t="n">
-        <v>0.365142881890717</v>
+        <v>365142.881890716</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0307565605239098</v>
+        <v>30.7565605239098</v>
       </c>
     </row>
     <row r="100">
@@ -3164,19 +3170,19 @@
         <v>104</v>
       </c>
       <c r="B100" t="n">
-        <v>0.00000270864500942482</v>
+        <v>0.133864061126652</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0000021748491725957</v>
+        <v>0.0500167711692256</v>
       </c>
       <c r="D100" t="n">
-        <v>0.00000100804581781855</v>
+        <v>0.0179935248922902</v>
       </c>
       <c r="E100" t="n">
-        <v>0.00000000000484428398959457</v>
+        <v>0.365142881890717</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0000001120265973877</v>
+        <v>0.0307565605239098</v>
       </c>
     </row>
     <row r="101">
@@ -3184,19 +3190,19 @@
         <v>105</v>
       </c>
       <c r="B101" t="n">
-        <v>2708.64500942482</v>
+        <v>0.00000270864500942482</v>
       </c>
       <c r="C101" t="n">
-        <v>2174.8491725957</v>
+        <v>0.0000021748491725957</v>
       </c>
       <c r="D101" t="n">
-        <v>1008.04581781855</v>
+        <v>0.00000100804581781855</v>
       </c>
       <c r="E101" t="n">
-        <v>4844283.98959458</v>
+        <v>0.00000000000484428398959457</v>
       </c>
       <c r="F101" t="n">
-        <v>112.0265973877</v>
+        <v>0.0000001120265973877</v>
       </c>
     </row>
     <row r="102">
@@ -3204,19 +3210,19 @@
         <v>106</v>
       </c>
       <c r="B102" t="n">
-        <v>2.70864500942482</v>
+        <v>2708.64500942482</v>
       </c>
       <c r="C102" t="n">
-        <v>2.1748491725957</v>
+        <v>2174.8491725957</v>
       </c>
       <c r="D102" t="n">
-        <v>1.00804581781855</v>
+        <v>1008.04581781855</v>
       </c>
       <c r="E102" t="n">
-        <v>4.84428398959457</v>
+        <v>4844283.98959458</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1120265973877</v>
+        <v>112.0265973877</v>
       </c>
     </row>
     <row r="103">
@@ -3224,19 +3230,19 @@
         <v>107</v>
       </c>
       <c r="B103" t="n">
-        <v>0.000000603709455244407</v>
+        <v>2.70864500942482</v>
       </c>
       <c r="C103" t="n">
-        <v>0.000000258505991723723</v>
+        <v>2.1748491725957</v>
       </c>
       <c r="D103" t="n">
-        <v>0.000000103099850434774</v>
+        <v>1.00804581781855</v>
       </c>
       <c r="E103" t="n">
-        <v>0.00000000000290671820307297</v>
+        <v>4.84428398959457</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0000000867776355926408</v>
+        <v>0.1120265973877</v>
       </c>
     </row>
     <row r="104">
@@ -3244,19 +3250,19 @@
         <v>108</v>
       </c>
       <c r="B104" t="n">
-        <v>603.709455244407</v>
+        <v>0.000000603709455244407</v>
       </c>
       <c r="C104" t="n">
-        <v>258.505991723723</v>
+        <v>0.000000258505991723723</v>
       </c>
       <c r="D104" t="n">
-        <v>103.099850434774</v>
+        <v>0.000000103099850434774</v>
       </c>
       <c r="E104" t="n">
-        <v>2906718.20307297</v>
+        <v>0.00000000000290671820307297</v>
       </c>
       <c r="F104" t="n">
-        <v>86.7776355926407</v>
+        <v>0.0000000867776355926408</v>
       </c>
     </row>
     <row r="105">
@@ -3264,19 +3270,19 @@
         <v>109</v>
       </c>
       <c r="B105" t="n">
-        <v>0.603709455244407</v>
+        <v>603.709455244407</v>
       </c>
       <c r="C105" t="n">
-        <v>0.258505991723723</v>
+        <v>258.505991723723</v>
       </c>
       <c r="D105" t="n">
-        <v>0.103099850434774</v>
+        <v>103.099850434774</v>
       </c>
       <c r="E105" t="n">
-        <v>2.90671820307297</v>
+        <v>2906718.20307297</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0867776355926408</v>
+        <v>86.7776355926407</v>
       </c>
     </row>
     <row r="106">
@@ -3284,19 +3290,19 @@
         <v>110</v>
       </c>
       <c r="B106" t="n">
-        <v>0.0000000519865296818508</v>
+        <v>0.603709455244407</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0000000336834271583058</v>
+        <v>0.258505991723723</v>
       </c>
       <c r="D106" t="n">
-        <v>0.00000000589621592153962</v>
+        <v>0.103099850434774</v>
       </c>
       <c r="E106" t="n">
-        <v>0.00000000000000246463521261005</v>
+        <v>2.90671820307297</v>
       </c>
       <c r="F106" t="n">
-        <v>0.00000000252686867835324</v>
+        <v>0.0867776355926408</v>
       </c>
     </row>
     <row r="107">
@@ -3304,19 +3310,19 @@
         <v>111</v>
       </c>
       <c r="B107" t="n">
-        <v>51.9865296818509</v>
+        <v>0.0000000519865296818508</v>
       </c>
       <c r="C107" t="n">
-        <v>33.6834271583058</v>
+        <v>0.0000000336834271583058</v>
       </c>
       <c r="D107" t="n">
-        <v>5.89621592153962</v>
+        <v>0.00000000589621592153962</v>
       </c>
       <c r="E107" t="n">
-        <v>2464.63521261005</v>
+        <v>0.00000000000000246463521261005</v>
       </c>
       <c r="F107" t="n">
-        <v>2.52686867835324</v>
+        <v>0.00000000252686867835324</v>
       </c>
     </row>
     <row r="108">
@@ -3324,19 +3330,19 @@
         <v>112</v>
       </c>
       <c r="B108" t="n">
-        <v>0.0519865296818509</v>
+        <v>51.9865296818509</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0336834271583058</v>
+        <v>33.6834271583058</v>
       </c>
       <c r="D108" t="n">
-        <v>0.00589621592153962</v>
+        <v>5.89621592153962</v>
       </c>
       <c r="E108" t="n">
-        <v>0.00246463521261005</v>
+        <v>2464.63521261005</v>
       </c>
       <c r="F108" t="n">
-        <v>0.00252686867835324</v>
+        <v>2.52686867835324</v>
       </c>
     </row>
     <row r="109">
@@ -3344,19 +3350,19 @@
         <v>113</v>
       </c>
       <c r="B109" t="n">
-        <v>15.9842227979275</v>
+        <v>0.0519865296818509</v>
       </c>
       <c r="C109" t="n">
-        <v>15.1</v>
+        <v>0.0336834271583058</v>
       </c>
       <c r="D109" t="n">
-        <v>22.9</v>
+        <v>0.00589621592153962</v>
       </c>
       <c r="E109" t="n">
-        <v>25.1199138099724</v>
+        <v>0.00246463521261005</v>
       </c>
       <c r="F109" t="n">
-        <v>0.25510291436404</v>
+        <v>0.00252686867835324</v>
       </c>
     </row>
     <row r="110">
@@ -3364,19 +3370,19 @@
         <v>114</v>
       </c>
       <c r="B110" t="n">
-        <v>0.471360103626943</v>
+        <v>15.9842227979275</v>
       </c>
       <c r="C110" t="n">
-        <v>0.272</v>
+        <v>15.1</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="E110" t="n">
-        <v>0.239067586871678</v>
+        <v>25.1199138099724</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0248866647017723</v>
+        <v>0.25510291436404</v>
       </c>
     </row>
     <row r="111">
@@ -3384,19 +3390,19 @@
         <v>115</v>
       </c>
       <c r="B111" t="n">
-        <v>0.00000000506395885836771</v>
+        <v>0.471360103626943</v>
       </c>
       <c r="C111" t="n">
-        <v>0.00000000284846313203247</v>
+        <v>0.272</v>
       </c>
       <c r="D111" t="n">
-        <v>0.00000000110375675266283</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0000000000000000852360090088939</v>
+        <v>0.239067586871678</v>
       </c>
       <c r="F111" t="n">
-        <v>0.00000000046991347734327</v>
+        <v>0.0248866647017723</v>
       </c>
     </row>
     <row r="112">
@@ -3404,19 +3410,19 @@
         <v>116</v>
       </c>
       <c r="B112" t="n">
-        <v>5.06395885836771</v>
+        <v>0.00000000506395885836771</v>
       </c>
       <c r="C112" t="n">
-        <v>2.84846313203246</v>
+        <v>0.00000000284846313203247</v>
       </c>
       <c r="D112" t="n">
-        <v>1.10375675266283</v>
+        <v>0.00000000110375675266283</v>
       </c>
       <c r="E112" t="n">
-        <v>85.2360090088939</v>
+        <v>0.0000000000000000852360090088939</v>
       </c>
       <c r="F112" t="n">
-        <v>0.46991347734327</v>
+        <v>0.00000000046991347734327</v>
       </c>
     </row>
     <row r="113">
@@ -3424,19 +3430,19 @@
         <v>117</v>
       </c>
       <c r="B113" t="n">
-        <v>0.00506395885836771</v>
+        <v>5.06395885836771</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00284846313203246</v>
+        <v>2.84846313203246</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00110375675266283</v>
+        <v>1.10375675266283</v>
       </c>
       <c r="E113" t="n">
-        <v>0.0000852360090088939</v>
+        <v>85.2360090088939</v>
       </c>
       <c r="F113" t="n">
-        <v>0.000469913477343271</v>
+        <v>0.46991347734327</v>
       </c>
     </row>
     <row r="114">
@@ -3444,19 +3450,19 @@
         <v>118</v>
       </c>
       <c r="B114" t="n">
-        <v>0.0000000000147572279928087</v>
+        <v>0.00506395885836771</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00000000000805710489645839</v>
+        <v>0.00284846313203246</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00000000000358241539731574</v>
+        <v>0.00110375675266283</v>
       </c>
       <c r="E114" t="n">
-        <v>0.000000000000000000000425813751448312</v>
+        <v>0.0000852360090088939</v>
       </c>
       <c r="F114" t="n">
-        <v>0.00000000000105030682840964</v>
+        <v>0.000469913477343271</v>
       </c>
     </row>
     <row r="115">
@@ -3464,19 +3470,19 @@
         <v>119</v>
       </c>
       <c r="B115" t="n">
-        <v>0.0147572279928087</v>
+        <v>0.0000000000147572279928087</v>
       </c>
       <c r="C115" t="n">
-        <v>0.00805710489645839</v>
+        <v>0.00000000000805710489645839</v>
       </c>
       <c r="D115" t="n">
-        <v>0.00358241539731574</v>
+        <v>0.00000000000358241539731574</v>
       </c>
       <c r="E115" t="n">
-        <v>0.000425813751448312</v>
+        <v>0.000000000000000000000425813751448312</v>
       </c>
       <c r="F115" t="n">
-        <v>0.00105030682840964</v>
+        <v>0.00000000000105030682840964</v>
       </c>
     </row>
     <row r="116">
@@ -3484,19 +3490,19 @@
         <v>120</v>
       </c>
       <c r="B116" t="n">
-        <v>0.0000147572279928087</v>
+        <v>0.0147572279928087</v>
       </c>
       <c r="C116" t="n">
-        <v>0.00000805710489645839</v>
+        <v>0.00805710489645839</v>
       </c>
       <c r="D116" t="n">
-        <v>0.00000358241539731574</v>
+        <v>0.00358241539731574</v>
       </c>
       <c r="E116" t="n">
-        <v>0.000000000425813751448312</v>
+        <v>0.000425813751448312</v>
       </c>
       <c r="F116" t="n">
-        <v>0.00000105030682840964</v>
+        <v>0.00105030682840964</v>
       </c>
     </row>
     <row r="117">
@@ -3504,19 +3510,19 @@
         <v>121</v>
       </c>
       <c r="B117" t="n">
-        <v>0.0000000214169343633855</v>
+        <v>0.0000147572279928087</v>
       </c>
       <c r="C117" t="n">
-        <v>0.0000000192688895950255</v>
+        <v>0.00000805710489645839</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0000000169367826430289</v>
+        <v>0.00000358241539731574</v>
       </c>
       <c r="E117" t="n">
-        <v>0.000000000000000270778983478396</v>
+        <v>0.000000000425813751448312</v>
       </c>
       <c r="F117" t="n">
-        <v>0.00000000083755594272736</v>
+        <v>0.00000105030682840964</v>
       </c>
     </row>
     <row r="118">
@@ -3524,19 +3530,19 @@
         <v>122</v>
       </c>
       <c r="B118" t="n">
-        <v>21.4169343633855</v>
+        <v>0.0000000214169343633855</v>
       </c>
       <c r="C118" t="n">
-        <v>19.2688895950255</v>
+        <v>0.0000000192688895950255</v>
       </c>
       <c r="D118" t="n">
-        <v>16.9367826430289</v>
+        <v>0.0000000169367826430289</v>
       </c>
       <c r="E118" t="n">
-        <v>270.778983478396</v>
+        <v>0.000000000000000270778983478396</v>
       </c>
       <c r="F118" t="n">
-        <v>0.83755594272736</v>
+        <v>0.00000000083755594272736</v>
       </c>
     </row>
     <row r="119">
@@ -3544,19 +3550,19 @@
         <v>123</v>
       </c>
       <c r="B119" t="n">
-        <v>0.0214169343633855</v>
+        <v>21.4169343633855</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0192688895950255</v>
+        <v>19.2688895950255</v>
       </c>
       <c r="D119" t="n">
-        <v>0.0169367826430289</v>
+        <v>16.9367826430289</v>
       </c>
       <c r="E119" t="n">
-        <v>0.000270778983478396</v>
+        <v>270.778983478396</v>
       </c>
       <c r="F119" t="n">
-        <v>0.00083755594272736</v>
+        <v>0.83755594272736</v>
       </c>
     </row>
     <row r="120">
@@ -3564,19 +3570,19 @@
         <v>124</v>
       </c>
       <c r="B120" t="n">
-        <v>0.00000000060205647047297</v>
+        <v>0.0214169343633855</v>
       </c>
       <c r="C120" t="n">
-        <v>0.000000000336314268101212</v>
+        <v>0.0192688895950255</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0000000000859046722645473</v>
+        <v>0.0169367826430289</v>
       </c>
       <c r="E120" t="n">
-        <v>0.00000000000000000149197490951298</v>
+        <v>0.000270778983478396</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0000000000621708932928549</v>
+        <v>0.00083755594272736</v>
       </c>
     </row>
     <row r="121">
@@ -3584,19 +3590,19 @@
         <v>125</v>
       </c>
       <c r="B121" t="n">
-        <v>0.60205647047297</v>
+        <v>0.00000000060205647047297</v>
       </c>
       <c r="C121" t="n">
-        <v>0.336314268101212</v>
+        <v>0.000000000336314268101212</v>
       </c>
       <c r="D121" t="n">
-        <v>0.0859046722645473</v>
+        <v>0.0000000000859046722645473</v>
       </c>
       <c r="E121" t="n">
-        <v>1.49197490951298</v>
+        <v>0.00000000000000000149197490951298</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0621708932928549</v>
+        <v>0.0000000000621708932928549</v>
       </c>
     </row>
     <row r="122">
@@ -3604,19 +3610,19 @@
         <v>126</v>
       </c>
       <c r="B122" t="n">
-        <v>0.00060205647047297</v>
+        <v>0.60205647047297</v>
       </c>
       <c r="C122" t="n">
-        <v>0.000336314268101212</v>
+        <v>0.336314268101212</v>
       </c>
       <c r="D122" t="n">
-        <v>0.0000859046722645473</v>
+        <v>0.0859046722645473</v>
       </c>
       <c r="E122" t="n">
-        <v>0.00000149197490951298</v>
+        <v>1.49197490951298</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0000621708932928549</v>
+        <v>0.0621708932928549</v>
       </c>
     </row>
     <row r="123">
@@ -3624,19 +3630,19 @@
         <v>127</v>
       </c>
       <c r="B123" t="n">
-        <v>0.000000000276590271366244</v>
+        <v>0.00060205647047297</v>
       </c>
       <c r="C123" t="n">
-        <v>0.000000000155243637389724</v>
+        <v>0.000336314268101212</v>
       </c>
       <c r="D123" t="n">
-        <v>0.0000000000459837445898614</v>
+        <v>0.0000859046722645473</v>
       </c>
       <c r="E123" t="n">
-        <v>0.0000000000000000000920825416545141</v>
+        <v>0.00000149197490951298</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0000000000154452519369259</v>
+        <v>0.0000621708932928549</v>
       </c>
     </row>
     <row r="124">
@@ -3644,19 +3650,19 @@
         <v>128</v>
       </c>
       <c r="B124" t="n">
-        <v>0.276590271366244</v>
+        <v>0.000000000276590271366244</v>
       </c>
       <c r="C124" t="n">
-        <v>0.155243637389723</v>
+        <v>0.000000000155243637389724</v>
       </c>
       <c r="D124" t="n">
-        <v>0.0459837445898614</v>
+        <v>0.0000000000459837445898614</v>
       </c>
       <c r="E124" t="n">
-        <v>0.0920825416545141</v>
+        <v>0.0000000000000000000920825416545141</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0154452519369259</v>
+        <v>0.0000000000154452519369259</v>
       </c>
     </row>
     <row r="125">
@@ -3664,19 +3670,19 @@
         <v>129</v>
       </c>
       <c r="B125" t="n">
-        <v>0.000276590271366244</v>
+        <v>0.276590271366244</v>
       </c>
       <c r="C125" t="n">
-        <v>0.000155243637389724</v>
+        <v>0.155243637389723</v>
       </c>
       <c r="D125" t="n">
-        <v>0.0000459837445898614</v>
+        <v>0.0459837445898614</v>
       </c>
       <c r="E125" t="n">
-        <v>0.0000000920825416545141</v>
+        <v>0.0920825416545141</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0000154452519369259</v>
+        <v>0.0154452519369259</v>
       </c>
     </row>
     <row r="126">
@@ -3684,19 +3690,19 @@
         <v>130</v>
       </c>
       <c r="B126" t="n">
-        <v>0.0000000000000000999611447355286</v>
+        <v>0.000276590271366244</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0000000000000000999736510206449</v>
+        <v>0.000155243637389724</v>
       </c>
       <c r="D126" t="n">
-        <v>0.0000000000000000999780450040587</v>
+        <v>0.0000459837445898614</v>
       </c>
       <c r="E126" t="n">
-        <v>0.00000000000000000000000000000000000000506188512693348</v>
+        <v>0.0000000920825416545141</v>
       </c>
       <c r="F126" t="n">
-        <v>0.00000000000000000000362128320332555</v>
+        <v>0.0000154452519369259</v>
       </c>
     </row>
     <row r="127">
@@ -3704,19 +3710,19 @@
         <v>131</v>
       </c>
       <c r="B127" t="n">
-        <v>0.0000000999611447355286</v>
+        <v>0.0000000000000000999611447355286</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0000000999736510206449</v>
+        <v>0.0000000000000000999736510206449</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0000000999780450040587</v>
+        <v>0.0000000000000000999780450040587</v>
       </c>
       <c r="E127" t="n">
-        <v>0.00000000000000000000506188512693352</v>
+        <v>0.00000000000000000000000000000000000000506188512693348</v>
       </c>
       <c r="F127" t="n">
-        <v>0.00000000000362128320332557</v>
+        <v>0.00000000000000000000362128320332555</v>
       </c>
     </row>
     <row r="128">
@@ -3724,19 +3730,19 @@
         <v>132</v>
       </c>
       <c r="B128" t="n">
-        <v>0.0000000000999611447355286</v>
+        <v>0.0000000999611447355286</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0000000000999736510206449</v>
+        <v>0.0000000999736510206449</v>
       </c>
       <c r="D128" t="n">
-        <v>0.0000000000999780450040587</v>
+        <v>0.0000000999780450040587</v>
       </c>
       <c r="E128" t="n">
-        <v>0.00000000000000000000000000506188512693352</v>
+        <v>0.00000000000000000000506188512693352</v>
       </c>
       <c r="F128" t="n">
-        <v>0.00000000000000362128320332557</v>
+        <v>0.00000000000362128320332557</v>
       </c>
     </row>
     <row r="129">
@@ -3744,19 +3750,19 @@
         <v>133</v>
       </c>
       <c r="B129" t="n">
-        <v>0.000000104099137305699</v>
+        <v>0.0000000000999611447355286</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0000000819</v>
+        <v>0.0000000000999736510206449</v>
       </c>
       <c r="D129" t="n">
-        <v>0.000000104</v>
+        <v>0.0000000000999780450040587</v>
       </c>
       <c r="E129" t="n">
-        <v>0.00000000000000533434632790058</v>
+        <v>0.00000000000000000000000000506188512693352</v>
       </c>
       <c r="F129" t="n">
-        <v>0.00000000371746554419557</v>
+        <v>0.00000000000000362128320332557</v>
       </c>
     </row>
     <row r="130">
@@ -3764,19 +3770,19 @@
         <v>134</v>
       </c>
       <c r="B130" t="n">
-        <v>0.00000000142520515740162</v>
+        <v>0.000000104099137305699</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0000000000755096679627698</v>
+        <v>0.0000000819</v>
       </c>
       <c r="D130" t="n">
-        <v>0.00000000000747961848707179</v>
+        <v>0.000000104</v>
       </c>
       <c r="E130" t="n">
-        <v>0.0000000000000000928226715323519</v>
+        <v>0.00000000000000533434632790058</v>
       </c>
       <c r="F130" t="n">
-        <v>0.000000000490380711602519</v>
+        <v>0.00000000371746554419557</v>
       </c>
     </row>
     <row r="131">
@@ -3784,19 +3790,19 @@
         <v>135</v>
       </c>
       <c r="B131" t="n">
-        <v>1.42520515740162</v>
+        <v>0.00000000142520515740162</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0755096679627698</v>
+        <v>0.0000000000755096679627698</v>
       </c>
       <c r="D131" t="n">
-        <v>0.00747961848707179</v>
+        <v>0.00000000000747961848707179</v>
       </c>
       <c r="E131" t="n">
-        <v>92.8226715323519</v>
+        <v>0.0000000000000000928226715323519</v>
       </c>
       <c r="F131" t="n">
-        <v>0.490380711602519</v>
+        <v>0.000000000490380711602519</v>
       </c>
     </row>
     <row r="132">
@@ -3804,19 +3810,19 @@
         <v>136</v>
       </c>
       <c r="B132" t="n">
-        <v>0.00142520515740163</v>
+        <v>1.42520515740162</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0000755096679627698</v>
+        <v>0.0755096679627698</v>
       </c>
       <c r="D132" t="n">
-        <v>0.00000747961848707179</v>
+        <v>0.00747961848707179</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0000928226715323519</v>
+        <v>92.8226715323519</v>
       </c>
       <c r="F132" t="n">
-        <v>0.000490380711602519</v>
+        <v>0.490380711602519</v>
       </c>
     </row>
     <row r="133">
@@ -3824,19 +3830,19 @@
         <v>137</v>
       </c>
       <c r="B133" t="n">
-        <v>0.00000951983439345315</v>
+        <v>0.00142520515740163</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0000095306386356242</v>
+        <v>0.0000755096679627698</v>
       </c>
       <c r="D133" t="n">
-        <v>0.0000152877237269422</v>
+        <v>0.00000747961848707179</v>
       </c>
       <c r="E133" t="n">
-        <v>0.000000000015045222786518</v>
+        <v>0.0000928226715323519</v>
       </c>
       <c r="F133" t="n">
-        <v>0.000000197426596751727</v>
+        <v>0.000490380711602519</v>
       </c>
     </row>
     <row r="134">
@@ -3844,19 +3850,19 @@
         <v>138</v>
       </c>
       <c r="B134" t="n">
-        <v>9519.83439345315</v>
+        <v>0.00000951983439345315</v>
       </c>
       <c r="C134" t="n">
-        <v>9530.6386356242</v>
+        <v>0.0000095306386356242</v>
       </c>
       <c r="D134" t="n">
-        <v>15287.7237269422</v>
+        <v>0.0000152877237269422</v>
       </c>
       <c r="E134" t="n">
-        <v>15045222.786518</v>
+        <v>0.000000000015045222786518</v>
       </c>
       <c r="F134" t="n">
-        <v>197.426596751727</v>
+        <v>0.000000197426596751727</v>
       </c>
     </row>
     <row r="135">
@@ -3864,19 +3870,19 @@
         <v>139</v>
       </c>
       <c r="B135" t="n">
-        <v>9.51983439345315</v>
+        <v>9519.83439345315</v>
       </c>
       <c r="C135" t="n">
-        <v>9.5306386356242</v>
+        <v>9530.6386356242</v>
       </c>
       <c r="D135" t="n">
-        <v>15.2877237269422</v>
+        <v>15287.7237269422</v>
       </c>
       <c r="E135" t="n">
-        <v>15.045222786518</v>
+        <v>15045222.786518</v>
       </c>
       <c r="F135" t="n">
-        <v>0.197426596751727</v>
+        <v>197.426596751727</v>
       </c>
     </row>
     <row r="136">
@@ -3884,19 +3890,19 @@
         <v>140</v>
       </c>
       <c r="B136" t="n">
-        <v>104.099137305699</v>
+        <v>9.51983439345315</v>
       </c>
       <c r="C136" t="n">
-        <v>81.9</v>
+        <v>9.5306386356242</v>
       </c>
       <c r="D136" t="n">
-        <v>104</v>
+        <v>15.2877237269422</v>
       </c>
       <c r="E136" t="n">
-        <v>5334.34632790058</v>
+        <v>15.045222786518</v>
       </c>
       <c r="F136" t="n">
-        <v>3.71746554419557</v>
+        <v>0.197426596751727</v>
       </c>
     </row>
     <row r="137">
@@ -3904,19 +3910,19 @@
         <v>141</v>
       </c>
       <c r="B137" t="n">
-        <v>0.104099137305699</v>
+        <v>104.099137305699</v>
       </c>
       <c r="C137" t="n">
-        <v>0.0819</v>
+        <v>81.9</v>
       </c>
       <c r="D137" t="n">
-        <v>0.104</v>
+        <v>104</v>
       </c>
       <c r="E137" t="n">
-        <v>0.00533434632790058</v>
+        <v>5334.34632790058</v>
       </c>
       <c r="F137" t="n">
-        <v>0.00371746554419557</v>
+        <v>3.71746554419557</v>
       </c>
     </row>
     <row r="138">
@@ -3924,19 +3930,19 @@
         <v>142</v>
       </c>
       <c r="B138" t="n">
-        <v>-9.43059296294576</v>
+        <v>0.104099137305699</v>
       </c>
       <c r="C138" t="n">
-        <v>-9.40573397758987</v>
+        <v>0.0819</v>
       </c>
       <c r="D138" t="n">
-        <v>-9.38236632295615</v>
+        <v>0.104</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0100422896872455</v>
+        <v>0.00533434632790058</v>
       </c>
       <c r="F138" t="n">
-        <v>0.00510061707311408</v>
+        <v>0.00371746554419557</v>
       </c>
     </row>
     <row r="139">
@@ -3944,13 +3950,13 @@
         <v>143</v>
       </c>
       <c r="B139" t="n">
-        <v>-3.43059296294576</v>
+        <v>-9.43059296294576</v>
       </c>
       <c r="C139" t="n">
-        <v>-3.40573397758987</v>
+        <v>-9.40573397758987</v>
       </c>
       <c r="D139" t="n">
-        <v>-3.38236632295615</v>
+        <v>-9.38236632295615</v>
       </c>
       <c r="E139" t="n">
         <v>0.0100422896872455</v>
@@ -3964,13 +3970,13 @@
         <v>144</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.430592962945761</v>
+        <v>-3.43059296294576</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.405733977589867</v>
+        <v>-3.40573397758987</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.382366322956154</v>
+        <v>-3.38236632295615</v>
       </c>
       <c r="E140" t="n">
         <v>0.0100422896872455</v>
@@ -3984,13 +3990,13 @@
         <v>145</v>
       </c>
       <c r="B141" t="n">
-        <v>-6.43059296294576</v>
+        <v>-0.430592962945761</v>
       </c>
       <c r="C141" t="n">
-        <v>-6.40573397758987</v>
+        <v>-0.405733977589867</v>
       </c>
       <c r="D141" t="n">
-        <v>-6.38236632295615</v>
+        <v>-0.382366322956154</v>
       </c>
       <c r="E141" t="n">
         <v>0.0100422896872455</v>
@@ -4004,19 +4010,19 @@
         <v>146</v>
       </c>
       <c r="B142" t="n">
-        <v>-11.3147477943653</v>
+        <v>-6.43059296294576</v>
       </c>
       <c r="C142" t="n">
-        <v>-11.3367998908763</v>
+        <v>-6.40573397758987</v>
       </c>
       <c r="D142" t="n">
-        <v>-11.0125318054326</v>
+        <v>-6.38236632295615</v>
       </c>
       <c r="E142" t="n">
-        <v>0.224143841170913</v>
+        <v>0.0100422896872455</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0240973759224841</v>
+        <v>0.00510061707311408</v>
       </c>
     </row>
     <row r="143">
@@ -4024,13 +4030,13 @@
         <v>147</v>
       </c>
       <c r="B143" t="n">
-        <v>-5.31474779436532</v>
+        <v>-11.3147477943653</v>
       </c>
       <c r="C143" t="n">
-        <v>-5.33679989087631</v>
+        <v>-11.3367998908763</v>
       </c>
       <c r="D143" t="n">
-        <v>-5.01253180543255</v>
+        <v>-11.0125318054326</v>
       </c>
       <c r="E143" t="n">
         <v>0.224143841170913</v>
@@ -4044,13 +4050,13 @@
         <v>148</v>
       </c>
       <c r="B144" t="n">
-        <v>-2.31474779436532</v>
+        <v>-5.31474779436532</v>
       </c>
       <c r="C144" t="n">
-        <v>-2.3367998908763</v>
+        <v>-5.33679989087631</v>
       </c>
       <c r="D144" t="n">
-        <v>-2.01253180543255</v>
+        <v>-5.01253180543255</v>
       </c>
       <c r="E144" t="n">
         <v>0.224143841170913</v>
@@ -4064,13 +4070,13 @@
         <v>149</v>
       </c>
       <c r="B145" t="n">
-        <v>-8.31474779436532</v>
+        <v>-2.31474779436532</v>
       </c>
       <c r="C145" t="n">
-        <v>-8.3367998908763</v>
+        <v>-2.3367998908763</v>
       </c>
       <c r="D145" t="n">
-        <v>-8.01253180543255</v>
+        <v>-2.01253180543255</v>
       </c>
       <c r="E145" t="n">
         <v>0.224143841170913</v>
@@ -4084,19 +4090,19 @@
         <v>150</v>
       </c>
       <c r="B146" t="n">
-        <v>-10.3587555581758</v>
+        <v>-8.31474779436532</v>
       </c>
       <c r="C146" t="n">
-        <v>-10.3262763463401</v>
+        <v>-8.3367998908763</v>
       </c>
       <c r="D146" t="n">
-        <v>-10.4066985203407</v>
+        <v>-8.01253180543255</v>
       </c>
       <c r="E146" t="n">
-        <v>0.025212765909473</v>
+        <v>0.224143841170913</v>
       </c>
       <c r="F146" t="n">
-        <v>0.00808195807942596</v>
+        <v>0.0240973759224841</v>
       </c>
     </row>
     <row r="147">
@@ -4104,13 +4110,13 @@
         <v>151</v>
       </c>
       <c r="B147" t="n">
-        <v>-4.35875555817576</v>
+        <v>-10.3587555581758</v>
       </c>
       <c r="C147" t="n">
-        <v>-4.32627634634009</v>
+        <v>-10.3262763463401</v>
       </c>
       <c r="D147" t="n">
-        <v>-4.40669852034068</v>
+        <v>-10.4066985203407</v>
       </c>
       <c r="E147" t="n">
         <v>0.025212765909473</v>
@@ -4124,13 +4130,13 @@
         <v>152</v>
       </c>
       <c r="B148" t="n">
-        <v>-1.35875555817576</v>
+        <v>-4.35875555817576</v>
       </c>
       <c r="C148" t="n">
-        <v>-1.32627634634009</v>
+        <v>-4.32627634634009</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.40669852034068</v>
+        <v>-4.40669852034068</v>
       </c>
       <c r="E148" t="n">
         <v>0.025212765909473</v>
@@ -4144,13 +4150,13 @@
         <v>153</v>
       </c>
       <c r="B149" t="n">
-        <v>-7.35875555817576</v>
+        <v>-1.35875555817576</v>
       </c>
       <c r="C149" t="n">
-        <v>-7.32627634634009</v>
+        <v>-1.32627634634009</v>
       </c>
       <c r="D149" t="n">
-        <v>-7.40669852034068</v>
+        <v>-1.40669852034068</v>
       </c>
       <c r="E149" t="n">
         <v>0.025212765909473</v>
@@ -4164,19 +4170,19 @@
         <v>154</v>
       </c>
       <c r="B150" t="n">
-        <v>-11.1854661856085</v>
+        <v>-7.35875555817576</v>
       </c>
       <c r="C150" t="n">
-        <v>-11.2210878249715</v>
+        <v>-7.32627634634009</v>
       </c>
       <c r="D150" t="n">
-        <v>-11.3122688673918</v>
+        <v>-7.40669852034068</v>
       </c>
       <c r="E150" t="n">
-        <v>0.103418441379416</v>
+        <v>0.025212765909473</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0163683665422893</v>
+        <v>0.00808195807942596</v>
       </c>
     </row>
     <row r="151">
@@ -4184,13 +4190,13 @@
         <v>155</v>
       </c>
       <c r="B151" t="n">
-        <v>-5.18546618560848</v>
+        <v>-11.1854661856085</v>
       </c>
       <c r="C151" t="n">
-        <v>-5.22108782497146</v>
+        <v>-11.2210878249715</v>
       </c>
       <c r="D151" t="n">
-        <v>-5.31226886739177</v>
+        <v>-11.3122688673918</v>
       </c>
       <c r="E151" t="n">
         <v>0.103418441379416</v>
@@ -4204,13 +4210,13 @@
         <v>156</v>
       </c>
       <c r="B152" t="n">
-        <v>-2.18546618560848</v>
+        <v>-5.18546618560848</v>
       </c>
       <c r="C152" t="n">
-        <v>-2.22108782497146</v>
+        <v>-5.22108782497146</v>
       </c>
       <c r="D152" t="n">
-        <v>-2.31226886739177</v>
+        <v>-5.31226886739177</v>
       </c>
       <c r="E152" t="n">
         <v>0.103418441379416</v>
@@ -4224,13 +4230,13 @@
         <v>157</v>
       </c>
       <c r="B153" t="n">
-        <v>-8.18546618560848</v>
+        <v>-2.18546618560848</v>
       </c>
       <c r="C153" t="n">
-        <v>-8.22108782497146</v>
+        <v>-2.22108782497146</v>
       </c>
       <c r="D153" t="n">
-        <v>-8.31226886739177</v>
+        <v>-2.31226886739177</v>
       </c>
       <c r="E153" t="n">
         <v>0.103418441379416</v>
@@ -4244,19 +4250,19 @@
         <v>158</v>
       </c>
       <c r="B154" t="n">
-        <v>-12.7591658091723</v>
+        <v>-8.18546618560848</v>
       </c>
       <c r="C154" t="n">
-        <v>-12.7489697937181</v>
+        <v>-8.22108782497146</v>
       </c>
       <c r="D154" t="n">
-        <v>-13.4665559096128</v>
+        <v>-8.31226886739177</v>
       </c>
       <c r="E154" t="n">
-        <v>0.160802814870411</v>
+        <v>0.103418441379416</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0204104777820417</v>
+        <v>0.0163683665422893</v>
       </c>
     </row>
     <row r="155">
@@ -4264,13 +4270,13 @@
         <v>159</v>
       </c>
       <c r="B155" t="n">
-        <v>-6.75916580917232</v>
+        <v>-12.7591658091723</v>
       </c>
       <c r="C155" t="n">
-        <v>-6.74896979371813</v>
+        <v>-12.7489697937181</v>
       </c>
       <c r="D155" t="n">
-        <v>-7.46655590961282</v>
+        <v>-13.4665559096128</v>
       </c>
       <c r="E155" t="n">
         <v>0.160802814870411</v>
@@ -4284,13 +4290,13 @@
         <v>160</v>
       </c>
       <c r="B156" t="n">
-        <v>-3.75916580917232</v>
+        <v>-6.75916580917232</v>
       </c>
       <c r="C156" t="n">
-        <v>-3.74896979371813</v>
+        <v>-6.74896979371813</v>
       </c>
       <c r="D156" t="n">
-        <v>-4.46655590961282</v>
+        <v>-7.46655590961282</v>
       </c>
       <c r="E156" t="n">
         <v>0.160802814870411</v>
@@ -4304,13 +4310,13 @@
         <v>161</v>
       </c>
       <c r="B157" t="n">
-        <v>-9.75916580917232</v>
+        <v>-3.75916580917232</v>
       </c>
       <c r="C157" t="n">
-        <v>-9.74896979371813</v>
+        <v>-3.74896979371813</v>
       </c>
       <c r="D157" t="n">
-        <v>-10.4665559096128</v>
+        <v>-4.46655590961282</v>
       </c>
       <c r="E157" t="n">
         <v>0.160802814870411</v>
@@ -4324,19 +4330,19 @@
         <v>162</v>
       </c>
       <c r="B158" t="n">
-        <v>-12.5786572434634</v>
+        <v>-9.75916580917232</v>
       </c>
       <c r="C158" t="n">
-        <v>-12.5836099129991</v>
+        <v>-9.74896979371813</v>
       </c>
       <c r="D158" t="n">
-        <v>-12.8749219750061</v>
+        <v>-10.4665559096128</v>
       </c>
       <c r="E158" t="n">
-        <v>0.113267568618417</v>
+        <v>0.160802814870411</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0171300699630476</v>
+        <v>0.0204104777820417</v>
       </c>
     </row>
     <row r="159">
@@ -4344,13 +4350,13 @@
         <v>163</v>
       </c>
       <c r="B159" t="n">
-        <v>-6.57865724346345</v>
+        <v>-12.5786572434634</v>
       </c>
       <c r="C159" t="n">
-        <v>-6.5836099129991</v>
+        <v>-12.5836099129991</v>
       </c>
       <c r="D159" t="n">
-        <v>-6.87492197500612</v>
+        <v>-12.8749219750061</v>
       </c>
       <c r="E159" t="n">
         <v>0.113267568618417</v>
@@ -4364,13 +4370,13 @@
         <v>164</v>
       </c>
       <c r="B160" t="n">
-        <v>-3.57865724346345</v>
+        <v>-6.57865724346345</v>
       </c>
       <c r="C160" t="n">
-        <v>-3.5836099129991</v>
+        <v>-6.5836099129991</v>
       </c>
       <c r="D160" t="n">
-        <v>-3.87492197500612</v>
+        <v>-6.87492197500612</v>
       </c>
       <c r="E160" t="n">
         <v>0.113267568618417</v>
@@ -4384,13 +4390,13 @@
         <v>165</v>
       </c>
       <c r="B161" t="n">
-        <v>-9.57865724346345</v>
+        <v>-3.57865724346345</v>
       </c>
       <c r="C161" t="n">
-        <v>-9.5836099129991</v>
+        <v>-3.5836099129991</v>
       </c>
       <c r="D161" t="n">
-        <v>-9.87492197500612</v>
+        <v>-3.87492197500612</v>
       </c>
       <c r="E161" t="n">
         <v>0.113267568618417</v>
@@ -4404,19 +4410,19 @@
         <v>166</v>
       </c>
       <c r="B162" t="n">
-        <v>-5.47116687504781</v>
+        <v>-9.57865724346345</v>
       </c>
       <c r="C162" t="n">
-        <v>-5.32643653278655</v>
+        <v>-9.5836099129991</v>
       </c>
       <c r="D162" t="n">
-        <v>-5.49285172058057</v>
+        <v>-9.87492197500612</v>
       </c>
       <c r="E162" t="n">
-        <v>0.510227324658742</v>
+        <v>0.113267568618417</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0363570137291615</v>
+        <v>0.0171300699630476</v>
       </c>
     </row>
     <row r="163">
@@ -4424,13 +4430,13 @@
         <v>167</v>
       </c>
       <c r="B163" t="n">
-        <v>3.52883312495219</v>
+        <v>-5.47116687504781</v>
       </c>
       <c r="C163" t="n">
-        <v>3.67356346721345</v>
+        <v>-5.32643653278655</v>
       </c>
       <c r="D163" t="n">
-        <v>3.50714827941943</v>
+        <v>-5.49285172058057</v>
       </c>
       <c r="E163" t="n">
         <v>0.510227324658742</v>
@@ -4444,13 +4450,13 @@
         <v>168</v>
       </c>
       <c r="B164" t="n">
-        <v>0.528833124952191</v>
+        <v>3.52883312495219</v>
       </c>
       <c r="C164" t="n">
-        <v>0.673563467213447</v>
+        <v>3.67356346721345</v>
       </c>
       <c r="D164" t="n">
-        <v>0.507148279419425</v>
+        <v>3.50714827941943</v>
       </c>
       <c r="E164" t="n">
         <v>0.510227324658742</v>
@@ -4464,19 +4470,19 @@
         <v>169</v>
       </c>
       <c r="B165" t="n">
-        <v>-4.7317683572035</v>
+        <v>0.528833124952191</v>
       </c>
       <c r="C165" t="n">
-        <v>-4.59133244737573</v>
+        <v>0.673563467213447</v>
       </c>
       <c r="D165" t="n">
-        <v>-4.34942949380702</v>
+        <v>0.507148279419425</v>
       </c>
       <c r="E165" t="n">
-        <v>0.222326271322696</v>
+        <v>0.510227324658742</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0239994749145223</v>
+        <v>0.0363570137291615</v>
       </c>
     </row>
     <row r="166">
@@ -4484,13 +4490,13 @@
         <v>170</v>
       </c>
       <c r="B166" t="n">
-        <v>4.2682316427965</v>
+        <v>-4.7317683572035</v>
       </c>
       <c r="C166" t="n">
-        <v>4.40866755262427</v>
+        <v>-4.59133244737573</v>
       </c>
       <c r="D166" t="n">
-        <v>4.65057050619298</v>
+        <v>-4.34942949380702</v>
       </c>
       <c r="E166" t="n">
         <v>0.222326271322696</v>
@@ -4504,13 +4510,13 @@
         <v>171</v>
       </c>
       <c r="B167" t="n">
-        <v>1.2682316427965</v>
+        <v>4.2682316427965</v>
       </c>
       <c r="C167" t="n">
-        <v>1.40866755262427</v>
+        <v>4.40866755262427</v>
       </c>
       <c r="D167" t="n">
-        <v>1.65057050619298</v>
+        <v>4.65057050619298</v>
       </c>
       <c r="E167" t="n">
         <v>0.222326271322696</v>
@@ -4524,19 +4530,19 @@
         <v>172</v>
       </c>
       <c r="B168" t="n">
-        <v>-5.12905010839342</v>
+        <v>1.2682316427965</v>
       </c>
       <c r="C168" t="n">
-        <v>-5.08857251093765</v>
+        <v>1.40866755262427</v>
       </c>
       <c r="D168" t="n">
-        <v>-5.33814810751036</v>
+        <v>1.65057050619298</v>
       </c>
       <c r="E168" t="n">
-        <v>0.277428634864824</v>
+        <v>0.222326271322696</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0268090849028563</v>
+        <v>0.0239994749145223</v>
       </c>
     </row>
     <row r="169">
@@ -4544,13 +4550,13 @@
         <v>173</v>
       </c>
       <c r="B169" t="n">
-        <v>3.87094989160658</v>
+        <v>-5.12905010839342</v>
       </c>
       <c r="C169" t="n">
-        <v>3.91142748906236</v>
+        <v>-5.08857251093765</v>
       </c>
       <c r="D169" t="n">
-        <v>3.66185189248964</v>
+        <v>-5.33814810751036</v>
       </c>
       <c r="E169" t="n">
         <v>0.277428634864824</v>
@@ -4564,13 +4570,13 @@
         <v>174</v>
       </c>
       <c r="B170" t="n">
-        <v>0.870949891606577</v>
+        <v>3.87094989160658</v>
       </c>
       <c r="C170" t="n">
-        <v>0.911427489062355</v>
+        <v>3.91142748906236</v>
       </c>
       <c r="D170" t="n">
-        <v>0.661851892489637</v>
+        <v>3.66185189248964</v>
       </c>
       <c r="E170" t="n">
         <v>0.277428634864824</v>
@@ -4584,19 +4590,19 @@
         <v>175</v>
       </c>
       <c r="B171" t="n">
-        <v>-2.97800662468358</v>
+        <v>0.870949891606577</v>
       </c>
       <c r="C171" t="n">
-        <v>-2.89980186238729</v>
+        <v>0.911427489062355</v>
       </c>
       <c r="D171" t="n">
-        <v>-2.80410034759077</v>
+        <v>0.661851892489637</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0636457667404803</v>
+        <v>0.277428634864824</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0128407712409894</v>
+        <v>0.0268090849028563</v>
       </c>
     </row>
     <row r="172">
@@ -4604,13 +4610,13 @@
         <v>176</v>
       </c>
       <c r="B172" t="n">
-        <v>6.02199337531642</v>
+        <v>-2.97800662468358</v>
       </c>
       <c r="C172" t="n">
-        <v>6.10019813761271</v>
+        <v>-2.89980186238729</v>
       </c>
       <c r="D172" t="n">
-        <v>6.19589965240923</v>
+        <v>-2.80410034759077</v>
       </c>
       <c r="E172" t="n">
         <v>0.0636457667404803</v>
@@ -4624,13 +4630,13 @@
         <v>177</v>
       </c>
       <c r="B173" t="n">
-        <v>3.02199337531642</v>
+        <v>6.02199337531642</v>
       </c>
       <c r="C173" t="n">
-        <v>3.10019813761271</v>
+        <v>6.10019813761271</v>
       </c>
       <c r="D173" t="n">
-        <v>3.19589965240923</v>
+        <v>6.19589965240923</v>
       </c>
       <c r="E173" t="n">
         <v>0.0636457667404803</v>
@@ -4644,19 +4650,19 @@
         <v>178</v>
       </c>
       <c r="B174" t="n">
-        <v>-3.65101105730638</v>
+        <v>3.02199337531642</v>
       </c>
       <c r="C174" t="n">
-        <v>-3.63171411078192</v>
+        <v>3.10019813761271</v>
       </c>
       <c r="D174" t="n">
-        <v>-4.09691001300806</v>
+        <v>3.19589965240923</v>
       </c>
       <c r="E174" t="n">
-        <v>0.168805445928065</v>
+        <v>0.0636457667404803</v>
       </c>
       <c r="F174" t="n">
-        <v>0.02091219280955</v>
+        <v>0.0128407712409894</v>
       </c>
     </row>
     <row r="175">
@@ -4664,13 +4670,13 @@
         <v>179</v>
       </c>
       <c r="B175" t="n">
-        <v>5.34898894269362</v>
+        <v>-3.65101105730638</v>
       </c>
       <c r="C175" t="n">
-        <v>5.36828588921808</v>
+        <v>-3.63171411078192</v>
       </c>
       <c r="D175" t="n">
-        <v>4.90308998699194</v>
+        <v>-4.09691001300806</v>
       </c>
       <c r="E175" t="n">
         <v>0.168805445928065</v>
@@ -4684,13 +4690,13 @@
         <v>180</v>
       </c>
       <c r="B176" t="n">
-        <v>2.34898894269362</v>
+        <v>5.34898894269362</v>
       </c>
       <c r="C176" t="n">
-        <v>2.36828588921808</v>
+        <v>5.36828588921808</v>
       </c>
       <c r="D176" t="n">
-        <v>1.90308998699194</v>
+        <v>4.90308998699194</v>
       </c>
       <c r="E176" t="n">
         <v>0.168805445928065</v>
@@ -4704,19 +4710,19 @@
         <v>181</v>
       </c>
       <c r="B177" t="n">
-        <v>-8.03306989879472</v>
+        <v>2.34898894269362</v>
       </c>
       <c r="C177" t="n">
-        <v>-8.04674547598485</v>
+        <v>2.36828588921808</v>
       </c>
       <c r="D177" t="n">
-        <v>-9.82681373158773</v>
+        <v>1.90308998699194</v>
       </c>
       <c r="E177" t="n">
-        <v>0.398079352298723</v>
+        <v>0.168805445928065</v>
       </c>
       <c r="F177" t="n">
-        <v>0.03211376120614</v>
+        <v>0.02091219280955</v>
       </c>
     </row>
     <row r="178">
@@ -4724,13 +4730,13 @@
         <v>182</v>
       </c>
       <c r="B178" t="n">
-        <v>0.966930101205278</v>
+        <v>-8.03306989879472</v>
       </c>
       <c r="C178" t="n">
-        <v>0.953254524015154</v>
+        <v>-8.04674547598485</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.826813731587726</v>
+        <v>-9.82681373158773</v>
       </c>
       <c r="E178" t="n">
         <v>0.398079352298723</v>
@@ -4744,13 +4750,13 @@
         <v>183</v>
       </c>
       <c r="B179" t="n">
-        <v>-2.03306989879472</v>
+        <v>0.966930101205278</v>
       </c>
       <c r="C179" t="n">
-        <v>-2.04674547598485</v>
+        <v>0.953254524015154</v>
       </c>
       <c r="D179" t="n">
-        <v>-3.82681373158773</v>
+        <v>-0.826813731587726</v>
       </c>
       <c r="E179" t="n">
         <v>0.398079352298723</v>
@@ -4764,19 +4770,19 @@
         <v>184</v>
       </c>
       <c r="B180" t="n">
-        <v>-2.61618579484238</v>
+        <v>-2.03306989879472</v>
       </c>
       <c r="C180" t="n">
-        <v>-2.548904695166</v>
+        <v>-2.04674547598485</v>
       </c>
       <c r="D180" t="n">
-        <v>-2.7476324855401</v>
+        <v>-3.82681373158773</v>
       </c>
       <c r="E180" t="n">
-        <v>0.0551253767470059</v>
+        <v>0.398079352298723</v>
       </c>
       <c r="F180" t="n">
-        <v>0.0119503914939021</v>
+        <v>0.03211376120614</v>
       </c>
     </row>
     <row r="181">
@@ -4784,13 +4790,13 @@
         <v>185</v>
       </c>
       <c r="B181" t="n">
-        <v>6.38381420515762</v>
+        <v>-2.61618579484238</v>
       </c>
       <c r="C181" t="n">
-        <v>6.451095304834</v>
+        <v>-2.548904695166</v>
       </c>
       <c r="D181" t="n">
-        <v>6.2523675144599</v>
+        <v>-2.7476324855401</v>
       </c>
       <c r="E181" t="n">
         <v>0.0551253767470059</v>
@@ -4804,13 +4810,13 @@
         <v>186</v>
       </c>
       <c r="B182" t="n">
-        <v>3.38381420515762</v>
+        <v>6.38381420515762</v>
       </c>
       <c r="C182" t="n">
-        <v>3.451095304834</v>
+        <v>6.451095304834</v>
       </c>
       <c r="D182" t="n">
-        <v>3.2523675144599</v>
+        <v>6.2523675144599</v>
       </c>
       <c r="E182" t="n">
         <v>0.0551253767470059</v>
@@ -4824,19 +4830,19 @@
         <v>187</v>
       </c>
       <c r="B183" t="n">
-        <v>-3.8624318393549</v>
+        <v>3.38381420515762</v>
       </c>
       <c r="C183" t="n">
-        <v>-3.85787816076663</v>
+        <v>3.451095304834</v>
       </c>
       <c r="D183" t="n">
-        <v>-4.04575749056067</v>
+        <v>3.2523675144599</v>
       </c>
       <c r="E183" t="n">
-        <v>0.110421154906443</v>
+        <v>0.0551253767470059</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0169134611523309</v>
+        <v>0.0119503914939021</v>
       </c>
     </row>
     <row r="184">
@@ -4844,13 +4850,13 @@
         <v>188</v>
       </c>
       <c r="B184" t="n">
-        <v>5.1375681606451</v>
+        <v>-3.8624318393549</v>
       </c>
       <c r="C184" t="n">
-        <v>5.14212183923337</v>
+        <v>-3.85787816076663</v>
       </c>
       <c r="D184" t="n">
-        <v>4.95424250943933</v>
+        <v>-4.04575749056067</v>
       </c>
       <c r="E184" t="n">
         <v>0.110421154906443</v>
@@ -4864,13 +4870,13 @@
         <v>189</v>
       </c>
       <c r="B185" t="n">
-        <v>2.1375681606451</v>
+        <v>5.1375681606451</v>
       </c>
       <c r="C185" t="n">
-        <v>2.14212183923337</v>
+        <v>5.14212183923337</v>
       </c>
       <c r="D185" t="n">
-        <v>1.95424250943932</v>
+        <v>4.95424250943933</v>
       </c>
       <c r="E185" t="n">
         <v>0.110421154906443</v>
@@ -4884,19 +4890,19 @@
         <v>190</v>
       </c>
       <c r="B186" t="n">
-        <v>-7.73570776825048</v>
+        <v>2.1375681606451</v>
       </c>
       <c r="C186" t="n">
-        <v>-7.69289664098812</v>
+        <v>2.14212183923337</v>
       </c>
       <c r="D186" t="n">
-        <v>-7.92346057232192</v>
+        <v>1.95424250943932</v>
       </c>
       <c r="E186" t="n">
-        <v>0.106046238137458</v>
+        <v>0.110421154906443</v>
       </c>
       <c r="F186" t="n">
-        <v>0.0165750169497532</v>
+        <v>0.0169134611523309</v>
       </c>
     </row>
     <row r="187">
@@ -4904,19 +4910,19 @@
         <v>191</v>
       </c>
       <c r="B187" t="n">
-        <v>1.26429223174952</v>
+        <v>2.40243371083576</v>
       </c>
       <c r="C187" t="n">
-        <v>1.30710335901188</v>
+        <v>2.41000071254346</v>
       </c>
       <c r="D187" t="n">
-        <v>1.07653942767808</v>
+        <v>2.41193941752404</v>
       </c>
       <c r="E187" t="n">
-        <v>0.106046238137458</v>
+        <v>0.000593447964128563</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0165750169497532</v>
+        <v>0.00123993143313745</v>
       </c>
     </row>
     <row r="188">
@@ -4924,13 +4930,13 @@
         <v>192</v>
       </c>
       <c r="B188" t="n">
-        <v>-1.73570776825048</v>
+        <v>-7.73570776825048</v>
       </c>
       <c r="C188" t="n">
-        <v>-1.69289664098812</v>
+        <v>-7.69289664098812</v>
       </c>
       <c r="D188" t="n">
-        <v>-1.92346057232192</v>
+        <v>-7.92346057232192</v>
       </c>
       <c r="E188" t="n">
         <v>0.106046238137458</v>
@@ -4944,19 +4950,19 @@
         <v>193</v>
       </c>
       <c r="B189" t="n">
-        <v>-20.7682049211339</v>
+        <v>1.26429223174952</v>
       </c>
       <c r="C189" t="n">
-        <v>-20.8011932449567</v>
+        <v>1.30710335901188</v>
       </c>
       <c r="D189" t="n">
-        <v>-19.7525138877493</v>
+        <v>1.07653942767808</v>
       </c>
       <c r="E189" t="n">
-        <v>0.601927056426142</v>
+        <v>0.106046238137458</v>
       </c>
       <c r="F189" t="n">
-        <v>0.0394891949682278</v>
+        <v>0.0165750169497532</v>
       </c>
     </row>
     <row r="190">
@@ -4964,19 +4970,19 @@
         <v>194</v>
       </c>
       <c r="B190" t="n">
-        <v>-11.7682049211339</v>
+        <v>-1.73570776825048</v>
       </c>
       <c r="C190" t="n">
-        <v>-11.8011932449567</v>
+        <v>-1.69289664098812</v>
       </c>
       <c r="D190" t="n">
-        <v>-10.7525138877493</v>
+        <v>-1.92346057232192</v>
       </c>
       <c r="E190" t="n">
-        <v>0.601927056426142</v>
+        <v>0.106046238137458</v>
       </c>
       <c r="F190" t="n">
-        <v>0.0394891949682278</v>
+        <v>0.0165750169497532</v>
       </c>
     </row>
     <row r="191">
@@ -4984,13 +4990,13 @@
         <v>195</v>
       </c>
       <c r="B191" t="n">
-        <v>-14.7682049211339</v>
+        <v>-20.7682049211339</v>
       </c>
       <c r="C191" t="n">
-        <v>-14.8011932449567</v>
+        <v>-20.8011932449567</v>
       </c>
       <c r="D191" t="n">
-        <v>-13.7525138877493</v>
+        <v>-19.7525138877493</v>
       </c>
       <c r="E191" t="n">
         <v>0.601927056426142</v>
@@ -5004,19 +5010,19 @@
         <v>196</v>
       </c>
       <c r="B192" t="n">
-        <v>-3.90674347613252</v>
+        <v>-11.7682049211339</v>
       </c>
       <c r="C192" t="n">
-        <v>-3.90782402744313</v>
+        <v>-11.8011932449567</v>
       </c>
       <c r="D192" t="n">
-        <v>-3.2718381944557</v>
+        <v>-10.7525138877493</v>
       </c>
       <c r="E192" t="n">
-        <v>0.187490333801313</v>
+        <v>0.601927056426142</v>
       </c>
       <c r="F192" t="n">
-        <v>0.022039198110895</v>
+        <v>0.0394891949682278</v>
       </c>
     </row>
     <row r="193">
@@ -5024,19 +5030,19 @@
         <v>197</v>
       </c>
       <c r="B193" t="n">
-        <v>5.09325652386748</v>
+        <v>-14.7682049211339</v>
       </c>
       <c r="C193" t="n">
-        <v>5.09217597255687</v>
+        <v>-14.8011932449567</v>
       </c>
       <c r="D193" t="n">
-        <v>5.7281618055443</v>
+        <v>-13.7525138877493</v>
       </c>
       <c r="E193" t="n">
-        <v>0.187490333801313</v>
+        <v>0.601927056426142</v>
       </c>
       <c r="F193" t="n">
-        <v>0.022039198110895</v>
+        <v>0.0394891949682278</v>
       </c>
     </row>
     <row r="194">
@@ -5044,13 +5050,13 @@
         <v>198</v>
       </c>
       <c r="B194" t="n">
-        <v>2.09325652386748</v>
+        <v>-3.90674347613252</v>
       </c>
       <c r="C194" t="n">
-        <v>2.09217597255687</v>
+        <v>-3.90782402744313</v>
       </c>
       <c r="D194" t="n">
-        <v>2.7281618055443</v>
+        <v>-3.2718381944557</v>
       </c>
       <c r="E194" t="n">
         <v>0.187490333801313</v>
@@ -5064,19 +5070,19 @@
         <v>199</v>
       </c>
       <c r="B195" t="n">
-        <v>-2.66080843995655</v>
+        <v>5.09325652386748</v>
       </c>
       <c r="C195" t="n">
-        <v>-2.58714205175729</v>
+        <v>5.09217597255687</v>
       </c>
       <c r="D195" t="n">
-        <v>-2.42588367715264</v>
+        <v>5.7281618055443</v>
       </c>
       <c r="E195" t="n">
-        <v>0.0619243957654582</v>
+        <v>0.187490333801313</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0126659344608061</v>
+        <v>0.022039198110895</v>
       </c>
     </row>
     <row r="196">
@@ -5084,19 +5090,19 @@
         <v>200</v>
       </c>
       <c r="B196" t="n">
-        <v>6.33919156004345</v>
+        <v>2.09325652386748</v>
       </c>
       <c r="C196" t="n">
-        <v>6.41285794824271</v>
+        <v>2.09217597255687</v>
       </c>
       <c r="D196" t="n">
-        <v>6.57411632284736</v>
+        <v>2.7281618055443</v>
       </c>
       <c r="E196" t="n">
-        <v>0.0619243957654582</v>
+        <v>0.187490333801313</v>
       </c>
       <c r="F196" t="n">
-        <v>0.0126659344608061</v>
+        <v>0.022039198110895</v>
       </c>
     </row>
     <row r="197">
@@ -5104,13 +5110,13 @@
         <v>201</v>
       </c>
       <c r="B197" t="n">
-        <v>3.33919156004345</v>
+        <v>-2.66080843995655</v>
       </c>
       <c r="C197" t="n">
-        <v>3.41285794824271</v>
+        <v>-2.58714205175729</v>
       </c>
       <c r="D197" t="n">
-        <v>3.57411632284736</v>
+        <v>-2.42588367715264</v>
       </c>
       <c r="E197" t="n">
         <v>0.0619243957654582</v>
@@ -5124,19 +5130,19 @@
         <v>202</v>
       </c>
       <c r="B198" t="n">
-        <v>-20.1188170925329</v>
+        <v>6.33919156004345</v>
       </c>
       <c r="C198" t="n">
-        <v>-20.1167325309577</v>
+        <v>6.41285794824271</v>
       </c>
       <c r="D198" t="n">
-        <v>-19.5065569081015</v>
+        <v>6.57411632284736</v>
       </c>
       <c r="E198" t="n">
-        <v>0.166143193931006</v>
+        <v>0.0619243957654582</v>
       </c>
       <c r="F198" t="n">
-        <v>0.020746633032969</v>
+        <v>0.0126659344608061</v>
       </c>
     </row>
     <row r="199">
@@ -5144,19 +5150,19 @@
         <v>203</v>
       </c>
       <c r="B199" t="n">
-        <v>-11.1188170925328</v>
+        <v>3.33919156004345</v>
       </c>
       <c r="C199" t="n">
-        <v>-11.1167325309577</v>
+        <v>3.41285794824271</v>
       </c>
       <c r="D199" t="n">
-        <v>-10.5065569081015</v>
+        <v>3.57411632284736</v>
       </c>
       <c r="E199" t="n">
-        <v>0.166143193931006</v>
+        <v>0.0619243957654582</v>
       </c>
       <c r="F199" t="n">
-        <v>0.020746633032969</v>
+        <v>0.0126659344608061</v>
       </c>
     </row>
     <row r="200">
@@ -5164,13 +5170,13 @@
         <v>204</v>
       </c>
       <c r="B200" t="n">
-        <v>-14.1188170925328</v>
+        <v>-20.1188170925329</v>
       </c>
       <c r="C200" t="n">
-        <v>-14.1167325309577</v>
+        <v>-20.1167325309577</v>
       </c>
       <c r="D200" t="n">
-        <v>-13.5065569081015</v>
+        <v>-19.5065569081015</v>
       </c>
       <c r="E200" t="n">
         <v>0.166143193931006</v>
@@ -5184,19 +5190,19 @@
         <v>205</v>
       </c>
       <c r="B201" t="n">
-        <v>-4.39006948872305</v>
+        <v>-11.1188170925328</v>
       </c>
       <c r="C201" t="n">
-        <v>-4.41060933654004</v>
+        <v>-11.1167325309577</v>
       </c>
       <c r="D201" t="n">
-        <v>-4.50445566245355</v>
+        <v>-10.5065569081015</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0538188903134248</v>
+        <v>0.166143193931006</v>
       </c>
       <c r="F201" t="n">
-        <v>0.0118079285642226</v>
+        <v>0.020746633032969</v>
       </c>
     </row>
     <row r="202">
@@ -5204,19 +5210,19 @@
         <v>206</v>
       </c>
       <c r="B202" t="n">
-        <v>4.60993051127695</v>
+        <v>-14.1188170925328</v>
       </c>
       <c r="C202" t="n">
-        <v>4.58939066345996</v>
+        <v>-14.1167325309577</v>
       </c>
       <c r="D202" t="n">
-        <v>4.49554433754645</v>
+        <v>-13.5065569081015</v>
       </c>
       <c r="E202" t="n">
-        <v>0.0538188903134248</v>
+        <v>0.166143193931006</v>
       </c>
       <c r="F202" t="n">
-        <v>0.0118079285642226</v>
+        <v>0.020746633032969</v>
       </c>
     </row>
     <row r="203">
@@ -5224,13 +5230,13 @@
         <v>207</v>
       </c>
       <c r="B203" t="n">
-        <v>1.60993051127695</v>
+        <v>-4.39006948872305</v>
       </c>
       <c r="C203" t="n">
-        <v>1.58939066345996</v>
+        <v>-4.41060933654004</v>
       </c>
       <c r="D203" t="n">
-        <v>1.49554433754645</v>
+        <v>-4.50445566245355</v>
       </c>
       <c r="E203" t="n">
         <v>0.0538188903134248</v>
@@ -5244,19 +5250,19 @@
         <v>208</v>
       </c>
       <c r="B204" t="n">
-        <v>-6.10947601277406</v>
+        <v>4.60993051127695</v>
       </c>
       <c r="C204" t="n">
-        <v>-5.99298665727373</v>
+        <v>4.58939066345996</v>
       </c>
       <c r="D204" t="n">
-        <v>-6.22866104335667</v>
+        <v>4.49554433754645</v>
       </c>
       <c r="E204" t="n">
-        <v>0.488514856018307</v>
+        <v>0.0538188903134248</v>
       </c>
       <c r="F204" t="n">
-        <v>0.0355750267539581</v>
+        <v>0.0118079285642226</v>
       </c>
     </row>
     <row r="205">
@@ -5264,19 +5270,19 @@
         <v>209</v>
       </c>
       <c r="B205" t="n">
-        <v>2.89052398722594</v>
+        <v>1.60993051127695</v>
       </c>
       <c r="C205" t="n">
-        <v>3.00701334272627</v>
+        <v>1.58939066345996</v>
       </c>
       <c r="D205" t="n">
-        <v>2.77133895664333</v>
+        <v>1.49554433754645</v>
       </c>
       <c r="E205" t="n">
-        <v>0.488514856018307</v>
+        <v>0.0538188903134248</v>
       </c>
       <c r="F205" t="n">
-        <v>0.0355750267539581</v>
+        <v>0.0118079285642226</v>
       </c>
     </row>
     <row r="206">
@@ -5284,13 +5290,13 @@
         <v>210</v>
       </c>
       <c r="B206" t="n">
-        <v>-0.109476012774064</v>
+        <v>-6.10947601277406</v>
       </c>
       <c r="C206" t="n">
-        <v>0.00701334272626688</v>
+        <v>-5.99298665727373</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.228661043356668</v>
+        <v>-6.22866104335667</v>
       </c>
       <c r="E206" t="n">
         <v>0.488514856018307</v>
@@ -5304,19 +5310,19 @@
         <v>211</v>
       </c>
       <c r="B207" t="n">
-        <v>-5.1450243336338</v>
+        <v>2.89052398722594</v>
       </c>
       <c r="C207" t="n">
-        <v>-5.01730582536857</v>
+        <v>3.00701334272627</v>
       </c>
       <c r="D207" t="n">
-        <v>-4.8618644610268</v>
+        <v>2.77133895664333</v>
       </c>
       <c r="E207" t="n">
-        <v>0.193593563969</v>
+        <v>0.488514856018307</v>
       </c>
       <c r="F207" t="n">
-        <v>0.0223950380774322</v>
+        <v>0.0355750267539581</v>
       </c>
     </row>
     <row r="208">
@@ -5324,19 +5330,19 @@
         <v>212</v>
       </c>
       <c r="B208" t="n">
-        <v>3.8549756663662</v>
+        <v>-0.109476012774064</v>
       </c>
       <c r="C208" t="n">
-        <v>3.98269417463143</v>
+        <v>0.00701334272626688</v>
       </c>
       <c r="D208" t="n">
-        <v>4.1381355389732</v>
+        <v>-0.228661043356668</v>
       </c>
       <c r="E208" t="n">
-        <v>0.193593563969</v>
+        <v>0.488514856018307</v>
       </c>
       <c r="F208" t="n">
-        <v>0.0223950380774322</v>
+        <v>0.0355750267539581</v>
       </c>
     </row>
     <row r="209">
@@ -5344,13 +5350,13 @@
         <v>213</v>
       </c>
       <c r="B209" t="n">
-        <v>0.854975666366198</v>
+        <v>-5.1450243336338</v>
       </c>
       <c r="C209" t="n">
-        <v>0.982694174631431</v>
+        <v>-5.01730582536857</v>
       </c>
       <c r="D209" t="n">
-        <v>1.1381355389732</v>
+        <v>-4.8618644610268</v>
       </c>
       <c r="E209" t="n">
         <v>0.193593563969</v>
@@ -5364,19 +5370,19 @@
         <v>214</v>
       </c>
       <c r="B210" t="n">
-        <v>-5.5457545264097</v>
+        <v>3.8549756663662</v>
       </c>
       <c r="C210" t="n">
-        <v>-5.55844020097594</v>
+        <v>3.98269417463143</v>
       </c>
       <c r="D210" t="n">
-        <v>-5.84642793285626</v>
+        <v>4.1381355389732</v>
       </c>
       <c r="E210" t="n">
-        <v>0.229476192036779</v>
+        <v>0.193593563969</v>
       </c>
       <c r="F210" t="n">
-        <v>0.0243823277566157</v>
+        <v>0.0223950380774322</v>
       </c>
     </row>
     <row r="211">
@@ -5384,19 +5390,19 @@
         <v>215</v>
       </c>
       <c r="B211" t="n">
-        <v>3.4542454735903</v>
+        <v>0.854975666366198</v>
       </c>
       <c r="C211" t="n">
-        <v>3.44155979902406</v>
+        <v>0.982694174631431</v>
       </c>
       <c r="D211" t="n">
-        <v>3.15357206714374</v>
+        <v>1.1381355389732</v>
       </c>
       <c r="E211" t="n">
-        <v>0.229476192036779</v>
+        <v>0.193593563969</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0243823277566157</v>
+        <v>0.0223950380774322</v>
       </c>
     </row>
     <row r="212">
@@ -5404,13 +5410,13 @@
         <v>216</v>
       </c>
       <c r="B212" t="n">
-        <v>0.454245473590296</v>
+        <v>-5.5457545264097</v>
       </c>
       <c r="C212" t="n">
-        <v>0.441559799024056</v>
+        <v>-5.55844020097594</v>
       </c>
       <c r="D212" t="n">
-        <v>0.153572067143742</v>
+        <v>-5.84642793285626</v>
       </c>
       <c r="E212" t="n">
         <v>0.229476192036779</v>
@@ -5424,19 +5430,19 @@
         <v>217</v>
       </c>
       <c r="B213" t="n">
-        <v>-3.39728011553017</v>
+        <v>3.4542454735903</v>
       </c>
       <c r="C213" t="n">
-        <v>-3.3292906521054</v>
+        <v>3.44155979902406</v>
       </c>
       <c r="D213" t="n">
-        <v>-3.26360349772336</v>
+        <v>3.15357206714374</v>
       </c>
       <c r="E213" t="n">
-        <v>0.0547684708105518</v>
+        <v>0.229476192036779</v>
       </c>
       <c r="F213" t="n">
-        <v>0.0119116426272429</v>
+        <v>0.0243823277566157</v>
       </c>
     </row>
     <row r="214">
@@ -5444,19 +5450,19 @@
         <v>218</v>
       </c>
       <c r="B214" t="n">
-        <v>5.60271988446983</v>
+        <v>0.454245473590296</v>
       </c>
       <c r="C214" t="n">
-        <v>5.6707093478946</v>
+        <v>0.441559799024056</v>
       </c>
       <c r="D214" t="n">
-        <v>5.73639650227664</v>
+        <v>0.153572067143742</v>
       </c>
       <c r="E214" t="n">
-        <v>0.0547684708105518</v>
+        <v>0.229476192036779</v>
       </c>
       <c r="F214" t="n">
-        <v>0.0119116426272429</v>
+        <v>0.0243823277566157</v>
       </c>
     </row>
     <row r="215">
@@ -5464,13 +5470,13 @@
         <v>219</v>
       </c>
       <c r="B215" t="n">
-        <v>2.60271988446983</v>
+        <v>-3.39728011553017</v>
       </c>
       <c r="C215" t="n">
-        <v>2.6707093478946</v>
+        <v>-3.3292906521054</v>
       </c>
       <c r="D215" t="n">
-        <v>2.73639650227664</v>
+        <v>-3.26360349772336</v>
       </c>
       <c r="E215" t="n">
         <v>0.0547684708105518</v>
@@ -5484,19 +5490,19 @@
         <v>220</v>
       </c>
       <c r="B216" t="n">
-        <v>-3.65525695144415</v>
+        <v>5.60271988446983</v>
       </c>
       <c r="C216" t="n">
-        <v>-3.68402965454308</v>
+        <v>5.6707093478946</v>
       </c>
       <c r="D216" t="n">
-        <v>-3.77469071827414</v>
+        <v>5.73639650227664</v>
       </c>
       <c r="E216" t="n">
-        <v>0.14866227749998</v>
+        <v>0.0547684708105518</v>
       </c>
       <c r="F216" t="n">
-        <v>0.0196248677431919</v>
+        <v>0.0119116426272429</v>
       </c>
     </row>
     <row r="217">
@@ -5504,19 +5510,19 @@
         <v>221</v>
       </c>
       <c r="B217" t="n">
-        <v>5.34474304855584</v>
+        <v>2.60271988446983</v>
       </c>
       <c r="C217" t="n">
-        <v>5.31597034545692</v>
+        <v>2.6707093478946</v>
       </c>
       <c r="D217" t="n">
-        <v>5.22530928172586</v>
+        <v>2.73639650227664</v>
       </c>
       <c r="E217" t="n">
-        <v>0.14866227749998</v>
+        <v>0.0547684708105518</v>
       </c>
       <c r="F217" t="n">
-        <v>0.0196248677431919</v>
+        <v>0.0119116426272429</v>
       </c>
     </row>
     <row r="218">
@@ -5524,13 +5530,13 @@
         <v>222</v>
       </c>
       <c r="B218" t="n">
-        <v>2.34474304855584</v>
+        <v>-3.65525695144415</v>
       </c>
       <c r="C218" t="n">
-        <v>2.31597034545692</v>
+        <v>-3.68402965454308</v>
       </c>
       <c r="D218" t="n">
-        <v>2.22530928172586</v>
+        <v>-3.77469071827414</v>
       </c>
       <c r="E218" t="n">
         <v>0.14866227749998</v>
@@ -5544,19 +5550,19 @@
         <v>223</v>
       </c>
       <c r="B219" t="n">
-        <v>-4.08795850644903</v>
+        <v>5.34474304855584</v>
       </c>
       <c r="C219" t="n">
-        <v>-4.10596108762881</v>
+        <v>5.31597034545692</v>
       </c>
       <c r="D219" t="n">
-        <v>-3.85698519974591</v>
+        <v>5.22530928172586</v>
       </c>
       <c r="E219" t="n">
-        <v>0.165569436768231</v>
+        <v>0.14866227749998</v>
       </c>
       <c r="F219" t="n">
-        <v>0.0207107789492461</v>
+        <v>0.0196248677431919</v>
       </c>
     </row>
     <row r="220">
@@ -5564,19 +5570,19 @@
         <v>224</v>
       </c>
       <c r="B220" t="n">
-        <v>4.91204149355097</v>
+        <v>2.34474304855584</v>
       </c>
       <c r="C220" t="n">
-        <v>4.89403891237119</v>
+        <v>2.31597034545692</v>
       </c>
       <c r="D220" t="n">
-        <v>5.14301480025409</v>
+        <v>2.22530928172586</v>
       </c>
       <c r="E220" t="n">
-        <v>0.165569436768231</v>
+        <v>0.14866227749998</v>
       </c>
       <c r="F220" t="n">
-        <v>0.0207107789492461</v>
+        <v>0.0196248677431919</v>
       </c>
     </row>
     <row r="221">
@@ -5584,13 +5590,13 @@
         <v>225</v>
       </c>
       <c r="B221" t="n">
-        <v>1.91204149355097</v>
+        <v>-4.08795850644903</v>
       </c>
       <c r="C221" t="n">
-        <v>1.89403891237119</v>
+        <v>-4.10596108762881</v>
       </c>
       <c r="D221" t="n">
-        <v>2.14301480025409</v>
+        <v>-3.85698519974591</v>
       </c>
       <c r="E221" t="n">
         <v>0.165569436768231</v>
@@ -5604,19 +5610,19 @@
         <v>226</v>
       </c>
       <c r="B222" t="n">
-        <v>-12.3137879156804</v>
+        <v>4.91204149355097</v>
       </c>
       <c r="C222" t="n">
-        <v>-12.3242296298785</v>
+        <v>4.89403891237119</v>
       </c>
       <c r="D222" t="n">
-        <v>-12.7759066307065</v>
+        <v>5.14301480025409</v>
       </c>
       <c r="E222" t="n">
-        <v>0.100743326516778</v>
+        <v>0.165569436768231</v>
       </c>
       <c r="F222" t="n">
-        <v>0.0161552800618765</v>
+        <v>0.0207107789492461</v>
       </c>
     </row>
     <row r="223">
@@ -5624,19 +5630,19 @@
         <v>227</v>
       </c>
       <c r="B223" t="n">
-        <v>-6.31378791568044</v>
+        <v>1.91204149355097</v>
       </c>
       <c r="C223" t="n">
-        <v>-6.32422962987851</v>
+        <v>1.89403891237119</v>
       </c>
       <c r="D223" t="n">
-        <v>-6.77590663070652</v>
+        <v>2.14301480025409</v>
       </c>
       <c r="E223" t="n">
-        <v>0.100743326516778</v>
+        <v>0.165569436768231</v>
       </c>
       <c r="F223" t="n">
-        <v>0.0161552800618765</v>
+        <v>0.0207107789492461</v>
       </c>
     </row>
     <row r="224">
@@ -5644,13 +5650,13 @@
         <v>228</v>
       </c>
       <c r="B224" t="n">
-        <v>-9.31378791568044</v>
+        <v>-12.3137879156804</v>
       </c>
       <c r="C224" t="n">
-        <v>-9.32422962987851</v>
+        <v>-12.3242296298785</v>
       </c>
       <c r="D224" t="n">
-        <v>-9.77590663070652</v>
+        <v>-12.7759066307065</v>
       </c>
       <c r="E224" t="n">
         <v>0.100743326516778</v>
@@ -5664,19 +5670,19 @@
         <v>229</v>
       </c>
       <c r="B225" t="n">
-        <v>-5.24105865023618</v>
+        <v>-6.31378791568044</v>
       </c>
       <c r="C225" t="n">
-        <v>-5.2300995592046</v>
+        <v>-6.32422962987851</v>
       </c>
       <c r="D225" t="n">
-        <v>-5.47443586370432</v>
+        <v>-6.77590663070652</v>
       </c>
       <c r="E225" t="n">
-        <v>0.126925019304733</v>
+        <v>0.100743326516778</v>
       </c>
       <c r="F225" t="n">
-        <v>0.0181334302749253</v>
+        <v>0.0161552800618765</v>
       </c>
     </row>
     <row r="226">
@@ -5684,19 +5690,19 @@
         <v>230</v>
       </c>
       <c r="B226" t="n">
-        <v>3.75894134976382</v>
+        <v>-9.31378791568044</v>
       </c>
       <c r="C226" t="n">
-        <v>3.7699004407954</v>
+        <v>-9.32422962987851</v>
       </c>
       <c r="D226" t="n">
-        <v>3.52556413629568</v>
+        <v>-9.77590663070652</v>
       </c>
       <c r="E226" t="n">
-        <v>0.126925019304733</v>
+        <v>0.100743326516778</v>
       </c>
       <c r="F226" t="n">
-        <v>0.0181334302749253</v>
+        <v>0.0161552800618765</v>
       </c>
     </row>
     <row r="227">
@@ -5704,13 +5710,13 @@
         <v>231</v>
       </c>
       <c r="B227" t="n">
-        <v>0.758941349763823</v>
+        <v>-5.24105865023618</v>
       </c>
       <c r="C227" t="n">
-        <v>0.769900440795398</v>
+        <v>-5.2300995592046</v>
       </c>
       <c r="D227" t="n">
-        <v>0.525564136295676</v>
+        <v>-5.47443586370432</v>
       </c>
       <c r="E227" t="n">
         <v>0.126925019304733</v>
@@ -5724,19 +5730,19 @@
         <v>232</v>
       </c>
       <c r="B228" t="n">
-        <v>-6.71936705589618</v>
+        <v>3.75894134976382</v>
       </c>
       <c r="C228" t="n">
-        <v>-6.75113637641012</v>
+        <v>3.7699004407954</v>
       </c>
       <c r="D228" t="n">
-        <v>-6.59308025306971</v>
+        <v>3.52556413629568</v>
       </c>
       <c r="E228" t="n">
-        <v>0.195766615648459</v>
+        <v>0.126925019304733</v>
       </c>
       <c r="F228" t="n">
-        <v>0.0225203773958831</v>
+        <v>0.0181334302749253</v>
       </c>
     </row>
     <row r="229">
@@ -5744,19 +5750,19 @@
         <v>233</v>
       </c>
       <c r="B229" t="n">
-        <v>2.28063294410382</v>
+        <v>0.758941349763823</v>
       </c>
       <c r="C229" t="n">
-        <v>2.24886362358988</v>
+        <v>0.769900440795398</v>
       </c>
       <c r="D229" t="n">
-        <v>2.40691974693029</v>
+        <v>0.525564136295676</v>
       </c>
       <c r="E229" t="n">
-        <v>0.195766615648459</v>
+        <v>0.126925019304733</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0225203773958831</v>
+        <v>0.0181334302749253</v>
       </c>
     </row>
     <row r="230">
@@ -5764,13 +5770,13 @@
         <v>234</v>
       </c>
       <c r="B230" t="n">
-        <v>-0.719367055896181</v>
+        <v>-6.71936705589618</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.75113637641012</v>
+        <v>-6.75113637641012</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.593080253069712</v>
+        <v>-6.59308025306971</v>
       </c>
       <c r="E230" t="n">
         <v>0.195766615648459</v>
@@ -5784,19 +5790,19 @@
         <v>235</v>
       </c>
       <c r="B231" t="n">
-        <v>-7.29780787608565</v>
+        <v>2.28063294410382</v>
       </c>
       <c r="C231" t="n">
-        <v>-7.30088456249741</v>
+        <v>2.24886362358988</v>
       </c>
       <c r="D231" t="n">
-        <v>-7.74488375097813</v>
+        <v>2.40691974693029</v>
       </c>
       <c r="E231" t="n">
-        <v>0.282047080590764</v>
+        <v>0.195766615648459</v>
       </c>
       <c r="F231" t="n">
-        <v>0.0270313136682057</v>
+        <v>0.0225203773958831</v>
       </c>
     </row>
     <row r="232">
@@ -5804,19 +5810,19 @@
         <v>236</v>
       </c>
       <c r="B232" t="n">
-        <v>1.70219212391435</v>
+        <v>-0.719367055896181</v>
       </c>
       <c r="C232" t="n">
-        <v>1.69911543750259</v>
+        <v>-0.75113637641012</v>
       </c>
       <c r="D232" t="n">
-        <v>1.25511624902187</v>
+        <v>-0.593080253069712</v>
       </c>
       <c r="E232" t="n">
-        <v>0.282047080590764</v>
+        <v>0.195766615648459</v>
       </c>
       <c r="F232" t="n">
-        <v>0.0270313136682057</v>
+        <v>0.0225203773958831</v>
       </c>
     </row>
     <row r="233">
@@ -5824,13 +5830,13 @@
         <v>237</v>
       </c>
       <c r="B233" t="n">
-        <v>-1.29780787608565</v>
+        <v>-7.29780787608565</v>
       </c>
       <c r="C233" t="n">
-        <v>-1.30088456249741</v>
+        <v>-7.30088456249741</v>
       </c>
       <c r="D233" t="n">
-        <v>-1.74488375097813</v>
+        <v>-7.74488375097813</v>
       </c>
       <c r="E233" t="n">
         <v>0.282047080590764</v>
@@ -5844,19 +5850,19 @@
         <v>238</v>
       </c>
       <c r="B234" t="n">
-        <v>-5.66835924651595</v>
+        <v>1.70219212391435</v>
       </c>
       <c r="C234" t="n">
-        <v>-5.66258181576849</v>
+        <v>1.69911543750259</v>
       </c>
       <c r="D234" t="n">
-        <v>-5.99651972783737</v>
+        <v>1.25511624902187</v>
       </c>
       <c r="E234" t="n">
-        <v>0.0852470345732533</v>
+        <v>0.282047080590764</v>
       </c>
       <c r="F234" t="n">
-        <v>0.0148609299785404</v>
+        <v>0.0270313136682057</v>
       </c>
     </row>
     <row r="235">
@@ -5864,19 +5870,19 @@
         <v>239</v>
       </c>
       <c r="B235" t="n">
-        <v>3.33164075348405</v>
+        <v>-1.29780787608565</v>
       </c>
       <c r="C235" t="n">
-        <v>3.33741818423151</v>
+        <v>-1.30088456249741</v>
       </c>
       <c r="D235" t="n">
-        <v>3.00348027216263</v>
+        <v>-1.74488375097813</v>
       </c>
       <c r="E235" t="n">
-        <v>0.0852470345732533</v>
+        <v>0.282047080590764</v>
       </c>
       <c r="F235" t="n">
-        <v>0.0148609299785404</v>
+        <v>0.0270313136682057</v>
       </c>
     </row>
     <row r="236">
@@ -5884,13 +5890,13 @@
         <v>240</v>
       </c>
       <c r="B236" t="n">
-        <v>0.331640753484046</v>
+        <v>-5.66835924651595</v>
       </c>
       <c r="C236" t="n">
-        <v>0.337418184231511</v>
+        <v>-5.66258181576849</v>
       </c>
       <c r="D236" t="n">
-        <v>0.00348027216263097</v>
+        <v>-5.99651972783737</v>
       </c>
       <c r="E236" t="n">
         <v>0.0852470345732533</v>
@@ -5904,19 +5910,19 @@
         <v>241</v>
       </c>
       <c r="B237" t="n">
-        <v>-6.56298825801238</v>
+        <v>3.33164075348405</v>
       </c>
       <c r="C237" t="n">
-        <v>-6.58754641809639</v>
+        <v>3.33741818423151</v>
       </c>
       <c r="D237" t="n">
-        <v>-6.98674196473976</v>
+        <v>3.00348027216263</v>
       </c>
       <c r="E237" t="n">
-        <v>0.2690323214326</v>
+        <v>0.0852470345732533</v>
       </c>
       <c r="F237" t="n">
-        <v>0.0264002826877136</v>
+        <v>0.0148609299785404</v>
       </c>
     </row>
     <row r="238">
@@ -5924,19 +5930,19 @@
         <v>242</v>
       </c>
       <c r="B238" t="n">
-        <v>2.43701174198762</v>
+        <v>0.331640753484046</v>
       </c>
       <c r="C238" t="n">
-        <v>2.41245358190361</v>
+        <v>0.337418184231511</v>
       </c>
       <c r="D238" t="n">
-        <v>2.01325803526024</v>
+        <v>0.00348027216263097</v>
       </c>
       <c r="E238" t="n">
-        <v>0.2690323214326</v>
+        <v>0.0852470345732533</v>
       </c>
       <c r="F238" t="n">
-        <v>0.0264002826877136</v>
+        <v>0.0148609299785404</v>
       </c>
     </row>
     <row r="239">
@@ -5944,13 +5950,13 @@
         <v>243</v>
       </c>
       <c r="B239" t="n">
-        <v>-0.562988258012385</v>
+        <v>-6.56298825801238</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.587546418096389</v>
+        <v>-6.58754641809639</v>
       </c>
       <c r="D239" t="n">
-        <v>-0.986741964739757</v>
+        <v>-6.98674196473976</v>
       </c>
       <c r="E239" t="n">
         <v>0.2690323214326</v>
@@ -5964,19 +5970,19 @@
         <v>244</v>
       </c>
       <c r="B240" t="n">
-        <v>-7.44769008322978</v>
+        <v>2.43701174198762</v>
       </c>
       <c r="C240" t="n">
-        <v>-7.47258465659123</v>
+        <v>2.41245358190361</v>
       </c>
       <c r="D240" t="n">
-        <v>-8.22942662083826</v>
+        <v>2.01325803526024</v>
       </c>
       <c r="E240" t="n">
-        <v>0.152788493102304</v>
+        <v>0.2690323214326</v>
       </c>
       <c r="F240" t="n">
-        <v>0.0198953540220827</v>
+        <v>0.0264002826877136</v>
       </c>
     </row>
     <row r="241">
@@ -5984,19 +5990,19 @@
         <v>245</v>
       </c>
       <c r="B241" t="n">
-        <v>1.55230991677022</v>
+        <v>-0.562988258012385</v>
       </c>
       <c r="C241" t="n">
-        <v>1.52741534340877</v>
+        <v>-0.587546418096389</v>
       </c>
       <c r="D241" t="n">
-        <v>0.77057337916174</v>
+        <v>-0.986741964739757</v>
       </c>
       <c r="E241" t="n">
-        <v>0.152788493102304</v>
+        <v>0.2690323214326</v>
       </c>
       <c r="F241" t="n">
-        <v>0.0198953540220827</v>
+        <v>0.0264002826877136</v>
       </c>
     </row>
     <row r="242">
@@ -6004,13 +6010,13 @@
         <v>246</v>
       </c>
       <c r="B242" t="n">
-        <v>-1.44769008322978</v>
+        <v>-7.44769008322978</v>
       </c>
       <c r="C242" t="n">
-        <v>-1.47258465659123</v>
+        <v>-7.47258465659123</v>
       </c>
       <c r="D242" t="n">
-        <v>-2.22942662083826</v>
+        <v>-8.22942662083826</v>
       </c>
       <c r="E242" t="n">
         <v>0.152788493102304</v>
@@ -6024,19 +6030,19 @@
         <v>247</v>
       </c>
       <c r="B243" t="n">
-        <v>1.17928162520831</v>
+        <v>1.55230991677022</v>
       </c>
       <c r="C243" t="n">
-        <v>1.17897694729317</v>
+        <v>1.52741534340877</v>
       </c>
       <c r="D243" t="n">
-        <v>1.35983548233989</v>
+        <v>0.77057337916174</v>
       </c>
       <c r="E243" t="n">
-        <v>0.0239070328229495</v>
+        <v>0.152788493102304</v>
       </c>
       <c r="F243" t="n">
-        <v>0.0078698995034352</v>
+        <v>0.0198953540220827</v>
       </c>
     </row>
     <row r="244">
@@ -6044,19 +6050,19 @@
         <v>248</v>
       </c>
       <c r="B244" t="n">
-        <v>-0.387924893695415</v>
+        <v>-1.44769008322978</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.214670164989233</v>
+        <v>-1.47258465659123</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.565431095965801</v>
+        <v>-2.22942662083826</v>
       </c>
       <c r="E244" t="n">
-        <v>0.266895369325391</v>
+        <v>0.152788493102304</v>
       </c>
       <c r="F244" t="n">
-        <v>0.0308739007511309</v>
+        <v>0.0198953540220827</v>
       </c>
     </row>
     <row r="245">
@@ -6064,19 +6070,19 @@
         <v>249</v>
       </c>
       <c r="B245" t="n">
-        <v>-8.58532635347096</v>
+        <v>1.17928162520831</v>
       </c>
       <c r="C245" t="n">
-        <v>-8.54545641624325</v>
+        <v>1.17897694729317</v>
       </c>
       <c r="D245" t="n">
-        <v>-8.95712662644021</v>
+        <v>1.35983548233989</v>
       </c>
       <c r="E245" t="n">
-        <v>0.286106788001192</v>
+        <v>0.0239070328229495</v>
       </c>
       <c r="F245" t="n">
-        <v>0.0272251592344264</v>
+        <v>0.0078698995034352</v>
       </c>
     </row>
     <row r="246">
@@ -6084,19 +6090,19 @@
         <v>250</v>
       </c>
       <c r="B246" t="n">
-        <v>0.414673646529041</v>
+        <v>-0.387924893695415</v>
       </c>
       <c r="C246" t="n">
-        <v>0.454543583756748</v>
+        <v>-0.214670164989233</v>
       </c>
       <c r="D246" t="n">
-        <v>0.0428733735597898</v>
+        <v>-0.565431095965801</v>
       </c>
       <c r="E246" t="n">
-        <v>0.286106788001192</v>
+        <v>0.266895369325391</v>
       </c>
       <c r="F246" t="n">
-        <v>0.0272251592344264</v>
+        <v>0.0308739007511309</v>
       </c>
     </row>
     <row r="247">
@@ -6104,13 +6110,13 @@
         <v>251</v>
       </c>
       <c r="B247" t="n">
-        <v>-2.58532635347096</v>
+        <v>-8.58532635347096</v>
       </c>
       <c r="C247" t="n">
-        <v>-2.54545641624325</v>
+        <v>-8.54545641624325</v>
       </c>
       <c r="D247" t="n">
-        <v>-2.95712662644021</v>
+        <v>-8.95712662644021</v>
       </c>
       <c r="E247" t="n">
         <v>0.286106788001192</v>
@@ -6124,19 +6130,19 @@
         <v>252</v>
       </c>
       <c r="B248" t="n">
-        <v>-11.1376754319643</v>
+        <v>0.414673646529041</v>
       </c>
       <c r="C248" t="n">
-        <v>-11.0938235262643</v>
+        <v>0.454543583756748</v>
       </c>
       <c r="D248" t="n">
-        <v>-11.4458240571519</v>
+        <v>0.0428733735597898</v>
       </c>
       <c r="E248" t="n">
-        <v>0.342127792431983</v>
+        <v>0.286106788001192</v>
       </c>
       <c r="F248" t="n">
-        <v>0.0297714868820981</v>
+        <v>0.0272251592344264</v>
       </c>
     </row>
     <row r="249">
@@ -6144,19 +6150,19 @@
         <v>253</v>
       </c>
       <c r="B249" t="n">
-        <v>-2.1376754319643</v>
+        <v>-2.58532635347096</v>
       </c>
       <c r="C249" t="n">
-        <v>-2.09382352626426</v>
+        <v>-2.54545641624325</v>
       </c>
       <c r="D249" t="n">
-        <v>-2.44582405715191</v>
+        <v>-2.95712662644021</v>
       </c>
       <c r="E249" t="n">
-        <v>0.342127792431983</v>
+        <v>0.286106788001192</v>
       </c>
       <c r="F249" t="n">
-        <v>0.0297714868820981</v>
+        <v>0.0272251592344264</v>
       </c>
     </row>
     <row r="250">
@@ -6164,13 +6170,13 @@
         <v>254</v>
       </c>
       <c r="B250" t="n">
-        <v>-5.1376754319643</v>
+        <v>-11.1376754319643</v>
       </c>
       <c r="C250" t="n">
-        <v>-5.09382352626426</v>
+        <v>-11.0938235262643</v>
       </c>
       <c r="D250" t="n">
-        <v>-5.44582405715191</v>
+        <v>-11.4458240571519</v>
       </c>
       <c r="E250" t="n">
         <v>0.342127792431983</v>
@@ -6184,19 +6190,19 @@
         <v>255</v>
       </c>
       <c r="B251" t="n">
-        <v>-7.81039476957295</v>
+        <v>-2.1376754319643</v>
       </c>
       <c r="C251" t="n">
-        <v>-7.71514785095294</v>
+        <v>-2.09382352626426</v>
       </c>
       <c r="D251" t="n">
-        <v>-7.77116908592302</v>
+        <v>-2.44582405715191</v>
       </c>
       <c r="E251" t="n">
-        <v>0.16641007564819</v>
+        <v>0.342127792431983</v>
       </c>
       <c r="F251" t="n">
-        <v>0.0207632893737257</v>
+        <v>0.0297714868820981</v>
       </c>
     </row>
     <row r="252">
@@ -6204,19 +6210,19 @@
         <v>256</v>
       </c>
       <c r="B252" t="n">
-        <v>1.18960523042705</v>
+        <v>-5.1376754319643</v>
       </c>
       <c r="C252" t="n">
-        <v>1.28485214904706</v>
+        <v>-5.09382352626426</v>
       </c>
       <c r="D252" t="n">
-        <v>1.22883091407698</v>
+        <v>-5.44582405715191</v>
       </c>
       <c r="E252" t="n">
-        <v>0.16641007564819</v>
+        <v>0.342127792431983</v>
       </c>
       <c r="F252" t="n">
-        <v>0.0207632893737257</v>
+        <v>0.0297714868820981</v>
       </c>
     </row>
     <row r="253">
@@ -6224,13 +6230,13 @@
         <v>257</v>
       </c>
       <c r="B253" t="n">
-        <v>-1.81039476957295</v>
+        <v>-7.81039476957295</v>
       </c>
       <c r="C253" t="n">
-        <v>-1.71514785095294</v>
+        <v>-7.71514785095294</v>
       </c>
       <c r="D253" t="n">
-        <v>-1.77116908592302</v>
+        <v>-7.77116908592302</v>
       </c>
       <c r="E253" t="n">
         <v>0.16641007564819</v>
@@ -6244,19 +6250,19 @@
         <v>258</v>
       </c>
       <c r="B254" t="n">
-        <v>-9.48234680236329</v>
+        <v>1.18960523042705</v>
       </c>
       <c r="C254" t="n">
-        <v>-9.47325479550294</v>
+        <v>1.28485214904706</v>
       </c>
       <c r="D254" t="n">
-        <v>-10.0659832147074</v>
+        <v>1.22883091407698</v>
       </c>
       <c r="E254" t="n">
-        <v>0.192017860945023</v>
+        <v>0.16641007564819</v>
       </c>
       <c r="F254" t="n">
-        <v>0.0223037126573844</v>
+        <v>0.0207632893737257</v>
       </c>
     </row>
     <row r="255">
@@ -6264,19 +6270,19 @@
         <v>259</v>
       </c>
       <c r="B255" t="n">
-        <v>-0.482346802363294</v>
+        <v>-1.81039476957295</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.47325479550294</v>
+        <v>-1.71514785095294</v>
       </c>
       <c r="D255" t="n">
-        <v>-1.06598321470742</v>
+        <v>-1.77116908592302</v>
       </c>
       <c r="E255" t="n">
-        <v>0.192017860945023</v>
+        <v>0.16641007564819</v>
       </c>
       <c r="F255" t="n">
-        <v>0.0223037126573844</v>
+        <v>0.0207632893737257</v>
       </c>
     </row>
     <row r="256">
@@ -6284,13 +6290,13 @@
         <v>260</v>
       </c>
       <c r="B256" t="n">
-        <v>-3.48234680236329</v>
+        <v>-9.48234680236329</v>
       </c>
       <c r="C256" t="n">
-        <v>-3.47325479550294</v>
+        <v>-9.47325479550294</v>
       </c>
       <c r="D256" t="n">
-        <v>-4.06598321470742</v>
+        <v>-10.0659832147074</v>
       </c>
       <c r="E256" t="n">
         <v>0.192017860945023</v>
@@ -6304,19 +6310,19 @@
         <v>261</v>
       </c>
       <c r="B257" t="n">
-        <v>-9.78356888805875</v>
+        <v>-0.482346802363294</v>
       </c>
       <c r="C257" t="n">
-        <v>-9.80898619716051</v>
+        <v>-0.47325479550294</v>
       </c>
       <c r="D257" t="n">
-        <v>-10.3373956657658</v>
+        <v>-1.06598321470742</v>
       </c>
       <c r="E257" t="n">
-        <v>0.241671282988214</v>
+        <v>0.192017860945023</v>
       </c>
       <c r="F257" t="n">
-        <v>0.0250218186130668</v>
+        <v>0.0223037126573844</v>
       </c>
     </row>
     <row r="258">
@@ -6324,19 +6330,19 @@
         <v>262</v>
       </c>
       <c r="B258" t="n">
-        <v>-0.783568888058748</v>
+        <v>-3.48234680236329</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.808986197160512</v>
+        <v>-3.47325479550294</v>
       </c>
       <c r="D258" t="n">
-        <v>-1.33739566576581</v>
+        <v>-4.06598321470742</v>
       </c>
       <c r="E258" t="n">
-        <v>0.241671282988214</v>
+        <v>0.192017860945023</v>
       </c>
       <c r="F258" t="n">
-        <v>0.0250218186130668</v>
+        <v>0.0223037126573844</v>
       </c>
     </row>
     <row r="259">
@@ -6344,13 +6350,13 @@
         <v>263</v>
       </c>
       <c r="B259" t="n">
-        <v>-3.78356888805875</v>
+        <v>-9.78356888805875</v>
       </c>
       <c r="C259" t="n">
-        <v>-3.80898619716051</v>
+        <v>-9.80898619716051</v>
       </c>
       <c r="D259" t="n">
-        <v>-4.33739566576581</v>
+        <v>-10.3373956657658</v>
       </c>
       <c r="E259" t="n">
         <v>0.241671282988214</v>
@@ -6364,19 +6370,19 @@
         <v>264</v>
       </c>
       <c r="B260" t="n">
-        <v>-16.0001688893144</v>
+        <v>-0.783568888058748</v>
       </c>
       <c r="C260" t="n">
-        <v>-16.0001144472419</v>
+        <v>-0.808986197160512</v>
       </c>
       <c r="D260" t="n">
-        <v>-16.0000953598044</v>
+        <v>-1.33739566576581</v>
       </c>
       <c r="E260" t="n">
-        <v>0.0000000962471936592136</v>
+        <v>0.241671282988214</v>
       </c>
       <c r="F260" t="n">
-        <v>0.0000157906637382125</v>
+        <v>0.0250218186130668</v>
       </c>
     </row>
     <row r="261">
@@ -6384,19 +6390,19 @@
         <v>265</v>
       </c>
       <c r="B261" t="n">
-        <v>-7.00016888931441</v>
+        <v>-3.78356888805875</v>
       </c>
       <c r="C261" t="n">
-        <v>-7.00011444724188</v>
+        <v>-3.80898619716051</v>
       </c>
       <c r="D261" t="n">
-        <v>-7.00009535980438</v>
+        <v>-4.33739566576581</v>
       </c>
       <c r="E261" t="n">
-        <v>0.0000000962471936592264</v>
+        <v>0.241671282988214</v>
       </c>
       <c r="F261" t="n">
-        <v>0.0000157906637382136</v>
+        <v>0.0250218186130668</v>
       </c>
     </row>
     <row r="262">
@@ -6404,19 +6410,19 @@
         <v>266</v>
       </c>
       <c r="B262" t="n">
-        <v>-10.0001688893144</v>
+        <v>-16.0001688893144</v>
       </c>
       <c r="C262" t="n">
-        <v>-10.0001144472419</v>
+        <v>-16.0001144472419</v>
       </c>
       <c r="D262" t="n">
-        <v>-10.0000953598044</v>
+        <v>-16.0000953598044</v>
       </c>
       <c r="E262" t="n">
-        <v>0.0000000962471936592294</v>
+        <v>0.0000000962471936592136</v>
       </c>
       <c r="F262" t="n">
-        <v>0.0000157906637382138</v>
+        <v>0.0000157906637382125</v>
       </c>
     </row>
     <row r="263">
@@ -6424,19 +6430,19 @@
         <v>267</v>
       </c>
       <c r="B263" t="n">
-        <v>-7.06909585835686</v>
+        <v>-7.00016888931441</v>
       </c>
       <c r="C263" t="n">
-        <v>-7.08671609823958</v>
+        <v>-7.00011444724188</v>
       </c>
       <c r="D263" t="n">
-        <v>-6.98296666070122</v>
+        <v>-7.00009535980438</v>
       </c>
       <c r="E263" t="n">
-        <v>0.0835980316493435</v>
+        <v>0.0000000962471936592264</v>
       </c>
       <c r="F263" t="n">
-        <v>0.0147164945393527</v>
+        <v>0.0000157906637382136</v>
       </c>
     </row>
     <row r="264">
@@ -6444,19 +6450,19 @@
         <v>268</v>
       </c>
       <c r="B264" t="n">
-        <v>-10.1525917761504</v>
+        <v>-10.0001688893144</v>
       </c>
       <c r="C264" t="n">
-        <v>-10.1219982998966</v>
+        <v>-10.0001144472419</v>
       </c>
       <c r="D264" t="n">
-        <v>-11.1261205536309</v>
+        <v>-10.0000953598044</v>
       </c>
       <c r="E264" t="n">
-        <v>0.71629861954669</v>
+        <v>0.0000000962471936592294</v>
       </c>
       <c r="F264" t="n">
-        <v>0.0430777890050241</v>
+        <v>0.0000157906637382138</v>
       </c>
     </row>
     <row r="265">
@@ -6464,19 +6470,19 @@
         <v>269</v>
       </c>
       <c r="B265" t="n">
-        <v>-1.15259177615043</v>
+        <v>-7.06909585835686</v>
       </c>
       <c r="C265" t="n">
-        <v>-1.12199829989665</v>
+        <v>-7.08671609823958</v>
       </c>
       <c r="D265" t="n">
-        <v>-2.12612055363087</v>
+        <v>-6.98296666070122</v>
       </c>
       <c r="E265" t="n">
-        <v>0.71629861954669</v>
+        <v>0.0835980316493435</v>
       </c>
       <c r="F265" t="n">
-        <v>0.0430777890050241</v>
+        <v>0.0147164945393527</v>
       </c>
     </row>
     <row r="266">
@@ -6484,13 +6490,13 @@
         <v>270</v>
       </c>
       <c r="B266" t="n">
-        <v>-4.15259177615043</v>
+        <v>-10.1525917761504</v>
       </c>
       <c r="C266" t="n">
-        <v>-4.12199829989665</v>
+        <v>-10.1219982998966</v>
       </c>
       <c r="D266" t="n">
-        <v>-5.12612055363087</v>
+        <v>-11.1261205536309</v>
       </c>
       <c r="E266" t="n">
         <v>0.71629861954669</v>
@@ -6504,19 +6510,19 @@
         <v>271</v>
       </c>
       <c r="B267" t="n">
-        <v>-5.06463887066509</v>
+        <v>-1.15259177615043</v>
       </c>
       <c r="C267" t="n">
-        <v>-5.02087801373083</v>
+        <v>-1.12199829989665</v>
       </c>
       <c r="D267" t="n">
-        <v>-4.81565717426209</v>
+        <v>-2.12612055363087</v>
       </c>
       <c r="E267" t="n">
-        <v>0.0436346956879248</v>
+        <v>0.71629861954669</v>
       </c>
       <c r="F267" t="n">
-        <v>0.0106321800717221</v>
+        <v>0.0430777890050241</v>
       </c>
     </row>
     <row r="268">
@@ -6524,19 +6530,19 @@
         <v>272</v>
       </c>
       <c r="B268" t="n">
-        <v>3.93536112933491</v>
+        <v>-4.15259177615043</v>
       </c>
       <c r="C268" t="n">
-        <v>3.97912198626917</v>
+        <v>-4.12199829989665</v>
       </c>
       <c r="D268" t="n">
-        <v>4.18434282573791</v>
+        <v>-5.12612055363087</v>
       </c>
       <c r="E268" t="n">
-        <v>0.0436346956879248</v>
+        <v>0.71629861954669</v>
       </c>
       <c r="F268" t="n">
-        <v>0.0106321800717221</v>
+        <v>0.0430777890050241</v>
       </c>
     </row>
     <row r="269">
@@ -6544,13 +6550,13 @@
         <v>273</v>
       </c>
       <c r="B269" t="n">
-        <v>0.935361129334911</v>
+        <v>-5.06463887066509</v>
       </c>
       <c r="C269" t="n">
-        <v>0.979121986269174</v>
+        <v>-5.02087801373083</v>
       </c>
       <c r="D269" t="n">
-        <v>1.18434282573791</v>
+        <v>-4.81565717426209</v>
       </c>
       <c r="E269" t="n">
         <v>0.0436346956879248</v>
@@ -6564,19 +6570,19 @@
         <v>274</v>
       </c>
       <c r="B270" t="n">
-        <v>1.93090414164314</v>
+        <v>3.93536112933491</v>
       </c>
       <c r="C270" t="n">
-        <v>1.91328390176042</v>
+        <v>3.97912198626917</v>
       </c>
       <c r="D270" t="n">
-        <v>2.01703333929878</v>
+        <v>4.18434282573791</v>
       </c>
       <c r="E270" t="n">
-        <v>0.0835980316493435</v>
+        <v>0.0436346956879248</v>
       </c>
       <c r="F270" t="n">
-        <v>0.0147164945393527</v>
+        <v>0.0106321800717221</v>
       </c>
     </row>
     <row r="271">
@@ -6584,19 +6590,19 @@
         <v>275</v>
       </c>
       <c r="B271" t="n">
-        <v>-1.06909585835686</v>
+        <v>0.935361129334911</v>
       </c>
       <c r="C271" t="n">
-        <v>-1.08671609823958</v>
+        <v>0.979121986269174</v>
       </c>
       <c r="D271" t="n">
-        <v>-0.98296666070122</v>
+        <v>1.18434282573791</v>
       </c>
       <c r="E271" t="n">
-        <v>0.0835980316493435</v>
+        <v>0.0436346956879248</v>
       </c>
       <c r="F271" t="n">
-        <v>0.0147164945393527</v>
+        <v>0.0106321800717221</v>
       </c>
     </row>
     <row r="272">
@@ -6604,19 +6610,19 @@
         <v>276</v>
       </c>
       <c r="B272" t="n">
-        <v>-0.666611909893623</v>
+        <v>1.93090414164314</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.66059766321667</v>
+        <v>1.91328390176042</v>
       </c>
       <c r="D272" t="n">
-        <v>-0.47976307308921</v>
+        <v>2.01703333929878</v>
       </c>
       <c r="E272" t="n">
-        <v>0.0529478407200874</v>
+        <v>0.0835980316493435</v>
       </c>
       <c r="F272" t="n">
-        <v>0.0117119841108882</v>
+        <v>0.0147164945393527</v>
       </c>
     </row>
     <row r="273">
@@ -6624,19 +6630,19 @@
         <v>277</v>
       </c>
       <c r="B273" t="n">
-        <v>7.61722797927461</v>
+        <v>-1.06909585835686</v>
       </c>
       <c r="C273" t="n">
-        <v>7.63</v>
+        <v>-1.08671609823958</v>
       </c>
       <c r="D273" t="n">
-        <v>7.63</v>
+        <v>-0.98296666070122</v>
       </c>
       <c r="E273" t="n">
-        <v>0.184809179059283</v>
+        <v>0.0835980316493435</v>
       </c>
       <c r="F273" t="n">
-        <v>0.0218810478869333</v>
+        <v>0.0147164945393527</v>
       </c>
     </row>
     <row r="274">
@@ -6644,18 +6650,58 @@
         <v>278</v>
       </c>
       <c r="B274" t="n">
+        <v>-0.666611909893623</v>
+      </c>
+      <c r="C274" t="n">
+        <v>-0.66059766321667</v>
+      </c>
+      <c r="D274" t="n">
+        <v>-0.47976307308921</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.0529478407200874</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0.0117119841108882</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>279</v>
+      </c>
+      <c r="B275" t="n">
+        <v>7.61722797927461</v>
+      </c>
+      <c r="C275" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="D275" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.184809179059283</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0.0218810478869333</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>280</v>
+      </c>
+      <c r="B276" t="n">
         <v>0.243462866770415</v>
       </c>
-      <c r="C274" t="n">
+      <c r="C276" t="n">
         <v>0.218475296387963</v>
       </c>
-      <c r="D274" t="n">
+      <c r="D276" t="n">
         <v>0.331311817486975</v>
       </c>
-      <c r="E274" t="n">
+      <c r="E276" t="n">
         <v>0.0134185743271285</v>
       </c>
-      <c r="F274" t="n">
+      <c r="F276" t="n">
         <v>0.00589602797866525</v>
       </c>
     </row>
@@ -7672,7 +7718,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B51" t="n">
         <v>0.0000000310144846454978</v>
@@ -7692,7 +7738,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52" t="n">
         <v>31.0144846454978</v>
@@ -7712,7 +7758,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53" t="n">
         <v>0.0310144846454978</v>
@@ -7732,7 +7778,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B54" t="n">
         <v>0.00000000000000000000746920232073839</v>
@@ -7752,7 +7798,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B55" t="n">
         <v>0.00000000000746920232073839</v>
@@ -7772,7 +7818,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B56" t="n">
         <v>0.00000000000000746920232073839</v>
@@ -7792,7 +7838,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B57" t="n">
         <v>0.0000276780654936006</v>
@@ -7812,7 +7858,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B58" t="n">
         <v>27678.0654936006</v>
@@ -7832,7 +7878,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B59" t="n">
         <v>27.6780654936006</v>
@@ -7852,7 +7898,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B60" t="n">
         <v>0.000902764098380694</v>
@@ -7872,7 +7918,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B61" t="n">
         <v>902764.098380694</v>
@@ -7892,7 +7938,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B62" t="n">
         <v>902.764098380694</v>
@@ -7912,7 +7958,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B63" t="n">
         <v>0.0000000000000000000106940462939211</v>
@@ -7932,7 +7978,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B64" t="n">
         <v>0.0000000000106940462939211</v>
@@ -7952,7 +7998,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B65" t="n">
         <v>0.0000000000000106940462939211</v>
@@ -7972,7 +8018,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B66" t="n">
         <v>0.0000475295336787565</v>
@@ -7992,7 +8038,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B67" t="n">
         <v>47529.5336787565</v>
@@ -8012,7 +8058,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B68" t="n">
         <v>47.5295336787565</v>
@@ -8032,7 +8078,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69" t="n">
         <v>0.00000324230678257677</v>
@@ -8052,7 +8098,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B70" t="n">
         <v>3242.30678257677</v>
@@ -8072,7 +8118,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B71" t="n">
         <v>3.24230678257677</v>
@@ -8092,7 +8138,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B72" t="n">
         <v>0.00000320078289287486</v>
@@ -8112,7 +8158,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B73" t="n">
         <v>3200.78289287486</v>
@@ -8132,7 +8178,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B74" t="n">
         <v>3.20078289287486</v>
@@ -8152,7 +8198,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B75" t="n">
         <v>0.00000480536699281214</v>
@@ -8172,7 +8218,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B76" t="n">
         <v>4805.36699281214</v>
@@ -8192,7 +8238,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" t="n">
         <v>4.80536699281214</v>
@@ -8212,7 +8258,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B78" t="n">
         <v>0.000445417616580311</v>
@@ -8232,7 +8278,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B79" t="n">
         <v>445417.616580311</v>
@@ -8252,7 +8298,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B80" t="n">
         <v>445.417616580311</v>
@@ -8272,7 +8318,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B81" t="n">
         <v>0.000316880829015544</v>
@@ -8292,7 +8338,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B82" t="n">
         <v>316880.829015544</v>
@@ -8312,7 +8358,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B83" t="n">
         <v>316.880829015544</v>
@@ -8332,7 +8378,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B84" t="n">
         <v>5.38370466321244</v>
@@ -8352,7 +8398,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B85" t="n">
         <v>0.000119058497409326</v>
@@ -8372,7 +8418,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B86" t="n">
         <v>119058.497409326</v>
@@ -8392,7 +8438,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B87" t="n">
         <v>119.058497409326</v>
@@ -8412,7 +8458,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B88" t="n">
         <v>0.000000000000770579957409138</v>
@@ -8432,7 +8478,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B89" t="n">
         <v>0.000000770579957409138</v>
@@ -8452,7 +8498,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B90" t="n">
         <v>0.000000000770579957409138</v>
@@ -8472,7 +8518,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B91" t="n">
         <v>0.00000790646232674756</v>
@@ -8492,7 +8538,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B92" t="n">
         <v>7906.46232674757</v>
@@ -8512,7 +8558,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B93" t="n">
         <v>7.90646232674757</v>
@@ -8532,7 +8578,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B94" t="n">
         <v>0.0000000887438483653967</v>
@@ -8552,7 +8598,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B95" t="n">
         <v>88.7438483653967</v>
@@ -8572,7 +8618,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B96" t="n">
         <v>0.0887438483653967</v>
@@ -8592,7 +8638,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B97" t="n">
         <v>0.000000142045197459229</v>
@@ -8612,7 +8658,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B98" t="n">
         <v>142.045197459229</v>
@@ -8632,7 +8678,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B99" t="n">
         <v>0.142045197459229</v>
@@ -8652,7 +8698,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B100" t="n">
         <v>0.00000269894919570771</v>
@@ -8672,7 +8718,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B101" t="n">
         <v>2698.94919570771</v>
@@ -8692,7 +8738,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B102" t="n">
         <v>2.69894919570771</v>
@@ -8712,7 +8758,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B103" t="n">
         <v>0.000000645110272922381</v>
@@ -8732,7 +8778,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B104" t="n">
         <v>645.110272922381</v>
@@ -8752,7 +8798,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B105" t="n">
         <v>0.645110272922381</v>
@@ -8772,7 +8818,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B106" t="n">
         <v>0.0000000606682802917006</v>
@@ -8792,7 +8838,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B107" t="n">
         <v>60.6682802917006</v>
@@ -8812,7 +8858,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B108" t="n">
         <v>0.0606682802917006</v>
@@ -8832,7 +8878,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B109" t="n">
         <v>15.9842227979275</v>
@@ -8852,7 +8898,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B110" t="n">
         <v>0.471360103626943</v>
@@ -8872,7 +8918,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B111" t="n">
         <v>0.00000000438072158069764</v>
@@ -8892,7 +8938,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B112" t="n">
         <v>4.38072158069764</v>
@@ -8912,7 +8958,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B113" t="n">
         <v>0.00438072158069764</v>
@@ -8932,7 +8978,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B114" t="n">
         <v>0.0000000000198705190782111</v>
@@ -8952,7 +8998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B115" t="n">
         <v>0.0198705190782111</v>
@@ -8972,7 +9018,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B116" t="n">
         <v>0.0000198705190782111</v>
@@ -8992,7 +9038,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B117" t="n">
         <v>0.0000000062016156847442</v>
@@ -9012,7 +9058,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B118" t="n">
         <v>6.2016156847442</v>
@@ -9032,7 +9078,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B119" t="n">
         <v>0.0062016156847442</v>
@@ -9052,7 +9098,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B120" t="n">
         <v>0.000000000648581405127695</v>
@@ -9072,7 +9118,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B121" t="n">
         <v>0.648581405127695</v>
@@ -9092,7 +9138,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B122" t="n">
         <v>0.000648581405127695</v>
@@ -9112,7 +9158,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B123" t="n">
         <v>0.000000000350175441881575</v>
@@ -9132,7 +9178,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B124" t="n">
         <v>0.350175441881575</v>
@@ -9152,7 +9198,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B125" t="n">
         <v>0.000350175441881575</v>
@@ -9172,7 +9218,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B126" t="n">
         <v>0.0000000000000000999646973262527</v>
@@ -9192,7 +9238,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B127" t="n">
         <v>0.0000000999646973262527</v>
@@ -9212,7 +9258,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B128" t="n">
         <v>0.0000000000999646973262527</v>
@@ -9232,7 +9278,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B129" t="n">
         <v>0.000000104099137305699</v>
@@ -9252,7 +9298,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B130" t="n">
         <v>0.000000000860854385686675</v>
@@ -9272,7 +9318,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B131" t="n">
         <v>0.860854385686675</v>
@@ -9292,7 +9338,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B132" t="n">
         <v>0.000860854385686675</v>
@@ -9312,7 +9358,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B133" t="n">
         <v>0.00000649233111218818</v>
@@ -9332,7 +9378,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B134" t="n">
         <v>6492.33111218818</v>
@@ -9352,7 +9398,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B135" t="n">
         <v>6.49233111218818</v>
@@ -9372,7 +9418,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B136" t="n">
         <v>104.099137305699</v>
@@ -9392,7 +9438,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B137" t="n">
         <v>0.104099137305699</v>
@@ -9412,7 +9458,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B138" t="n">
         <v>-9.42930793778969</v>
@@ -9432,7 +9478,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B139" t="n">
         <v>-3.42930793778969</v>
@@ -9452,7 +9498,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B140" t="n">
         <v>-0.429307937789685</v>
@@ -9472,7 +9518,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B141" t="n">
         <v>-6.42930793778969</v>
@@ -9492,7 +9538,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B142" t="n">
         <v>-11.3244265835902</v>
@@ -9512,7 +9558,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B143" t="n">
         <v>-5.32442658359016</v>
@@ -9532,7 +9578,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B144" t="n">
         <v>-2.32442658359016</v>
@@ -9552,7 +9598,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B145" t="n">
         <v>-8.32442658359016</v>
@@ -9572,7 +9618,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B146" t="n">
         <v>-10.3570835604135</v>
@@ -9592,7 +9638,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B147" t="n">
         <v>-4.35708356041347</v>
@@ -9612,7 +9658,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B148" t="n">
         <v>-1.35708356041347</v>
@@ -9632,7 +9678,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B149" t="n">
         <v>-7.35708356041347</v>
@@ -9652,7 +9698,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B150" t="n">
         <v>-11.1926925697674</v>
@@ -9672,7 +9718,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B151" t="n">
         <v>-5.19269256976736</v>
@@ -9692,7 +9738,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B152" t="n">
         <v>-2.19269256976736</v>
@@ -9712,7 +9758,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B153" t="n">
         <v>-8.19269256976736</v>
@@ -9732,7 +9778,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B154" t="n">
         <v>-12.669384729144</v>
@@ -9752,7 +9798,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B155" t="n">
         <v>-6.66938472914396</v>
@@ -9772,7 +9818,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B156" t="n">
         <v>-3.66938472914396</v>
@@ -9792,7 +9838,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B157" t="n">
         <v>-9.66938472914396</v>
@@ -9812,7 +9858,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B158" t="n">
         <v>-12.4898499471774</v>
@@ -9832,7 +9878,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B159" t="n">
         <v>-6.48984994717738</v>
@@ -9852,7 +9898,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B160" t="n">
         <v>-3.48984994717737</v>
@@ -9872,7 +9918,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B161" t="n">
         <v>-9.48984994717737</v>
@@ -9892,7 +9938,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B162" t="n">
         <v>-6.11598684803654</v>
@@ -9912,7 +9958,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B163" t="n">
         <v>2.88401315196346</v>
@@ -9932,7 +9978,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B164" t="n">
         <v>-0.115986848036539</v>
@@ -9952,7 +9998,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B165" t="n">
         <v>-5.37902517824316</v>
@@ -9972,7 +10018,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B166" t="n">
         <v>3.62097482175684</v>
@@ -9992,7 +10038,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B167" t="n">
         <v>0.620974821756843</v>
@@ -10012,7 +10058,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B168" t="n">
         <v>-5.11091690555914</v>
@@ -10032,7 +10078,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B169" t="n">
         <v>3.88908309444086</v>
@@ -10052,7 +10098,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B170" t="n">
         <v>0.889083094440858</v>
@@ -10072,7 +10118,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B171" t="n">
         <v>-2.97800662468358</v>
@@ -10092,7 +10138,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B172" t="n">
         <v>6.02199337531642</v>
@@ -10112,7 +10158,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B173" t="n">
         <v>3.02199337531642</v>
@@ -10132,7 +10178,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B174" t="n">
         <v>-3.65101105730638</v>
@@ -10152,7 +10198,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B175" t="n">
         <v>5.34898894269362</v>
@@ -10172,7 +10218,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B176" t="n">
         <v>2.34898894269362</v>
@@ -10192,7 +10238,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B177" t="n">
         <v>-8.03306989879472</v>
@@ -10212,7 +10258,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B178" t="n">
         <v>0.966930101205278</v>
@@ -10232,7 +10278,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B179" t="n">
         <v>-2.03306989879472</v>
@@ -10252,7 +10298,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B180" t="n">
         <v>-2.61618579484238</v>
@@ -10272,7 +10318,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B181" t="n">
         <v>6.38381420515762</v>
@@ -10292,7 +10338,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B182" t="n">
         <v>3.38381420515762</v>
@@ -10312,7 +10358,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B183" t="n">
         <v>-3.8624318393549</v>
@@ -10332,7 +10378,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B184" t="n">
         <v>5.1375681606451</v>
@@ -10352,7 +10398,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B185" t="n">
         <v>2.1375681606451</v>
@@ -10372,7 +10418,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B186" t="n">
         <v>-7.64404785956147</v>
@@ -10392,7 +10438,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B187" t="n">
         <v>1.35595214043853</v>
@@ -10412,7 +10458,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B188" t="n">
         <v>-1.64404785956147</v>
@@ -10432,7 +10478,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B189" t="n">
         <v>-20.8685301204301</v>
@@ -10452,7 +10498,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B190" t="n">
         <v>-11.8685301204301</v>
@@ -10472,7 +10518,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B191" t="n">
         <v>-14.8685301204301</v>
@@ -10492,7 +10538,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B192" t="n">
         <v>-4.56438170024587</v>
@@ -10512,7 +10558,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B193" t="n">
         <v>4.43561829975413</v>
@@ -10532,7 +10578,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B194" t="n">
         <v>1.43561829975413</v>
@@ -10552,7 +10598,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B195" t="n">
         <v>-3.3208835525604</v>
@@ -10572,7 +10618,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B196" t="n">
         <v>5.6791164474396</v>
@@ -10592,7 +10638,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B197" t="n">
         <v>2.6791164474396</v>
@@ -10612,7 +10658,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B198" t="n">
         <v>-20.221579061294</v>
@@ -10632,7 +10678,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B199" t="n">
         <v>-11.221579061294</v>
@@ -10652,7 +10698,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B200" t="n">
         <v>-14.221579061294</v>
@@ -10672,7 +10718,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B201" t="n">
         <v>-4.39006948872305</v>
@@ -10692,7 +10738,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B202" t="n">
         <v>4.60993051127695</v>
@@ -10712,7 +10758,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B203" t="n">
         <v>1.60993051127695</v>
@@ -10732,7 +10778,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B204" t="n">
         <v>-6.753908979177</v>
@@ -10752,7 +10798,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B205" t="n">
         <v>2.246091020823</v>
@@ -10772,7 +10818,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B206" t="n">
         <v>-0.753908979176996</v>
@@ -10792,7 +10838,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B207" t="n">
         <v>-5.79189417065519</v>
@@ -10812,7 +10858,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B208" t="n">
         <v>3.20810582934481</v>
@@ -10832,7 +10878,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B209" t="n">
         <v>0.208105829344813</v>
@@ -10852,7 +10898,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B210" t="n">
         <v>-5.52723431891734</v>
@@ -10872,7 +10918,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B211" t="n">
         <v>3.47276568108266</v>
@@ -10892,7 +10938,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B212" t="n">
         <v>0.472765681082662</v>
@@ -10912,7 +10958,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B213" t="n">
         <v>-3.39728011553017</v>
@@ -10932,7 +10978,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B214" t="n">
         <v>5.60271988446983</v>
@@ -10952,7 +10998,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B215" t="n">
         <v>2.60271988446983</v>
@@ -10972,7 +11018,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B216" t="n">
         <v>-3.65525695144415</v>
@@ -10992,7 +11038,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B217" t="n">
         <v>5.34474304855584</v>
@@ -11012,7 +11058,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B218" t="n">
         <v>2.34474304855584</v>
@@ -11032,7 +11078,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B219" t="n">
         <v>-4.08795850644903</v>
@@ -11052,7 +11098,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B220" t="n">
         <v>4.91204149355097</v>
@@ -11072,7 +11118,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B221" t="n">
         <v>1.91204149355097</v>
@@ -11092,7 +11138,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B222" t="n">
         <v>-12.2246831891206</v>
@@ -11112,7 +11158,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B223" t="n">
         <v>-6.22468318912056</v>
@@ -11132,7 +11178,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B224" t="n">
         <v>-9.22468318912055</v>
@@ -11152,7 +11198,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B225" t="n">
         <v>-5.24304035875144</v>
@@ -11172,7 +11218,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B226" t="n">
         <v>3.75695964124856</v>
@@ -11192,7 +11238,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B227" t="n">
         <v>0.756959641248558</v>
@@ -11212,7 +11258,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B228" t="n">
         <v>-7.28982370054765</v>
@@ -11232,7 +11278,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B229" t="n">
         <v>1.71017629945235</v>
@@ -11252,7 +11298,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B230" t="n">
         <v>-1.28982370054765</v>
@@ -11272,7 +11318,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B231" t="n">
         <v>-7.25783337325316</v>
@@ -11292,7 +11338,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B232" t="n">
         <v>1.74216662674684</v>
@@ -11312,7 +11358,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B233" t="n">
         <v>-1.25783337325316</v>
@@ -11332,7 +11378,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B234" t="n">
         <v>-5.6700664262043</v>
@@ -11352,7 +11398,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B235" t="n">
         <v>3.3299335737957</v>
@@ -11372,7 +11418,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B236" t="n">
         <v>0.329933573795699</v>
@@ -11392,7 +11438,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B237" t="n">
         <v>-6.52301375406182</v>
@@ -11412,7 +11458,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B238" t="n">
         <v>2.47698624593818</v>
@@ -11432,7 +11478,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B239" t="n">
         <v>-0.523013754061816</v>
@@ -11452,7 +11498,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B240" t="n">
         <v>-7.3475245713113</v>
@@ -11472,7 +11518,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B241" t="n">
         <v>1.6524754286887</v>
@@ -11492,7 +11538,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B242" t="n">
         <v>-1.3475245713113</v>
@@ -11512,7 +11558,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B243" t="n">
         <v>1.17928162520831</v>
@@ -11532,7 +11578,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B244" t="n">
         <v>-0.387924893695415</v>
@@ -11552,7 +11598,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B245" t="n">
         <v>-9.14262398806834</v>
@@ -11572,7 +11618,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B246" t="n">
         <v>-0.142623988068339</v>
@@ -11592,7 +11638,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B247" t="n">
         <v>-3.14262398806834</v>
@@ -11612,7 +11658,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B248" t="n">
         <v>-11.0372472512135</v>
@@ -11632,7 +11678,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B249" t="n">
         <v>-2.03724725121349</v>
@@ -11652,7 +11698,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B250" t="n">
         <v>-5.03724725121349</v>
@@ -11672,7 +11718,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B251" t="n">
         <v>-8.37012933920423</v>
@@ -11692,7 +11738,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B252" t="n">
         <v>0.62987066079577</v>
@@ -11712,7 +11758,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B253" t="n">
         <v>-2.37012933920423</v>
@@ -11732,7 +11778,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B254" t="n">
         <v>-9.38444313617553</v>
@@ -11752,7 +11798,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B255" t="n">
         <v>-0.384443136175533</v>
@@ -11772,7 +11818,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B256" t="n">
         <v>-3.38444313617553</v>
@@ -11792,7 +11838,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B257" t="n">
         <v>-9.67791337129567</v>
@@ -11812,7 +11858,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B258" t="n">
         <v>-0.67791337129567</v>
@@ -11832,7 +11878,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B259" t="n">
         <v>-3.67791337129567</v>
@@ -11852,7 +11898,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B260" t="n">
         <v>-16.0001534369502</v>
@@ -11872,7 +11918,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B261" t="n">
         <v>-7.00015343695019</v>
@@ -11892,7 +11938,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B262" t="n">
         <v>-10.0001534369502</v>
@@ -11912,7 +11958,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B263" t="n">
         <v>-7.06909585835686</v>
@@ -11932,7 +11978,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B264" t="n">
         <v>-10.0522512110379</v>
@@ -11952,7 +11998,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B265" t="n">
         <v>-1.05225121103792</v>
@@ -11972,7 +12018,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B266" t="n">
         <v>-4.05225121103792</v>
@@ -11992,7 +12038,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B267" t="n">
         <v>-5.2136790078794</v>
@@ -12012,7 +12058,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B268" t="n">
         <v>3.7863209921206</v>
@@ -12032,7 +12078,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B269" t="n">
         <v>0.786320992120599</v>
@@ -12052,7 +12098,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B270" t="n">
         <v>1.93090414164314</v>
@@ -12072,7 +12118,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B271" t="n">
         <v>-1.06909585835686</v>
@@ -12092,7 +12138,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B272" t="n">
         <v>-0.574952001204607</v>
@@ -12112,7 +12158,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B273" t="n">
         <v>7.61722797927461</v>
@@ -12132,7 +12178,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B274" t="n">
         <v>0.32572981231456</v>
@@ -13163,7 +13209,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B51" t="n">
         <v>0.0000000191601935462101</v>
@@ -13183,7 +13229,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52" t="n">
         <v>19.1601935462101</v>
@@ -13203,7 +13249,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53" t="n">
         <v>0.0191601935462101</v>
@@ -13223,7 +13269,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B54" t="n">
         <v>0.0000000000000000000121302839875381</v>
@@ -13243,7 +13289,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B55" t="n">
         <v>0.0000000000121302839875381</v>
@@ -13263,7 +13309,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B56" t="n">
         <v>0.0000000000000121302839875381</v>
@@ -13283,7 +13329,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B57" t="n">
         <v>0.000192265249604718</v>
@@ -13303,7 +13349,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B58" t="n">
         <v>192265.249604718</v>
@@ -13323,7 +13369,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B59" t="n">
         <v>192.265249604718</v>
@@ -13343,7 +13389,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B60" t="n">
         <v>0.00242028722185246</v>
@@ -13363,7 +13409,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B61" t="n">
         <v>2420287.22185246</v>
@@ -13383,7 +13429,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B62" t="n">
         <v>2420.28722185246</v>
@@ -13403,7 +13449,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B63" t="n">
         <v>0.000000000000000000018265489104333</v>
@@ -13423,7 +13469,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B64" t="n">
         <v>0.000000000018265489104333</v>
@@ -13443,7 +13489,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B65" t="n">
         <v>0.000000000000018265489104333</v>
@@ -13463,7 +13509,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B66" t="n">
         <v>0.0000475295336787565</v>
@@ -13483,7 +13529,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B67" t="n">
         <v>47529.5336787565</v>
@@ -13503,7 +13549,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B68" t="n">
         <v>47.5295336787565</v>
@@ -13523,7 +13569,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69" t="n">
         <v>0.0000020921220254558</v>
@@ -13543,7 +13589,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B70" t="n">
         <v>2092.1220254558</v>
@@ -13563,7 +13609,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B71" t="n">
         <v>2.0921220254558</v>
@@ -13583,7 +13629,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B72" t="n">
         <v>0.00000938802686528885</v>
@@ -13603,7 +13649,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B73" t="n">
         <v>9388.02686528885</v>
@@ -13623,7 +13669,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B74" t="n">
         <v>9.38802686528885</v>
@@ -13643,7 +13689,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B75" t="n">
         <v>0.00000468321753169171</v>
@@ -13663,7 +13709,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B76" t="n">
         <v>4683.21753169171</v>
@@ -13683,7 +13729,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" t="n">
         <v>4.68321753169171</v>
@@ -13703,7 +13749,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B78" t="n">
         <v>0.000445417616580311</v>
@@ -13723,7 +13769,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B79" t="n">
         <v>445417.616580311</v>
@@ -13743,7 +13789,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B80" t="n">
         <v>445.417616580311</v>
@@ -13763,7 +13809,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B81" t="n">
         <v>0.000316880829015544</v>
@@ -13783,7 +13829,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B82" t="n">
         <v>316880.829015544</v>
@@ -13803,7 +13849,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B83" t="n">
         <v>316.880829015544</v>
@@ -13823,7 +13869,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B84" t="n">
         <v>5.38370466321244</v>
@@ -13843,7 +13889,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B85" t="n">
         <v>0.000119058497409326</v>
@@ -13863,7 +13909,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B86" t="n">
         <v>119058.497409326</v>
@@ -13883,7 +13929,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B87" t="n">
         <v>119.058497409326</v>
@@ -13903,7 +13949,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B88" t="n">
         <v>0.000000000000537252707295292</v>
@@ -13923,7 +13969,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B89" t="n">
         <v>0.000000537252707295292</v>
@@ -13943,7 +13989,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B90" t="n">
         <v>0.000000000537252707295292</v>
@@ -13963,7 +14009,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B91" t="n">
         <v>0.00000683966713250514</v>
@@ -13983,7 +14029,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B92" t="n">
         <v>6839.66713250514</v>
@@ -14003,7 +14049,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B93" t="n">
         <v>6.83966713250514</v>
@@ -14023,7 +14069,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B94" t="n">
         <v>0.000000115337405211828</v>
@@ -14043,7 +14089,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B95" t="n">
         <v>115.337405211828</v>
@@ -14063,7 +14109,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B96" t="n">
         <v>0.115337405211828</v>
@@ -14083,7 +14129,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B97" t="n">
         <v>0.0000000572742419090289</v>
@@ -14103,7 +14149,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B98" t="n">
         <v>57.2742419090289</v>
@@ -14123,7 +14169,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B99" t="n">
         <v>0.0572742419090289</v>
@@ -14143,7 +14189,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B100" t="n">
         <v>0.00000194254525909402</v>
@@ -14163,7 +14209,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B101" t="n">
         <v>1942.54525909402</v>
@@ -14183,7 +14229,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B102" t="n">
         <v>1.94254525909402</v>
@@ -14203,7 +14249,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B103" t="n">
         <v>0.000000259103040616489</v>
@@ -14223,7 +14269,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B104" t="n">
         <v>259.103040616489</v>
@@ -14243,7 +14289,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B105" t="n">
         <v>0.259103040616489</v>
@@ -14263,7 +14309,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B106" t="n">
         <v>0.0000000598360545202948</v>
@@ -14283,7 +14329,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B107" t="n">
         <v>59.8360545202948</v>
@@ -14303,7 +14349,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B108" t="n">
         <v>0.0598360545202948</v>
@@ -14323,7 +14369,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B109" t="n">
         <v>15.9842227979275</v>
@@ -14343,7 +14389,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B110" t="n">
         <v>0.471360103626943</v>
@@ -14363,7 +14409,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B111" t="n">
         <v>0.00000000472724325285158</v>
@@ -14383,7 +14429,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B112" t="n">
         <v>4.72724325285158</v>
@@ -14403,7 +14449,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B113" t="n">
         <v>0.00472724325285158</v>
@@ -14423,7 +14469,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B114" t="n">
         <v>0.0000000000124120397689803</v>
@@ -14443,7 +14489,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B115" t="n">
         <v>0.0124120397689803</v>
@@ -14463,7 +14509,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B116" t="n">
         <v>0.0000124120397689803</v>
@@ -14483,7 +14529,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B117" t="n">
         <v>0.0000000179834043728616</v>
@@ -14503,7 +14549,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B118" t="n">
         <v>17.9834043728616</v>
@@ -14523,7 +14569,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B119" t="n">
         <v>0.0179834043728616</v>
@@ -14543,7 +14589,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B120" t="n">
         <v>0.000000000561063013948023</v>
@@ -14563,7 +14609,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B121" t="n">
         <v>0.561063013948023</v>
@@ -14583,7 +14629,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B122" t="n">
         <v>0.000561063013948023</v>
@@ -14603,7 +14649,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B123" t="n">
         <v>0.000000000230548526359811</v>
@@ -14623,7 +14669,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B124" t="n">
         <v>0.230548526359811</v>
@@ -14643,7 +14689,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B125" t="n">
         <v>0.000230548526359811</v>
@@ -14663,7 +14709,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B126" t="n">
         <v>0.0000000000000000999563616600695</v>
@@ -14683,7 +14729,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B127" t="n">
         <v>0.0000000999563616600695</v>
@@ -14703,7 +14749,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B128" t="n">
         <v>0.0000000000999563616600695</v>
@@ -14723,7 +14769,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B129" t="n">
         <v>0.000000104099137305699</v>
@@ -14743,7 +14789,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B130" t="n">
         <v>0.00000000159866545687253</v>
@@ -14763,7 +14809,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B131" t="n">
         <v>1.59866545687253</v>
@@ -14783,7 +14829,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B132" t="n">
         <v>0.00159866545687253</v>
@@ -14803,7 +14849,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B133" t="n">
         <v>0.0000103839211758947</v>
@@ -14823,7 +14869,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B134" t="n">
         <v>10383.9211758947</v>
@@ -14843,7 +14889,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B135" t="n">
         <v>10.3839211758947</v>
@@ -14863,7 +14909,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B136" t="n">
         <v>104.099137305699</v>
@@ -14883,7 +14929,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B137" t="n">
         <v>0.104099137305699</v>
@@ -14903,7 +14949,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B138" t="n">
         <v>-9.43047625453963</v>
@@ -14923,7 +14969,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B139" t="n">
         <v>-3.43047625453963</v>
@@ -14943,7 +14989,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B140" t="n">
         <v>-0.430476254539628</v>
@@ -14963,7 +15009,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B141" t="n">
         <v>-6.43047625453963</v>
@@ -14983,7 +15029,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B142" t="n">
         <v>-11.3148794599625</v>
@@ -15003,7 +15049,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B143" t="n">
         <v>-5.3148794599625</v>
@@ -15023,7 +15069,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B144" t="n">
         <v>-2.3148794599625</v>
@@ -15043,7 +15089,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B145" t="n">
         <v>-8.3148794599625</v>
@@ -15063,7 +15109,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B146" t="n">
         <v>-10.3580837016221</v>
@@ -15083,7 +15129,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B147" t="n">
         <v>-4.35808370162213</v>
@@ -15103,7 +15149,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B148" t="n">
         <v>-1.35808370162213</v>
@@ -15123,7 +15169,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B149" t="n">
         <v>-7.35808370162213</v>
@@ -15143,7 +15189,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B150" t="n">
         <v>-11.1853448402758</v>
@@ -15163,7 +15209,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B151" t="n">
         <v>-5.18534484027584</v>
@@ -15183,7 +15229,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B152" t="n">
         <v>-2.18534484027584</v>
@@ -15203,7 +15249,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B153" t="n">
         <v>-8.18534484027584</v>
@@ -15223,7 +15269,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B154" t="n">
         <v>-12.8532844067397</v>
@@ -15243,7 +15289,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B155" t="n">
         <v>-6.85328440673965</v>
@@ -15263,7 +15309,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B156" t="n">
         <v>-3.85328440673965</v>
@@ -15283,7 +15329,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B157" t="n">
         <v>-9.85328440673965</v>
@@ -15303,7 +15349,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B158" t="n">
         <v>-12.6727739851647</v>
@@ -15323,7 +15369,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B159" t="n">
         <v>-6.67277398516467</v>
@@ -15343,7 +15389,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B160" t="n">
         <v>-3.67277398516467</v>
@@ -15363,7 +15409,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B161" t="n">
         <v>-9.67277398516467</v>
@@ -15383,7 +15429,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B162" t="n">
         <v>-5.47123491574122</v>
@@ -15403,7 +15449,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B163" t="n">
         <v>3.52876508425878</v>
@@ -15423,7 +15469,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B164" t="n">
         <v>0.528765084258778</v>
@@ -15443,7 +15489,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B165" t="n">
         <v>-4.73183121055391</v>
@@ -15463,7 +15509,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B166" t="n">
         <v>4.26816878944609</v>
@@ -15483,7 +15529,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B167" t="n">
         <v>1.26816878944609</v>
@@ -15503,7 +15549,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B168" t="n">
         <v>-5.1291843939392</v>
@@ -15523,7 +15569,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B169" t="n">
         <v>3.8708156060608</v>
@@ -15543,7 +15589,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B170" t="n">
         <v>0.8708156060608</v>
@@ -15563,7 +15609,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B171" t="n">
         <v>-2.97800662468358</v>
@@ -15583,7 +15629,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B172" t="n">
         <v>6.02199337531642</v>
@@ -15603,7 +15649,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B173" t="n">
         <v>3.02199337531642</v>
@@ -15623,7 +15669,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B174" t="n">
         <v>-3.65101105730638</v>
@@ -15643,7 +15689,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B175" t="n">
         <v>5.34898894269362</v>
@@ -15663,7 +15709,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B176" t="n">
         <v>2.34898894269362</v>
@@ -15683,7 +15729,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B177" t="n">
         <v>-8.03306989879472</v>
@@ -15703,7 +15749,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B178" t="n">
         <v>0.966930101205278</v>
@@ -15723,7 +15769,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B179" t="n">
         <v>-2.03306989879472</v>
@@ -15743,7 +15789,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B180" t="n">
         <v>-2.61618579484238</v>
@@ -15763,7 +15809,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B181" t="n">
         <v>6.38381420515762</v>
@@ -15783,7 +15829,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B182" t="n">
         <v>3.38381420515762</v>
@@ -15803,7 +15849,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B183" t="n">
         <v>-3.8624318393549</v>
@@ -15823,7 +15869,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B184" t="n">
         <v>5.1375681606451</v>
@@ -15843,7 +15889,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B185" t="n">
         <v>2.1375681606451</v>
@@ -15863,7 +15909,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B186" t="n">
         <v>-7.8296777202845</v>
@@ -15883,7 +15929,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B187" t="n">
         <v>1.1703222797155</v>
@@ -15903,7 +15949,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B188" t="n">
         <v>-1.8296777202845</v>
@@ -15923,7 +15969,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B189" t="n">
         <v>-20.674237558062</v>
@@ -15943,7 +15989,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B190" t="n">
         <v>-11.674237558062</v>
@@ -15963,7 +16009,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B191" t="n">
         <v>-14.674237558062</v>
@@ -15983,7 +16029,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B192" t="n">
         <v>-3.90705667964021</v>
@@ -16003,7 +16049,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B193" t="n">
         <v>5.09294332035979</v>
@@ -16023,7 +16069,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B194" t="n">
         <v>2.09294332035979</v>
@@ -16043,7 +16089,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B195" t="n">
         <v>-2.66111647332121</v>
@@ -16063,7 +16109,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B196" t="n">
         <v>6.33888352667879</v>
@@ -16083,7 +16129,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B197" t="n">
         <v>3.33888352667879</v>
@@ -16103,7 +16149,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B198" t="n">
         <v>-20.0248445228654</v>
@@ -16123,7 +16169,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B199" t="n">
         <v>-11.0248445228654</v>
@@ -16143,7 +16189,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B200" t="n">
         <v>-14.0248445228654</v>
@@ -16163,7 +16209,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B201" t="n">
         <v>-4.39006948872305</v>
@@ -16183,7 +16229,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B202" t="n">
         <v>4.60993051127695</v>
@@ -16203,7 +16249,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B203" t="n">
         <v>1.60993051127695</v>
@@ -16223,7 +16269,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B204" t="n">
         <v>-6.10898888729648</v>
@@ -16243,7 +16289,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B205" t="n">
         <v>2.89101111270352</v>
@@ -16263,7 +16309,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B206" t="n">
         <v>-0.108988887296483</v>
@@ -16283,7 +16329,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B207" t="n">
         <v>-5.14453203903624</v>
@@ -16303,7 +16349,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B208" t="n">
         <v>3.85546796096376</v>
@@ -16323,7 +16369,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B209" t="n">
         <v>0.855467960963761</v>
@@ -16343,7 +16389,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B210" t="n">
         <v>-5.5453336356715</v>
@@ -16363,7 +16409,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B211" t="n">
         <v>3.4546663643285</v>
@@ -16383,7 +16429,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B212" t="n">
         <v>0.454666364328496</v>
@@ -16403,7 +16449,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B213" t="n">
         <v>-3.39728011553017</v>
@@ -16423,7 +16469,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B214" t="n">
         <v>5.60271988446983</v>
@@ -16443,7 +16489,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B215" t="n">
         <v>2.60271988446983</v>
@@ -16463,7 +16509,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B216" t="n">
         <v>-3.65525695144415</v>
@@ -16483,7 +16529,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B217" t="n">
         <v>5.34474304855584</v>
@@ -16503,7 +16549,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B218" t="n">
         <v>2.34474304855584</v>
@@ -16523,7 +16569,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B219" t="n">
         <v>-4.08795850644903</v>
@@ -16543,7 +16589,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B220" t="n">
         <v>4.91204149355097</v>
@@ -16563,7 +16609,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B221" t="n">
         <v>1.91204149355097</v>
@@ -16583,7 +16629,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B222" t="n">
         <v>-12.4079053588964</v>
@@ -16603,7 +16649,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B223" t="n">
         <v>-6.40790535889639</v>
@@ -16623,7 +16669,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B224" t="n">
         <v>-9.40790535889639</v>
@@ -16643,7 +16689,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B225" t="n">
         <v>-5.30458917856027</v>
@@ -16663,7 +16709,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B226" t="n">
         <v>3.69541082143973</v>
@@ -16683,7 +16729,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B227" t="n">
         <v>0.695410821439727</v>
@@ -16703,7 +16749,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B228" t="n">
         <v>-7.17699095098957</v>
@@ -16723,7 +16769,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B229" t="n">
         <v>1.82300904901043</v>
@@ -16743,7 +16789,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B230" t="n">
         <v>-1.17699095098957</v>
@@ -16763,7 +16809,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B231" t="n">
         <v>-7.66980963620123</v>
@@ -16783,7 +16829,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B232" t="n">
         <v>1.33019036379877</v>
@@ -16803,7 +16849,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B233" t="n">
         <v>-1.66980963620123</v>
@@ -16823,7 +16869,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B234" t="n">
         <v>-5.81436078399953</v>
@@ -16843,7 +16889,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B235" t="n">
         <v>3.18563921600047</v>
@@ -16863,7 +16909,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B236" t="n">
         <v>0.185639216000467</v>
@@ -16883,7 +16929,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B237" t="n">
         <v>-6.93499001470425</v>
@@ -16903,7 +16949,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B238" t="n">
         <v>2.06500998529575</v>
@@ -16923,7 +16969,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B239" t="n">
         <v>-0.934990014704251</v>
@@ -16943,7 +16989,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B240" t="n">
         <v>-7.35726832169801</v>
@@ -16963,7 +17009,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B241" t="n">
         <v>1.64273167830199</v>
@@ -16983,7 +17029,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B242" t="n">
         <v>-1.35726832169801</v>
@@ -17003,7 +17049,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B243" t="n">
         <v>1.17928162520831</v>
@@ -17023,7 +17069,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B244" t="n">
         <v>-0.387924893695415</v>
@@ -17043,7 +17089,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B245" t="n">
         <v>-8.67962781924752</v>
@@ -17063,7 +17109,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B246" t="n">
         <v>0.320372180752477</v>
@@ -17083,7 +17129,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B247" t="n">
         <v>-2.67962781924752</v>
@@ -17103,7 +17149,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B248" t="n">
         <v>-11.232014783183</v>
@@ -17123,7 +17169,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B249" t="n">
         <v>-2.23201478318303</v>
@@ -17143,7 +17189,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B250" t="n">
         <v>-5.23201478318303</v>
@@ -17163,7 +17209,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B251" t="n">
         <v>-7.90469107790376</v>
@@ -17183,7 +17229,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B252" t="n">
         <v>1.09530892209624</v>
@@ -17203,7 +17249,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B253" t="n">
         <v>-1.90469107790376</v>
@@ -17223,7 +17269,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B254" t="n">
         <v>-9.5763299430752</v>
@@ -17243,7 +17289,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B255" t="n">
         <v>-0.576329943075197</v>
@@ -17263,7 +17309,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B256" t="n">
         <v>-3.5763299430752</v>
@@ -17283,7 +17329,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B257" t="n">
         <v>-9.87793658574158</v>
@@ -17303,7 +17349,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B258" t="n">
         <v>-0.87793658574158</v>
@@ -17323,7 +17369,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B259" t="n">
         <v>-3.87793658574158</v>
@@ -17343,7 +17389,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B260" t="n">
         <v>-16.00018976568</v>
@@ -17363,7 +17409,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B261" t="n">
         <v>-7.00018976568003</v>
@@ -17383,7 +17429,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B262" t="n">
         <v>-10.00018976568</v>
@@ -17403,7 +17449,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B263" t="n">
         <v>-7.06909585835686</v>
@@ -17423,7 +17469,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B264" t="n">
         <v>-10.2465800565038</v>
@@ -17443,7 +17489,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B265" t="n">
         <v>-1.24658005650378</v>
@@ -17463,7 +17509,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B266" t="n">
         <v>-4.24658005650378</v>
@@ -17483,7 +17529,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B267" t="n">
         <v>-5.02570310306523</v>
@@ -17503,7 +17549,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B268" t="n">
         <v>3.97429689693477</v>
@@ -17523,7 +17569,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B269" t="n">
         <v>0.974296896934769</v>
@@ -17543,7 +17589,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B270" t="n">
         <v>1.93090414164314</v>
@@ -17563,7 +17609,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B271" t="n">
         <v>-1.06909585835686</v>
@@ -17583,7 +17629,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B272" t="n">
         <v>-0.760581861927642</v>
@@ -17603,7 +17649,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B273" t="n">
         <v>7.61722797927461</v>
@@ -17623,7 +17669,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B274" t="n">
         <v>0.200069140767506</v>

--- a/Zinc/4. Exploratory data analysis/Summary_stats.xlsx
+++ b/Zinc/4. Exploratory data analysis/Summary_stats.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -430,6 +430,453 @@
     <t xml:space="preserve">Zn_OH_2_uM</t>
   </si>
   <si>
+    <t xml:space="preserve">Zn_acute_tox_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_acute_tox_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_acute_tox_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_chronic_tox_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_chronic_tox_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_chronic_tox_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Ca_mol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Ca_nmol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Ca_nmol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Ca_umol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_H_mol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_H_nmol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_H_nmol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_H_umol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Mg_mol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Mg_nmol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Mg_nmol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Mg_umol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Na_mol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Na_nmol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Na_nmol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Na_umol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_ZnOH_mol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_ZnOH_nmol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_ZnOH_nmol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_ZnOH_umol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Zn_mol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Zn_nmol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Zn_nmol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_BL_Zn_umol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_CaCO3_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_CaCO3_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_CaCO3_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_CaHCO3_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_CaHCO3_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_CaHCO3_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_CaSO4_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_CaSO4_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_CaSO4_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Ca_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Ca_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Ca_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cl_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cl_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cl_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_DIC_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_DIC_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_DIC_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_DOC_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_DOC_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_DOC_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Elevation_m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Free_Zn_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Free_Zn_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Free_Zn_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_H2S_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_H2S_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_H2S_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_H2_CO3_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_H2_CO3_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_H2_CO3_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_HCO3_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_HCO3_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_HCO3_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_HS_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_HS_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_HS_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_K_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_K_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_MgCO3_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_MgCO3_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_MgCO3_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_MgHCO3_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_MgHCO3_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_MgHCO3_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_MgSO4_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_MgSO4_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_MgSO4_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Mg_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Mg_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Mg_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Na_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Na_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Na_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_SO4_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_SO4_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_SO4_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TBL_Zn_mol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TBL_Zn_nmol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TBL_Zn_umol_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Ca_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Ca_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Ca_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_H_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_H_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_H_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_K_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_K_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Mg_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Mg_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Mg_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Na_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Na_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Na_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Zn_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Zn_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_TOrg_Zn_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Temp_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Upstream_from_main_stem_km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnCO3_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnCO3_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnCO3_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnCl_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnCl_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnCl_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnHCO3_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnHCO3_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnHCO3_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnOH_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnOH_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnOH_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnSO4_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnSO4_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnSO4_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnS_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnS_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_ZnS_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_OH_2_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_OH_2_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_OH_2_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_acute_tox_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_acute_tox_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_acute_tox_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_chronic_tox_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_chronic_tox_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_chronic_tox_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_rel_prop_Zn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rel_prop_Zn</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zn_Toxicity_Daphnia_M</t>
   </si>
   <si>
@@ -439,402 +886,6 @@
     <t xml:space="preserve">Zn_Toxicity_Daphnia_uM</t>
   </si>
   <si>
-    <t xml:space="preserve">Zn_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Ca_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Ca_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Ca_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Ca_umol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_H_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_H_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_H_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_H_umol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Mg_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Mg_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Mg_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Mg_umol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Na_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Na_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Na_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Na_umol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_ZnOH_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_ZnOH_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_ZnOH_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_ZnOH_umol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Zn_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Zn_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Zn_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_BL_Zn_umol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_CaCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_CaCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_CaCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_CaHCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_CaHCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_CaHCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_CaSO4_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_CaSO4_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_CaSO4_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Ca_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Ca_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Ca_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cl_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cl_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cl_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cu_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cu_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cu_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DIC_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DIC_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DIC_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DOC_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DOC_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DOC_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Elevation_m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Free_Zn_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Free_Zn_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Free_Zn_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_H2S_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_H2S_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_H2S_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_H2_CO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_H2_CO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_H2_CO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_HCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_HCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_HCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_HS_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_HS_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_HS_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_K_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_K_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_K_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_MgCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_MgCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_MgCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_MgHCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_MgHCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_MgHCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_MgSO4_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_MgSO4_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_MgSO4_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Mg_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Mg_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Mg_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Na_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Na_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Na_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_SO4_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_SO4_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_SO4_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TBL_Zn_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TBL_Zn_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TBL_Zn_umol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Ca_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Ca_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Ca_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_H_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_H_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_H_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_K_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_K_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_K_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Mg_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Mg_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Mg_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Na_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Na_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Na_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Zn_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Zn_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_TOrg_Zn_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Temp_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Upstream_from_main_stem_km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnCl_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnCl_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnCl_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnHCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnHCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnHCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnOH_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnOH_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnOH_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnSO4_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnSO4_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnSO4_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnS_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnS_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_ZnS_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Zn_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Zn_OH_2_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Zn_OH_2_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Zn_OH_2_uM</t>
-  </si>
-  <si>
     <t xml:space="preserve">log_Zn_Toxicity_Daphnia_M</t>
   </si>
   <si>
@@ -842,21 +893,6 @@
   </si>
   <si>
     <t xml:space="preserve">log_Zn_Toxicity_Daphnia_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Zn_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Zn_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_rel_prop_Zn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rel_prop_Zn</t>
   </si>
 </sst>
 </file>
@@ -3850,19 +3886,19 @@
         <v>138</v>
       </c>
       <c r="B134" t="n">
-        <v>0.00000951983439345315</v>
+        <v>0.143622788130137</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0000095306386356242</v>
+        <v>0.139902792870998</v>
       </c>
       <c r="D134" t="n">
-        <v>0.0000152877237269422</v>
+        <v>0.196878671646118</v>
       </c>
       <c r="E134" t="n">
-        <v>0.000000000015045222786518</v>
+        <v>0.00414434096234592</v>
       </c>
       <c r="F134" t="n">
-        <v>0.000000197426596751727</v>
+        <v>0.00327668042651042</v>
       </c>
     </row>
     <row r="135">
@@ -3870,19 +3906,19 @@
         <v>139</v>
       </c>
       <c r="B135" t="n">
-        <v>9519.83439345315</v>
+        <v>143622788.130137</v>
       </c>
       <c r="C135" t="n">
-        <v>9530.6386356242</v>
+        <v>139902792.870999</v>
       </c>
       <c r="D135" t="n">
-        <v>15287.7237269422</v>
+        <v>196878671.646118</v>
       </c>
       <c r="E135" t="n">
-        <v>15045222.786518</v>
+        <v>4144340962345920</v>
       </c>
       <c r="F135" t="n">
-        <v>197.426596751727</v>
+        <v>3276680.42651042</v>
       </c>
     </row>
     <row r="136">
@@ -3890,19 +3926,19 @@
         <v>140</v>
       </c>
       <c r="B136" t="n">
-        <v>9.51983439345315</v>
+        <v>143622.788130137</v>
       </c>
       <c r="C136" t="n">
-        <v>9.5306386356242</v>
+        <v>139902.792870998</v>
       </c>
       <c r="D136" t="n">
-        <v>15.2877237269422</v>
+        <v>196878.671646118</v>
       </c>
       <c r="E136" t="n">
-        <v>15.045222786518</v>
+        <v>4144340962.34592</v>
       </c>
       <c r="F136" t="n">
-        <v>0.197426596751727</v>
+        <v>3276.68042651042</v>
       </c>
     </row>
     <row r="137">
@@ -3910,19 +3946,19 @@
         <v>141</v>
       </c>
       <c r="B137" t="n">
-        <v>104.099137305699</v>
+        <v>0.00000103826486057833</v>
       </c>
       <c r="C137" t="n">
-        <v>81.9</v>
+        <v>0.000000991773674741125</v>
       </c>
       <c r="D137" t="n">
-        <v>104</v>
+        <v>0.00000127666623939149</v>
       </c>
       <c r="E137" t="n">
-        <v>5334.34632790058</v>
+        <v>0.000000000000219061672847588</v>
       </c>
       <c r="F137" t="n">
-        <v>3.71746554419557</v>
+        <v>0.0000000238226213328827</v>
       </c>
     </row>
     <row r="138">
@@ -3930,19 +3966,19 @@
         <v>142</v>
       </c>
       <c r="B138" t="n">
-        <v>0.104099137305699</v>
+        <v>1038.26486057833</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0819</v>
+        <v>991.773674741126</v>
       </c>
       <c r="D138" t="n">
-        <v>0.104</v>
+        <v>1276.66623939149</v>
       </c>
       <c r="E138" t="n">
-        <v>0.00533434632790058</v>
+        <v>219061.672847588</v>
       </c>
       <c r="F138" t="n">
-        <v>0.00371746554419557</v>
+        <v>23.8226213328827</v>
       </c>
     </row>
     <row r="139">
@@ -3950,19 +3986,19 @@
         <v>143</v>
       </c>
       <c r="B139" t="n">
-        <v>-9.43059296294576</v>
+        <v>1.03826486057833</v>
       </c>
       <c r="C139" t="n">
-        <v>-9.40573397758987</v>
+        <v>0.991773674741126</v>
       </c>
       <c r="D139" t="n">
-        <v>-9.38236632295615</v>
+        <v>1.27666623939149</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0100422896872455</v>
+        <v>0.219061672847588</v>
       </c>
       <c r="F139" t="n">
-        <v>0.00510061707311408</v>
+        <v>0.0238226213328827</v>
       </c>
     </row>
     <row r="140">
@@ -3970,19 +4006,19 @@
         <v>144</v>
       </c>
       <c r="B140" t="n">
-        <v>-3.43059296294576</v>
+        <v>104.099137305699</v>
       </c>
       <c r="C140" t="n">
-        <v>-3.40573397758987</v>
+        <v>81.9</v>
       </c>
       <c r="D140" t="n">
-        <v>-3.38236632295615</v>
+        <v>104</v>
       </c>
       <c r="E140" t="n">
-        <v>0.0100422896872455</v>
+        <v>5334.34632790058</v>
       </c>
       <c r="F140" t="n">
-        <v>0.00510061707311408</v>
+        <v>3.71746554419557</v>
       </c>
     </row>
     <row r="141">
@@ -3990,19 +4026,19 @@
         <v>145</v>
       </c>
       <c r="B141" t="n">
-        <v>-0.430592962945761</v>
+        <v>0.104099137305699</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.405733977589867</v>
+        <v>0.0819</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.382366322956154</v>
+        <v>0.104</v>
       </c>
       <c r="E141" t="n">
-        <v>0.0100422896872455</v>
+        <v>0.00533434632790058</v>
       </c>
       <c r="F141" t="n">
-        <v>0.00510061707311408</v>
+        <v>0.00371746554419557</v>
       </c>
     </row>
     <row r="142">
@@ -4010,13 +4046,13 @@
         <v>146</v>
       </c>
       <c r="B142" t="n">
-        <v>-6.43059296294576</v>
+        <v>-9.43059296294576</v>
       </c>
       <c r="C142" t="n">
-        <v>-6.40573397758987</v>
+        <v>-9.40573397758987</v>
       </c>
       <c r="D142" t="n">
-        <v>-6.38236632295615</v>
+        <v>-9.38236632295615</v>
       </c>
       <c r="E142" t="n">
         <v>0.0100422896872455</v>
@@ -4030,19 +4066,19 @@
         <v>147</v>
       </c>
       <c r="B143" t="n">
-        <v>-11.3147477943653</v>
+        <v>-3.43059296294576</v>
       </c>
       <c r="C143" t="n">
-        <v>-11.3367998908763</v>
+        <v>-3.40573397758987</v>
       </c>
       <c r="D143" t="n">
-        <v>-11.0125318054326</v>
+        <v>-3.38236632295615</v>
       </c>
       <c r="E143" t="n">
-        <v>0.224143841170913</v>
+        <v>0.0100422896872455</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0240973759224841</v>
+        <v>0.00510061707311408</v>
       </c>
     </row>
     <row r="144">
@@ -4050,19 +4086,19 @@
         <v>148</v>
       </c>
       <c r="B144" t="n">
-        <v>-5.31474779436532</v>
+        <v>-0.430592962945761</v>
       </c>
       <c r="C144" t="n">
-        <v>-5.33679989087631</v>
+        <v>-0.405733977589867</v>
       </c>
       <c r="D144" t="n">
-        <v>-5.01253180543255</v>
+        <v>-0.382366322956154</v>
       </c>
       <c r="E144" t="n">
-        <v>0.224143841170913</v>
+        <v>0.0100422896872455</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0240973759224841</v>
+        <v>0.00510061707311408</v>
       </c>
     </row>
     <row r="145">
@@ -4070,19 +4106,19 @@
         <v>149</v>
       </c>
       <c r="B145" t="n">
-        <v>-2.31474779436532</v>
+        <v>-6.43059296294576</v>
       </c>
       <c r="C145" t="n">
-        <v>-2.3367998908763</v>
+        <v>-6.40573397758987</v>
       </c>
       <c r="D145" t="n">
-        <v>-2.01253180543255</v>
+        <v>-6.38236632295615</v>
       </c>
       <c r="E145" t="n">
-        <v>0.224143841170913</v>
+        <v>0.0100422896872455</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0240973759224841</v>
+        <v>0.00510061707311408</v>
       </c>
     </row>
     <row r="146">
@@ -4090,13 +4126,13 @@
         <v>150</v>
       </c>
       <c r="B146" t="n">
-        <v>-8.31474779436532</v>
+        <v>-11.3147477943653</v>
       </c>
       <c r="C146" t="n">
-        <v>-8.3367998908763</v>
+        <v>-11.3367998908763</v>
       </c>
       <c r="D146" t="n">
-        <v>-8.01253180543255</v>
+        <v>-11.0125318054326</v>
       </c>
       <c r="E146" t="n">
         <v>0.224143841170913</v>
@@ -4110,19 +4146,19 @@
         <v>151</v>
       </c>
       <c r="B147" t="n">
-        <v>-10.3587555581758</v>
+        <v>-5.31474779436532</v>
       </c>
       <c r="C147" t="n">
-        <v>-10.3262763463401</v>
+        <v>-5.33679989087631</v>
       </c>
       <c r="D147" t="n">
-        <v>-10.4066985203407</v>
+        <v>-5.01253180543255</v>
       </c>
       <c r="E147" t="n">
-        <v>0.025212765909473</v>
+        <v>0.224143841170913</v>
       </c>
       <c r="F147" t="n">
-        <v>0.00808195807942596</v>
+        <v>0.0240973759224841</v>
       </c>
     </row>
     <row r="148">
@@ -4130,19 +4166,19 @@
         <v>152</v>
       </c>
       <c r="B148" t="n">
-        <v>-4.35875555817576</v>
+        <v>-2.31474779436532</v>
       </c>
       <c r="C148" t="n">
-        <v>-4.32627634634009</v>
+        <v>-2.3367998908763</v>
       </c>
       <c r="D148" t="n">
-        <v>-4.40669852034068</v>
+        <v>-2.01253180543255</v>
       </c>
       <c r="E148" t="n">
-        <v>0.025212765909473</v>
+        <v>0.224143841170913</v>
       </c>
       <c r="F148" t="n">
-        <v>0.00808195807942596</v>
+        <v>0.0240973759224841</v>
       </c>
     </row>
     <row r="149">
@@ -4150,19 +4186,19 @@
         <v>153</v>
       </c>
       <c r="B149" t="n">
-        <v>-1.35875555817576</v>
+        <v>-8.31474779436532</v>
       </c>
       <c r="C149" t="n">
-        <v>-1.32627634634009</v>
+        <v>-8.3367998908763</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.40669852034068</v>
+        <v>-8.01253180543255</v>
       </c>
       <c r="E149" t="n">
-        <v>0.025212765909473</v>
+        <v>0.224143841170913</v>
       </c>
       <c r="F149" t="n">
-        <v>0.00808195807942596</v>
+        <v>0.0240973759224841</v>
       </c>
     </row>
     <row r="150">
@@ -4170,13 +4206,13 @@
         <v>154</v>
       </c>
       <c r="B150" t="n">
-        <v>-7.35875555817576</v>
+        <v>-10.3587555581758</v>
       </c>
       <c r="C150" t="n">
-        <v>-7.32627634634009</v>
+        <v>-10.3262763463401</v>
       </c>
       <c r="D150" t="n">
-        <v>-7.40669852034068</v>
+        <v>-10.4066985203407</v>
       </c>
       <c r="E150" t="n">
         <v>0.025212765909473</v>
@@ -4190,19 +4226,19 @@
         <v>155</v>
       </c>
       <c r="B151" t="n">
-        <v>-11.1854661856085</v>
+        <v>-4.35875555817576</v>
       </c>
       <c r="C151" t="n">
-        <v>-11.2210878249715</v>
+        <v>-4.32627634634009</v>
       </c>
       <c r="D151" t="n">
-        <v>-11.3122688673918</v>
+        <v>-4.40669852034068</v>
       </c>
       <c r="E151" t="n">
-        <v>0.103418441379416</v>
+        <v>0.025212765909473</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0163683665422893</v>
+        <v>0.00808195807942596</v>
       </c>
     </row>
     <row r="152">
@@ -4210,19 +4246,19 @@
         <v>156</v>
       </c>
       <c r="B152" t="n">
-        <v>-5.18546618560848</v>
+        <v>-1.35875555817576</v>
       </c>
       <c r="C152" t="n">
-        <v>-5.22108782497146</v>
+        <v>-1.32627634634009</v>
       </c>
       <c r="D152" t="n">
-        <v>-5.31226886739177</v>
+        <v>-1.40669852034068</v>
       </c>
       <c r="E152" t="n">
-        <v>0.103418441379416</v>
+        <v>0.025212765909473</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0163683665422893</v>
+        <v>0.00808195807942596</v>
       </c>
     </row>
     <row r="153">
@@ -4230,19 +4266,19 @@
         <v>157</v>
       </c>
       <c r="B153" t="n">
-        <v>-2.18546618560848</v>
+        <v>-7.35875555817576</v>
       </c>
       <c r="C153" t="n">
-        <v>-2.22108782497146</v>
+        <v>-7.32627634634009</v>
       </c>
       <c r="D153" t="n">
-        <v>-2.31226886739177</v>
+        <v>-7.40669852034068</v>
       </c>
       <c r="E153" t="n">
-        <v>0.103418441379416</v>
+        <v>0.025212765909473</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0163683665422893</v>
+        <v>0.00808195807942596</v>
       </c>
     </row>
     <row r="154">
@@ -4250,13 +4286,13 @@
         <v>158</v>
       </c>
       <c r="B154" t="n">
-        <v>-8.18546618560848</v>
+        <v>-11.1854661856085</v>
       </c>
       <c r="C154" t="n">
-        <v>-8.22108782497146</v>
+        <v>-11.2210878249715</v>
       </c>
       <c r="D154" t="n">
-        <v>-8.31226886739177</v>
+        <v>-11.3122688673918</v>
       </c>
       <c r="E154" t="n">
         <v>0.103418441379416</v>
@@ -4270,19 +4306,19 @@
         <v>159</v>
       </c>
       <c r="B155" t="n">
-        <v>-12.7591658091723</v>
+        <v>-5.18546618560848</v>
       </c>
       <c r="C155" t="n">
-        <v>-12.7489697937181</v>
+        <v>-5.22108782497146</v>
       </c>
       <c r="D155" t="n">
-        <v>-13.4665559096128</v>
+        <v>-5.31226886739177</v>
       </c>
       <c r="E155" t="n">
-        <v>0.160802814870411</v>
+        <v>0.103418441379416</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0204104777820417</v>
+        <v>0.0163683665422893</v>
       </c>
     </row>
     <row r="156">
@@ -4290,19 +4326,19 @@
         <v>160</v>
       </c>
       <c r="B156" t="n">
-        <v>-6.75916580917232</v>
+        <v>-2.18546618560848</v>
       </c>
       <c r="C156" t="n">
-        <v>-6.74896979371813</v>
+        <v>-2.22108782497146</v>
       </c>
       <c r="D156" t="n">
-        <v>-7.46655590961282</v>
+        <v>-2.31226886739177</v>
       </c>
       <c r="E156" t="n">
-        <v>0.160802814870411</v>
+        <v>0.103418441379416</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0204104777820417</v>
+        <v>0.0163683665422893</v>
       </c>
     </row>
     <row r="157">
@@ -4310,19 +4346,19 @@
         <v>161</v>
       </c>
       <c r="B157" t="n">
-        <v>-3.75916580917232</v>
+        <v>-8.18546618560848</v>
       </c>
       <c r="C157" t="n">
-        <v>-3.74896979371813</v>
+        <v>-8.22108782497146</v>
       </c>
       <c r="D157" t="n">
-        <v>-4.46655590961282</v>
+        <v>-8.31226886739177</v>
       </c>
       <c r="E157" t="n">
-        <v>0.160802814870411</v>
+        <v>0.103418441379416</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0204104777820417</v>
+        <v>0.0163683665422893</v>
       </c>
     </row>
     <row r="158">
@@ -4330,13 +4366,13 @@
         <v>162</v>
       </c>
       <c r="B158" t="n">
-        <v>-9.75916580917232</v>
+        <v>-12.7591658091723</v>
       </c>
       <c r="C158" t="n">
-        <v>-9.74896979371813</v>
+        <v>-12.7489697937181</v>
       </c>
       <c r="D158" t="n">
-        <v>-10.4665559096128</v>
+        <v>-13.4665559096128</v>
       </c>
       <c r="E158" t="n">
         <v>0.160802814870411</v>
@@ -4350,19 +4386,19 @@
         <v>163</v>
       </c>
       <c r="B159" t="n">
-        <v>-12.5786572434634</v>
+        <v>-6.75916580917232</v>
       </c>
       <c r="C159" t="n">
-        <v>-12.5836099129991</v>
+        <v>-6.74896979371813</v>
       </c>
       <c r="D159" t="n">
-        <v>-12.8749219750061</v>
+        <v>-7.46655590961282</v>
       </c>
       <c r="E159" t="n">
-        <v>0.113267568618417</v>
+        <v>0.160802814870411</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0171300699630476</v>
+        <v>0.0204104777820417</v>
       </c>
     </row>
     <row r="160">
@@ -4370,19 +4406,19 @@
         <v>164</v>
       </c>
       <c r="B160" t="n">
-        <v>-6.57865724346345</v>
+        <v>-3.75916580917232</v>
       </c>
       <c r="C160" t="n">
-        <v>-6.5836099129991</v>
+        <v>-3.74896979371813</v>
       </c>
       <c r="D160" t="n">
-        <v>-6.87492197500612</v>
+        <v>-4.46655590961282</v>
       </c>
       <c r="E160" t="n">
-        <v>0.113267568618417</v>
+        <v>0.160802814870411</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0171300699630476</v>
+        <v>0.0204104777820417</v>
       </c>
     </row>
     <row r="161">
@@ -4390,19 +4426,19 @@
         <v>165</v>
       </c>
       <c r="B161" t="n">
-        <v>-3.57865724346345</v>
+        <v>-9.75916580917232</v>
       </c>
       <c r="C161" t="n">
-        <v>-3.5836099129991</v>
+        <v>-9.74896979371813</v>
       </c>
       <c r="D161" t="n">
-        <v>-3.87492197500612</v>
+        <v>-10.4665559096128</v>
       </c>
       <c r="E161" t="n">
-        <v>0.113267568618417</v>
+        <v>0.160802814870411</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0171300699630476</v>
+        <v>0.0204104777820417</v>
       </c>
     </row>
     <row r="162">
@@ -4410,13 +4446,13 @@
         <v>166</v>
       </c>
       <c r="B162" t="n">
-        <v>-9.57865724346345</v>
+        <v>-12.5786572434634</v>
       </c>
       <c r="C162" t="n">
-        <v>-9.5836099129991</v>
+        <v>-12.5836099129991</v>
       </c>
       <c r="D162" t="n">
-        <v>-9.87492197500612</v>
+        <v>-12.8749219750061</v>
       </c>
       <c r="E162" t="n">
         <v>0.113267568618417</v>
@@ -4430,19 +4466,19 @@
         <v>167</v>
       </c>
       <c r="B163" t="n">
-        <v>-5.47116687504781</v>
+        <v>-6.57865724346345</v>
       </c>
       <c r="C163" t="n">
-        <v>-5.32643653278655</v>
+        <v>-6.5836099129991</v>
       </c>
       <c r="D163" t="n">
-        <v>-5.49285172058057</v>
+        <v>-6.87492197500612</v>
       </c>
       <c r="E163" t="n">
-        <v>0.510227324658742</v>
+        <v>0.113267568618417</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0363570137291615</v>
+        <v>0.0171300699630476</v>
       </c>
     </row>
     <row r="164">
@@ -4450,19 +4486,19 @@
         <v>168</v>
       </c>
       <c r="B164" t="n">
-        <v>3.52883312495219</v>
+        <v>-3.57865724346345</v>
       </c>
       <c r="C164" t="n">
-        <v>3.67356346721345</v>
+        <v>-3.5836099129991</v>
       </c>
       <c r="D164" t="n">
-        <v>3.50714827941943</v>
+        <v>-3.87492197500612</v>
       </c>
       <c r="E164" t="n">
-        <v>0.510227324658742</v>
+        <v>0.113267568618417</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0363570137291615</v>
+        <v>0.0171300699630476</v>
       </c>
     </row>
     <row r="165">
@@ -4470,19 +4506,19 @@
         <v>169</v>
       </c>
       <c r="B165" t="n">
-        <v>0.528833124952191</v>
+        <v>-9.57865724346345</v>
       </c>
       <c r="C165" t="n">
-        <v>0.673563467213447</v>
+        <v>-9.5836099129991</v>
       </c>
       <c r="D165" t="n">
-        <v>0.507148279419425</v>
+        <v>-9.87492197500612</v>
       </c>
       <c r="E165" t="n">
-        <v>0.510227324658742</v>
+        <v>0.113267568618417</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0363570137291615</v>
+        <v>0.0171300699630476</v>
       </c>
     </row>
     <row r="166">
@@ -4490,19 +4526,19 @@
         <v>170</v>
       </c>
       <c r="B166" t="n">
-        <v>-4.7317683572035</v>
+        <v>-5.47116687504781</v>
       </c>
       <c r="C166" t="n">
-        <v>-4.59133244737573</v>
+        <v>-5.32643653278655</v>
       </c>
       <c r="D166" t="n">
-        <v>-4.34942949380702</v>
+        <v>-5.49285172058057</v>
       </c>
       <c r="E166" t="n">
-        <v>0.222326271322696</v>
+        <v>0.510227324658742</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0239994749145223</v>
+        <v>0.0363570137291615</v>
       </c>
     </row>
     <row r="167">
@@ -4510,19 +4546,19 @@
         <v>171</v>
       </c>
       <c r="B167" t="n">
-        <v>4.2682316427965</v>
+        <v>3.52883312495219</v>
       </c>
       <c r="C167" t="n">
-        <v>4.40866755262427</v>
+        <v>3.67356346721345</v>
       </c>
       <c r="D167" t="n">
-        <v>4.65057050619298</v>
+        <v>3.50714827941943</v>
       </c>
       <c r="E167" t="n">
-        <v>0.222326271322696</v>
+        <v>0.510227324658742</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0239994749145223</v>
+        <v>0.0363570137291615</v>
       </c>
     </row>
     <row r="168">
@@ -4530,19 +4566,19 @@
         <v>172</v>
       </c>
       <c r="B168" t="n">
-        <v>1.2682316427965</v>
+        <v>0.528833124952191</v>
       </c>
       <c r="C168" t="n">
-        <v>1.40866755262427</v>
+        <v>0.673563467213447</v>
       </c>
       <c r="D168" t="n">
-        <v>1.65057050619298</v>
+        <v>0.507148279419425</v>
       </c>
       <c r="E168" t="n">
-        <v>0.222326271322696</v>
+        <v>0.510227324658742</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0239994749145223</v>
+        <v>0.0363570137291615</v>
       </c>
     </row>
     <row r="169">
@@ -4550,19 +4586,19 @@
         <v>173</v>
       </c>
       <c r="B169" t="n">
-        <v>-5.12905010839342</v>
+        <v>-4.7317683572035</v>
       </c>
       <c r="C169" t="n">
-        <v>-5.08857251093765</v>
+        <v>-4.59133244737573</v>
       </c>
       <c r="D169" t="n">
-        <v>-5.33814810751036</v>
+        <v>-4.34942949380702</v>
       </c>
       <c r="E169" t="n">
-        <v>0.277428634864824</v>
+        <v>0.222326271322696</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0268090849028563</v>
+        <v>0.0239994749145223</v>
       </c>
     </row>
     <row r="170">
@@ -4570,19 +4606,19 @@
         <v>174</v>
       </c>
       <c r="B170" t="n">
-        <v>3.87094989160658</v>
+        <v>4.2682316427965</v>
       </c>
       <c r="C170" t="n">
-        <v>3.91142748906236</v>
+        <v>4.40866755262427</v>
       </c>
       <c r="D170" t="n">
-        <v>3.66185189248964</v>
+        <v>4.65057050619298</v>
       </c>
       <c r="E170" t="n">
-        <v>0.277428634864824</v>
+        <v>0.222326271322696</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0268090849028563</v>
+        <v>0.0239994749145223</v>
       </c>
     </row>
     <row r="171">
@@ -4590,19 +4626,19 @@
         <v>175</v>
       </c>
       <c r="B171" t="n">
-        <v>0.870949891606577</v>
+        <v>1.2682316427965</v>
       </c>
       <c r="C171" t="n">
-        <v>0.911427489062355</v>
+        <v>1.40866755262427</v>
       </c>
       <c r="D171" t="n">
-        <v>0.661851892489637</v>
+        <v>1.65057050619298</v>
       </c>
       <c r="E171" t="n">
-        <v>0.277428634864824</v>
+        <v>0.222326271322696</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0268090849028563</v>
+        <v>0.0239994749145223</v>
       </c>
     </row>
     <row r="172">
@@ -4610,19 +4646,19 @@
         <v>176</v>
       </c>
       <c r="B172" t="n">
-        <v>-2.97800662468358</v>
+        <v>-5.12905010839342</v>
       </c>
       <c r="C172" t="n">
-        <v>-2.89980186238729</v>
+        <v>-5.08857251093765</v>
       </c>
       <c r="D172" t="n">
-        <v>-2.80410034759077</v>
+        <v>-5.33814810751036</v>
       </c>
       <c r="E172" t="n">
-        <v>0.0636457667404803</v>
+        <v>0.277428634864824</v>
       </c>
       <c r="F172" t="n">
-        <v>0.0128407712409894</v>
+        <v>0.0268090849028563</v>
       </c>
     </row>
     <row r="173">
@@ -4630,19 +4666,19 @@
         <v>177</v>
       </c>
       <c r="B173" t="n">
-        <v>6.02199337531642</v>
+        <v>3.87094989160658</v>
       </c>
       <c r="C173" t="n">
-        <v>6.10019813761271</v>
+        <v>3.91142748906236</v>
       </c>
       <c r="D173" t="n">
-        <v>6.19589965240923</v>
+        <v>3.66185189248964</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0636457667404803</v>
+        <v>0.277428634864824</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0128407712409894</v>
+        <v>0.0268090849028563</v>
       </c>
     </row>
     <row r="174">
@@ -4650,19 +4686,19 @@
         <v>178</v>
       </c>
       <c r="B174" t="n">
-        <v>3.02199337531642</v>
+        <v>0.870949891606577</v>
       </c>
       <c r="C174" t="n">
-        <v>3.10019813761271</v>
+        <v>0.911427489062355</v>
       </c>
       <c r="D174" t="n">
-        <v>3.19589965240923</v>
+        <v>0.661851892489637</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0636457667404803</v>
+        <v>0.277428634864824</v>
       </c>
       <c r="F174" t="n">
-        <v>0.0128407712409894</v>
+        <v>0.0268090849028563</v>
       </c>
     </row>
     <row r="175">
@@ -4670,19 +4706,19 @@
         <v>179</v>
       </c>
       <c r="B175" t="n">
-        <v>-3.65101105730638</v>
+        <v>-2.97800662468358</v>
       </c>
       <c r="C175" t="n">
-        <v>-3.63171411078192</v>
+        <v>-2.89980186238729</v>
       </c>
       <c r="D175" t="n">
-        <v>-4.09691001300806</v>
+        <v>-2.80410034759077</v>
       </c>
       <c r="E175" t="n">
-        <v>0.168805445928065</v>
+        <v>0.0636457667404803</v>
       </c>
       <c r="F175" t="n">
-        <v>0.02091219280955</v>
+        <v>0.0128407712409894</v>
       </c>
     </row>
     <row r="176">
@@ -4690,19 +4726,19 @@
         <v>180</v>
       </c>
       <c r="B176" t="n">
-        <v>5.34898894269362</v>
+        <v>6.02199337531642</v>
       </c>
       <c r="C176" t="n">
-        <v>5.36828588921808</v>
+        <v>6.10019813761271</v>
       </c>
       <c r="D176" t="n">
-        <v>4.90308998699194</v>
+        <v>6.19589965240923</v>
       </c>
       <c r="E176" t="n">
-        <v>0.168805445928065</v>
+        <v>0.0636457667404803</v>
       </c>
       <c r="F176" t="n">
-        <v>0.02091219280955</v>
+        <v>0.0128407712409894</v>
       </c>
     </row>
     <row r="177">
@@ -4710,19 +4746,19 @@
         <v>181</v>
       </c>
       <c r="B177" t="n">
-        <v>2.34898894269362</v>
+        <v>3.02199337531642</v>
       </c>
       <c r="C177" t="n">
-        <v>2.36828588921808</v>
+        <v>3.10019813761271</v>
       </c>
       <c r="D177" t="n">
-        <v>1.90308998699194</v>
+        <v>3.19589965240923</v>
       </c>
       <c r="E177" t="n">
-        <v>0.168805445928065</v>
+        <v>0.0636457667404803</v>
       </c>
       <c r="F177" t="n">
-        <v>0.02091219280955</v>
+        <v>0.0128407712409894</v>
       </c>
     </row>
     <row r="178">
@@ -4730,19 +4766,19 @@
         <v>182</v>
       </c>
       <c r="B178" t="n">
-        <v>-8.03306989879472</v>
+        <v>-3.65101105730638</v>
       </c>
       <c r="C178" t="n">
-        <v>-8.04674547598485</v>
+        <v>-3.63171411078192</v>
       </c>
       <c r="D178" t="n">
-        <v>-9.82681373158773</v>
+        <v>-4.09691001300806</v>
       </c>
       <c r="E178" t="n">
-        <v>0.398079352298723</v>
+        <v>0.168805445928065</v>
       </c>
       <c r="F178" t="n">
-        <v>0.03211376120614</v>
+        <v>0.02091219280955</v>
       </c>
     </row>
     <row r="179">
@@ -4750,19 +4786,19 @@
         <v>183</v>
       </c>
       <c r="B179" t="n">
-        <v>0.966930101205278</v>
+        <v>5.34898894269362</v>
       </c>
       <c r="C179" t="n">
-        <v>0.953254524015154</v>
+        <v>5.36828588921808</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.826813731587726</v>
+        <v>4.90308998699194</v>
       </c>
       <c r="E179" t="n">
-        <v>0.398079352298723</v>
+        <v>0.168805445928065</v>
       </c>
       <c r="F179" t="n">
-        <v>0.03211376120614</v>
+        <v>0.02091219280955</v>
       </c>
     </row>
     <row r="180">
@@ -4770,19 +4806,19 @@
         <v>184</v>
       </c>
       <c r="B180" t="n">
-        <v>-2.03306989879472</v>
+        <v>2.34898894269362</v>
       </c>
       <c r="C180" t="n">
-        <v>-2.04674547598485</v>
+        <v>2.36828588921808</v>
       </c>
       <c r="D180" t="n">
-        <v>-3.82681373158773</v>
+        <v>1.90308998699194</v>
       </c>
       <c r="E180" t="n">
-        <v>0.398079352298723</v>
+        <v>0.168805445928065</v>
       </c>
       <c r="F180" t="n">
-        <v>0.03211376120614</v>
+        <v>0.02091219280955</v>
       </c>
     </row>
     <row r="181">
@@ -4790,19 +4826,19 @@
         <v>185</v>
       </c>
       <c r="B181" t="n">
-        <v>-2.61618579484238</v>
+        <v>-8.03306989879472</v>
       </c>
       <c r="C181" t="n">
-        <v>-2.548904695166</v>
+        <v>-8.04674547598485</v>
       </c>
       <c r="D181" t="n">
-        <v>-2.7476324855401</v>
+        <v>-9.82681373158773</v>
       </c>
       <c r="E181" t="n">
-        <v>0.0551253767470059</v>
+        <v>0.398079352298723</v>
       </c>
       <c r="F181" t="n">
-        <v>0.0119503914939021</v>
+        <v>0.03211376120614</v>
       </c>
     </row>
     <row r="182">
@@ -4810,19 +4846,19 @@
         <v>186</v>
       </c>
       <c r="B182" t="n">
-        <v>6.38381420515762</v>
+        <v>0.966930101205278</v>
       </c>
       <c r="C182" t="n">
-        <v>6.451095304834</v>
+        <v>0.953254524015154</v>
       </c>
       <c r="D182" t="n">
-        <v>6.2523675144599</v>
+        <v>-0.826813731587726</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0551253767470059</v>
+        <v>0.398079352298723</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0119503914939021</v>
+        <v>0.03211376120614</v>
       </c>
     </row>
     <row r="183">
@@ -4830,19 +4866,19 @@
         <v>187</v>
       </c>
       <c r="B183" t="n">
-        <v>3.38381420515762</v>
+        <v>-2.03306989879472</v>
       </c>
       <c r="C183" t="n">
-        <v>3.451095304834</v>
+        <v>-2.04674547598485</v>
       </c>
       <c r="D183" t="n">
-        <v>3.2523675144599</v>
+        <v>-3.82681373158773</v>
       </c>
       <c r="E183" t="n">
-        <v>0.0551253767470059</v>
+        <v>0.398079352298723</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0119503914939021</v>
+        <v>0.03211376120614</v>
       </c>
     </row>
     <row r="184">
@@ -4850,19 +4886,19 @@
         <v>188</v>
       </c>
       <c r="B184" t="n">
-        <v>-3.8624318393549</v>
+        <v>-2.61618579484238</v>
       </c>
       <c r="C184" t="n">
-        <v>-3.85787816076663</v>
+        <v>-2.548904695166</v>
       </c>
       <c r="D184" t="n">
-        <v>-4.04575749056067</v>
+        <v>-2.7476324855401</v>
       </c>
       <c r="E184" t="n">
-        <v>0.110421154906443</v>
+        <v>0.0551253767470059</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0169134611523309</v>
+        <v>0.0119503914939021</v>
       </c>
     </row>
     <row r="185">
@@ -4870,19 +4906,19 @@
         <v>189</v>
       </c>
       <c r="B185" t="n">
-        <v>5.1375681606451</v>
+        <v>6.38381420515762</v>
       </c>
       <c r="C185" t="n">
-        <v>5.14212183923337</v>
+        <v>6.451095304834</v>
       </c>
       <c r="D185" t="n">
-        <v>4.95424250943933</v>
+        <v>6.2523675144599</v>
       </c>
       <c r="E185" t="n">
-        <v>0.110421154906443</v>
+        <v>0.0551253767470059</v>
       </c>
       <c r="F185" t="n">
-        <v>0.0169134611523309</v>
+        <v>0.0119503914939021</v>
       </c>
     </row>
     <row r="186">
@@ -4890,19 +4926,19 @@
         <v>190</v>
       </c>
       <c r="B186" t="n">
-        <v>2.1375681606451</v>
+        <v>3.38381420515762</v>
       </c>
       <c r="C186" t="n">
-        <v>2.14212183923337</v>
+        <v>3.451095304834</v>
       </c>
       <c r="D186" t="n">
-        <v>1.95424250943932</v>
+        <v>3.2523675144599</v>
       </c>
       <c r="E186" t="n">
-        <v>0.110421154906443</v>
+        <v>0.0551253767470059</v>
       </c>
       <c r="F186" t="n">
-        <v>0.0169134611523309</v>
+        <v>0.0119503914939021</v>
       </c>
     </row>
     <row r="187">
@@ -4910,19 +4946,19 @@
         <v>191</v>
       </c>
       <c r="B187" t="n">
-        <v>2.40243371083576</v>
+        <v>-3.8624318393549</v>
       </c>
       <c r="C187" t="n">
-        <v>2.41000071254346</v>
+        <v>-3.85787816076663</v>
       </c>
       <c r="D187" t="n">
-        <v>2.41193941752404</v>
+        <v>-4.04575749056067</v>
       </c>
       <c r="E187" t="n">
-        <v>0.000593447964128563</v>
+        <v>0.110421154906443</v>
       </c>
       <c r="F187" t="n">
-        <v>0.00123993143313745</v>
+        <v>0.0169134611523309</v>
       </c>
     </row>
     <row r="188">
@@ -4930,19 +4966,19 @@
         <v>192</v>
       </c>
       <c r="B188" t="n">
-        <v>-7.73570776825048</v>
+        <v>5.1375681606451</v>
       </c>
       <c r="C188" t="n">
-        <v>-7.69289664098812</v>
+        <v>5.14212183923337</v>
       </c>
       <c r="D188" t="n">
-        <v>-7.92346057232192</v>
+        <v>4.95424250943933</v>
       </c>
       <c r="E188" t="n">
-        <v>0.106046238137458</v>
+        <v>0.110421154906443</v>
       </c>
       <c r="F188" t="n">
-        <v>0.0165750169497532</v>
+        <v>0.0169134611523309</v>
       </c>
     </row>
     <row r="189">
@@ -4950,19 +4986,19 @@
         <v>193</v>
       </c>
       <c r="B189" t="n">
-        <v>1.26429223174952</v>
+        <v>2.1375681606451</v>
       </c>
       <c r="C189" t="n">
-        <v>1.30710335901188</v>
+        <v>2.14212183923337</v>
       </c>
       <c r="D189" t="n">
-        <v>1.07653942767808</v>
+        <v>1.95424250943932</v>
       </c>
       <c r="E189" t="n">
-        <v>0.106046238137458</v>
+        <v>0.110421154906443</v>
       </c>
       <c r="F189" t="n">
-        <v>0.0165750169497532</v>
+        <v>0.0169134611523309</v>
       </c>
     </row>
     <row r="190">
@@ -4970,19 +5006,19 @@
         <v>194</v>
       </c>
       <c r="B190" t="n">
-        <v>-1.73570776825048</v>
+        <v>2.40243371083576</v>
       </c>
       <c r="C190" t="n">
-        <v>-1.69289664098812</v>
+        <v>2.41000071254346</v>
       </c>
       <c r="D190" t="n">
-        <v>-1.92346057232192</v>
+        <v>2.41193941752404</v>
       </c>
       <c r="E190" t="n">
-        <v>0.106046238137458</v>
+        <v>0.000593447964128563</v>
       </c>
       <c r="F190" t="n">
-        <v>0.0165750169497532</v>
+        <v>0.00123993143313745</v>
       </c>
     </row>
     <row r="191">
@@ -4990,19 +5026,19 @@
         <v>195</v>
       </c>
       <c r="B191" t="n">
-        <v>-20.7682049211339</v>
+        <v>-7.73570776825048</v>
       </c>
       <c r="C191" t="n">
-        <v>-20.8011932449567</v>
+        <v>-7.69289664098812</v>
       </c>
       <c r="D191" t="n">
-        <v>-19.7525138877493</v>
+        <v>-7.92346057232192</v>
       </c>
       <c r="E191" t="n">
-        <v>0.601927056426142</v>
+        <v>0.106046238137458</v>
       </c>
       <c r="F191" t="n">
-        <v>0.0394891949682278</v>
+        <v>0.0165750169497532</v>
       </c>
     </row>
     <row r="192">
@@ -5010,19 +5046,19 @@
         <v>196</v>
       </c>
       <c r="B192" t="n">
-        <v>-11.7682049211339</v>
+        <v>1.26429223174952</v>
       </c>
       <c r="C192" t="n">
-        <v>-11.8011932449567</v>
+        <v>1.30710335901188</v>
       </c>
       <c r="D192" t="n">
-        <v>-10.7525138877493</v>
+        <v>1.07653942767808</v>
       </c>
       <c r="E192" t="n">
-        <v>0.601927056426142</v>
+        <v>0.106046238137458</v>
       </c>
       <c r="F192" t="n">
-        <v>0.0394891949682278</v>
+        <v>0.0165750169497532</v>
       </c>
     </row>
     <row r="193">
@@ -5030,19 +5066,19 @@
         <v>197</v>
       </c>
       <c r="B193" t="n">
-        <v>-14.7682049211339</v>
+        <v>-1.73570776825048</v>
       </c>
       <c r="C193" t="n">
-        <v>-14.8011932449567</v>
+        <v>-1.69289664098812</v>
       </c>
       <c r="D193" t="n">
-        <v>-13.7525138877493</v>
+        <v>-1.92346057232192</v>
       </c>
       <c r="E193" t="n">
-        <v>0.601927056426142</v>
+        <v>0.106046238137458</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0394891949682278</v>
+        <v>0.0165750169497532</v>
       </c>
     </row>
     <row r="194">
@@ -5050,19 +5086,19 @@
         <v>198</v>
       </c>
       <c r="B194" t="n">
-        <v>-3.90674347613252</v>
+        <v>-20.7682049211339</v>
       </c>
       <c r="C194" t="n">
-        <v>-3.90782402744313</v>
+        <v>-20.8011932449567</v>
       </c>
       <c r="D194" t="n">
-        <v>-3.2718381944557</v>
+        <v>-19.7525138877493</v>
       </c>
       <c r="E194" t="n">
-        <v>0.187490333801313</v>
+        <v>0.601927056426142</v>
       </c>
       <c r="F194" t="n">
-        <v>0.022039198110895</v>
+        <v>0.0394891949682278</v>
       </c>
     </row>
     <row r="195">
@@ -5070,19 +5106,19 @@
         <v>199</v>
       </c>
       <c r="B195" t="n">
-        <v>5.09325652386748</v>
+        <v>-11.7682049211339</v>
       </c>
       <c r="C195" t="n">
-        <v>5.09217597255687</v>
+        <v>-11.8011932449567</v>
       </c>
       <c r="D195" t="n">
-        <v>5.7281618055443</v>
+        <v>-10.7525138877493</v>
       </c>
       <c r="E195" t="n">
-        <v>0.187490333801313</v>
+        <v>0.601927056426142</v>
       </c>
       <c r="F195" t="n">
-        <v>0.022039198110895</v>
+        <v>0.0394891949682278</v>
       </c>
     </row>
     <row r="196">
@@ -5090,19 +5126,19 @@
         <v>200</v>
       </c>
       <c r="B196" t="n">
-        <v>2.09325652386748</v>
+        <v>-14.7682049211339</v>
       </c>
       <c r="C196" t="n">
-        <v>2.09217597255687</v>
+        <v>-14.8011932449567</v>
       </c>
       <c r="D196" t="n">
-        <v>2.7281618055443</v>
+        <v>-13.7525138877493</v>
       </c>
       <c r="E196" t="n">
-        <v>0.187490333801313</v>
+        <v>0.601927056426142</v>
       </c>
       <c r="F196" t="n">
-        <v>0.022039198110895</v>
+        <v>0.0394891949682278</v>
       </c>
     </row>
     <row r="197">
@@ -5110,19 +5146,19 @@
         <v>201</v>
       </c>
       <c r="B197" t="n">
-        <v>-2.66080843995655</v>
+        <v>-3.90674347613252</v>
       </c>
       <c r="C197" t="n">
-        <v>-2.58714205175729</v>
+        <v>-3.90782402744313</v>
       </c>
       <c r="D197" t="n">
-        <v>-2.42588367715264</v>
+        <v>-3.2718381944557</v>
       </c>
       <c r="E197" t="n">
-        <v>0.0619243957654582</v>
+        <v>0.187490333801313</v>
       </c>
       <c r="F197" t="n">
-        <v>0.0126659344608061</v>
+        <v>0.022039198110895</v>
       </c>
     </row>
     <row r="198">
@@ -5130,19 +5166,19 @@
         <v>202</v>
       </c>
       <c r="B198" t="n">
-        <v>6.33919156004345</v>
+        <v>5.09325652386748</v>
       </c>
       <c r="C198" t="n">
-        <v>6.41285794824271</v>
+        <v>5.09217597255687</v>
       </c>
       <c r="D198" t="n">
-        <v>6.57411632284736</v>
+        <v>5.7281618055443</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0619243957654582</v>
+        <v>0.187490333801313</v>
       </c>
       <c r="F198" t="n">
-        <v>0.0126659344608061</v>
+        <v>0.022039198110895</v>
       </c>
     </row>
     <row r="199">
@@ -5150,19 +5186,19 @@
         <v>203</v>
       </c>
       <c r="B199" t="n">
-        <v>3.33919156004345</v>
+        <v>2.09325652386748</v>
       </c>
       <c r="C199" t="n">
-        <v>3.41285794824271</v>
+        <v>2.09217597255687</v>
       </c>
       <c r="D199" t="n">
-        <v>3.57411632284736</v>
+        <v>2.7281618055443</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0619243957654582</v>
+        <v>0.187490333801313</v>
       </c>
       <c r="F199" t="n">
-        <v>0.0126659344608061</v>
+        <v>0.022039198110895</v>
       </c>
     </row>
     <row r="200">
@@ -5170,19 +5206,19 @@
         <v>204</v>
       </c>
       <c r="B200" t="n">
-        <v>-20.1188170925329</v>
+        <v>-2.66080843995655</v>
       </c>
       <c r="C200" t="n">
-        <v>-20.1167325309577</v>
+        <v>-2.58714205175729</v>
       </c>
       <c r="D200" t="n">
-        <v>-19.5065569081015</v>
+        <v>-2.42588367715264</v>
       </c>
       <c r="E200" t="n">
-        <v>0.166143193931006</v>
+        <v>0.0619243957654582</v>
       </c>
       <c r="F200" t="n">
-        <v>0.020746633032969</v>
+        <v>0.0126659344608061</v>
       </c>
     </row>
     <row r="201">
@@ -5190,19 +5226,19 @@
         <v>205</v>
       </c>
       <c r="B201" t="n">
-        <v>-11.1188170925328</v>
+        <v>6.33919156004345</v>
       </c>
       <c r="C201" t="n">
-        <v>-11.1167325309577</v>
+        <v>6.41285794824271</v>
       </c>
       <c r="D201" t="n">
-        <v>-10.5065569081015</v>
+        <v>6.57411632284736</v>
       </c>
       <c r="E201" t="n">
-        <v>0.166143193931006</v>
+        <v>0.0619243957654582</v>
       </c>
       <c r="F201" t="n">
-        <v>0.020746633032969</v>
+        <v>0.0126659344608061</v>
       </c>
     </row>
     <row r="202">
@@ -5210,19 +5246,19 @@
         <v>206</v>
       </c>
       <c r="B202" t="n">
-        <v>-14.1188170925328</v>
+        <v>3.33919156004345</v>
       </c>
       <c r="C202" t="n">
-        <v>-14.1167325309577</v>
+        <v>3.41285794824271</v>
       </c>
       <c r="D202" t="n">
-        <v>-13.5065569081015</v>
+        <v>3.57411632284736</v>
       </c>
       <c r="E202" t="n">
-        <v>0.166143193931006</v>
+        <v>0.0619243957654582</v>
       </c>
       <c r="F202" t="n">
-        <v>0.020746633032969</v>
+        <v>0.0126659344608061</v>
       </c>
     </row>
     <row r="203">
@@ -5230,19 +5266,19 @@
         <v>207</v>
       </c>
       <c r="B203" t="n">
-        <v>-4.39006948872305</v>
+        <v>-20.1188170925329</v>
       </c>
       <c r="C203" t="n">
-        <v>-4.41060933654004</v>
+        <v>-20.1167325309577</v>
       </c>
       <c r="D203" t="n">
-        <v>-4.50445566245355</v>
+        <v>-19.5065569081015</v>
       </c>
       <c r="E203" t="n">
-        <v>0.0538188903134248</v>
+        <v>0.166143193931006</v>
       </c>
       <c r="F203" t="n">
-        <v>0.0118079285642226</v>
+        <v>0.020746633032969</v>
       </c>
     </row>
     <row r="204">
@@ -5250,19 +5286,19 @@
         <v>208</v>
       </c>
       <c r="B204" t="n">
-        <v>4.60993051127695</v>
+        <v>-11.1188170925328</v>
       </c>
       <c r="C204" t="n">
-        <v>4.58939066345996</v>
+        <v>-11.1167325309577</v>
       </c>
       <c r="D204" t="n">
-        <v>4.49554433754645</v>
+        <v>-10.5065569081015</v>
       </c>
       <c r="E204" t="n">
-        <v>0.0538188903134248</v>
+        <v>0.166143193931006</v>
       </c>
       <c r="F204" t="n">
-        <v>0.0118079285642226</v>
+        <v>0.020746633032969</v>
       </c>
     </row>
     <row r="205">
@@ -5270,19 +5306,19 @@
         <v>209</v>
       </c>
       <c r="B205" t="n">
-        <v>1.60993051127695</v>
+        <v>-14.1188170925328</v>
       </c>
       <c r="C205" t="n">
-        <v>1.58939066345996</v>
+        <v>-14.1167325309577</v>
       </c>
       <c r="D205" t="n">
-        <v>1.49554433754645</v>
+        <v>-13.5065569081015</v>
       </c>
       <c r="E205" t="n">
-        <v>0.0538188903134248</v>
+        <v>0.166143193931006</v>
       </c>
       <c r="F205" t="n">
-        <v>0.0118079285642226</v>
+        <v>0.020746633032969</v>
       </c>
     </row>
     <row r="206">
@@ -5290,19 +5326,19 @@
         <v>210</v>
       </c>
       <c r="B206" t="n">
-        <v>-6.10947601277406</v>
+        <v>-4.39006948872305</v>
       </c>
       <c r="C206" t="n">
-        <v>-5.99298665727373</v>
+        <v>-4.41060933654004</v>
       </c>
       <c r="D206" t="n">
-        <v>-6.22866104335667</v>
+        <v>-4.50445566245355</v>
       </c>
       <c r="E206" t="n">
-        <v>0.488514856018307</v>
+        <v>0.0538188903134248</v>
       </c>
       <c r="F206" t="n">
-        <v>0.0355750267539581</v>
+        <v>0.0118079285642226</v>
       </c>
     </row>
     <row r="207">
@@ -5310,19 +5346,19 @@
         <v>211</v>
       </c>
       <c r="B207" t="n">
-        <v>2.89052398722594</v>
+        <v>4.60993051127695</v>
       </c>
       <c r="C207" t="n">
-        <v>3.00701334272627</v>
+        <v>4.58939066345996</v>
       </c>
       <c r="D207" t="n">
-        <v>2.77133895664333</v>
+        <v>4.49554433754645</v>
       </c>
       <c r="E207" t="n">
-        <v>0.488514856018307</v>
+        <v>0.0538188903134248</v>
       </c>
       <c r="F207" t="n">
-        <v>0.0355750267539581</v>
+        <v>0.0118079285642226</v>
       </c>
     </row>
     <row r="208">
@@ -5330,19 +5366,19 @@
         <v>212</v>
       </c>
       <c r="B208" t="n">
-        <v>-0.109476012774064</v>
+        <v>1.60993051127695</v>
       </c>
       <c r="C208" t="n">
-        <v>0.00701334272626688</v>
+        <v>1.58939066345996</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.228661043356668</v>
+        <v>1.49554433754645</v>
       </c>
       <c r="E208" t="n">
-        <v>0.488514856018307</v>
+        <v>0.0538188903134248</v>
       </c>
       <c r="F208" t="n">
-        <v>0.0355750267539581</v>
+        <v>0.0118079285642226</v>
       </c>
     </row>
     <row r="209">
@@ -5350,19 +5386,19 @@
         <v>213</v>
       </c>
       <c r="B209" t="n">
-        <v>-5.1450243336338</v>
+        <v>-6.10947601277406</v>
       </c>
       <c r="C209" t="n">
-        <v>-5.01730582536857</v>
+        <v>-5.99298665727373</v>
       </c>
       <c r="D209" t="n">
-        <v>-4.8618644610268</v>
+        <v>-6.22866104335667</v>
       </c>
       <c r="E209" t="n">
-        <v>0.193593563969</v>
+        <v>0.488514856018307</v>
       </c>
       <c r="F209" t="n">
-        <v>0.0223950380774322</v>
+        <v>0.0355750267539581</v>
       </c>
     </row>
     <row r="210">
@@ -5370,19 +5406,19 @@
         <v>214</v>
       </c>
       <c r="B210" t="n">
-        <v>3.8549756663662</v>
+        <v>2.89052398722594</v>
       </c>
       <c r="C210" t="n">
-        <v>3.98269417463143</v>
+        <v>3.00701334272627</v>
       </c>
       <c r="D210" t="n">
-        <v>4.1381355389732</v>
+        <v>2.77133895664333</v>
       </c>
       <c r="E210" t="n">
-        <v>0.193593563969</v>
+        <v>0.488514856018307</v>
       </c>
       <c r="F210" t="n">
-        <v>0.0223950380774322</v>
+        <v>0.0355750267539581</v>
       </c>
     </row>
     <row r="211">
@@ -5390,19 +5426,19 @@
         <v>215</v>
       </c>
       <c r="B211" t="n">
-        <v>0.854975666366198</v>
+        <v>-0.109476012774064</v>
       </c>
       <c r="C211" t="n">
-        <v>0.982694174631431</v>
+        <v>0.00701334272626688</v>
       </c>
       <c r="D211" t="n">
-        <v>1.1381355389732</v>
+        <v>-0.228661043356668</v>
       </c>
       <c r="E211" t="n">
-        <v>0.193593563969</v>
+        <v>0.488514856018307</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0223950380774322</v>
+        <v>0.0355750267539581</v>
       </c>
     </row>
     <row r="212">
@@ -5410,19 +5446,19 @@
         <v>216</v>
       </c>
       <c r="B212" t="n">
-        <v>-5.5457545264097</v>
+        <v>-5.1450243336338</v>
       </c>
       <c r="C212" t="n">
-        <v>-5.55844020097594</v>
+        <v>-5.01730582536857</v>
       </c>
       <c r="D212" t="n">
-        <v>-5.84642793285626</v>
+        <v>-4.8618644610268</v>
       </c>
       <c r="E212" t="n">
-        <v>0.229476192036779</v>
+        <v>0.193593563969</v>
       </c>
       <c r="F212" t="n">
-        <v>0.0243823277566157</v>
+        <v>0.0223950380774322</v>
       </c>
     </row>
     <row r="213">
@@ -5430,19 +5466,19 @@
         <v>217</v>
       </c>
       <c r="B213" t="n">
-        <v>3.4542454735903</v>
+        <v>3.8549756663662</v>
       </c>
       <c r="C213" t="n">
-        <v>3.44155979902406</v>
+        <v>3.98269417463143</v>
       </c>
       <c r="D213" t="n">
-        <v>3.15357206714374</v>
+        <v>4.1381355389732</v>
       </c>
       <c r="E213" t="n">
-        <v>0.229476192036779</v>
+        <v>0.193593563969</v>
       </c>
       <c r="F213" t="n">
-        <v>0.0243823277566157</v>
+        <v>0.0223950380774322</v>
       </c>
     </row>
     <row r="214">
@@ -5450,19 +5486,19 @@
         <v>218</v>
       </c>
       <c r="B214" t="n">
-        <v>0.454245473590296</v>
+        <v>0.854975666366198</v>
       </c>
       <c r="C214" t="n">
-        <v>0.441559799024056</v>
+        <v>0.982694174631431</v>
       </c>
       <c r="D214" t="n">
-        <v>0.153572067143742</v>
+        <v>1.1381355389732</v>
       </c>
       <c r="E214" t="n">
-        <v>0.229476192036779</v>
+        <v>0.193593563969</v>
       </c>
       <c r="F214" t="n">
-        <v>0.0243823277566157</v>
+        <v>0.0223950380774322</v>
       </c>
     </row>
     <row r="215">
@@ -5470,19 +5506,19 @@
         <v>219</v>
       </c>
       <c r="B215" t="n">
-        <v>-3.39728011553017</v>
+        <v>-5.5457545264097</v>
       </c>
       <c r="C215" t="n">
-        <v>-3.3292906521054</v>
+        <v>-5.55844020097594</v>
       </c>
       <c r="D215" t="n">
-        <v>-3.26360349772336</v>
+        <v>-5.84642793285626</v>
       </c>
       <c r="E215" t="n">
-        <v>0.0547684708105518</v>
+        <v>0.229476192036779</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0119116426272429</v>
+        <v>0.0243823277566157</v>
       </c>
     </row>
     <row r="216">
@@ -5490,19 +5526,19 @@
         <v>220</v>
       </c>
       <c r="B216" t="n">
-        <v>5.60271988446983</v>
+        <v>3.4542454735903</v>
       </c>
       <c r="C216" t="n">
-        <v>5.6707093478946</v>
+        <v>3.44155979902406</v>
       </c>
       <c r="D216" t="n">
-        <v>5.73639650227664</v>
+        <v>3.15357206714374</v>
       </c>
       <c r="E216" t="n">
-        <v>0.0547684708105518</v>
+        <v>0.229476192036779</v>
       </c>
       <c r="F216" t="n">
-        <v>0.0119116426272429</v>
+        <v>0.0243823277566157</v>
       </c>
     </row>
     <row r="217">
@@ -5510,19 +5546,19 @@
         <v>221</v>
       </c>
       <c r="B217" t="n">
-        <v>2.60271988446983</v>
+        <v>0.454245473590296</v>
       </c>
       <c r="C217" t="n">
-        <v>2.6707093478946</v>
+        <v>0.441559799024056</v>
       </c>
       <c r="D217" t="n">
-        <v>2.73639650227664</v>
+        <v>0.153572067143742</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0547684708105518</v>
+        <v>0.229476192036779</v>
       </c>
       <c r="F217" t="n">
-        <v>0.0119116426272429</v>
+        <v>0.0243823277566157</v>
       </c>
     </row>
     <row r="218">
@@ -5530,19 +5566,19 @@
         <v>222</v>
       </c>
       <c r="B218" t="n">
-        <v>-3.65525695144415</v>
+        <v>-3.39728011553017</v>
       </c>
       <c r="C218" t="n">
-        <v>-3.68402965454308</v>
+        <v>-3.3292906521054</v>
       </c>
       <c r="D218" t="n">
-        <v>-3.77469071827414</v>
+        <v>-3.26360349772336</v>
       </c>
       <c r="E218" t="n">
-        <v>0.14866227749998</v>
+        <v>0.0547684708105518</v>
       </c>
       <c r="F218" t="n">
-        <v>0.0196248677431919</v>
+        <v>0.0119116426272429</v>
       </c>
     </row>
     <row r="219">
@@ -5550,19 +5586,19 @@
         <v>223</v>
       </c>
       <c r="B219" t="n">
-        <v>5.34474304855584</v>
+        <v>5.60271988446983</v>
       </c>
       <c r="C219" t="n">
-        <v>5.31597034545692</v>
+        <v>5.6707093478946</v>
       </c>
       <c r="D219" t="n">
-        <v>5.22530928172586</v>
+        <v>5.73639650227664</v>
       </c>
       <c r="E219" t="n">
-        <v>0.14866227749998</v>
+        <v>0.0547684708105518</v>
       </c>
       <c r="F219" t="n">
-        <v>0.0196248677431919</v>
+        <v>0.0119116426272429</v>
       </c>
     </row>
     <row r="220">
@@ -5570,19 +5606,19 @@
         <v>224</v>
       </c>
       <c r="B220" t="n">
-        <v>2.34474304855584</v>
+        <v>2.60271988446983</v>
       </c>
       <c r="C220" t="n">
-        <v>2.31597034545692</v>
+        <v>2.6707093478946</v>
       </c>
       <c r="D220" t="n">
-        <v>2.22530928172586</v>
+        <v>2.73639650227664</v>
       </c>
       <c r="E220" t="n">
-        <v>0.14866227749998</v>
+        <v>0.0547684708105518</v>
       </c>
       <c r="F220" t="n">
-        <v>0.0196248677431919</v>
+        <v>0.0119116426272429</v>
       </c>
     </row>
     <row r="221">
@@ -5590,19 +5626,19 @@
         <v>225</v>
       </c>
       <c r="B221" t="n">
-        <v>-4.08795850644903</v>
+        <v>-3.65525695144415</v>
       </c>
       <c r="C221" t="n">
-        <v>-4.10596108762881</v>
+        <v>-3.68402965454308</v>
       </c>
       <c r="D221" t="n">
-        <v>-3.85698519974591</v>
+        <v>-3.77469071827414</v>
       </c>
       <c r="E221" t="n">
-        <v>0.165569436768231</v>
+        <v>0.14866227749998</v>
       </c>
       <c r="F221" t="n">
-        <v>0.0207107789492461</v>
+        <v>0.0196248677431919</v>
       </c>
     </row>
     <row r="222">
@@ -5610,19 +5646,19 @@
         <v>226</v>
       </c>
       <c r="B222" t="n">
-        <v>4.91204149355097</v>
+        <v>5.34474304855584</v>
       </c>
       <c r="C222" t="n">
-        <v>4.89403891237119</v>
+        <v>5.31597034545692</v>
       </c>
       <c r="D222" t="n">
-        <v>5.14301480025409</v>
+        <v>5.22530928172586</v>
       </c>
       <c r="E222" t="n">
-        <v>0.165569436768231</v>
+        <v>0.14866227749998</v>
       </c>
       <c r="F222" t="n">
-        <v>0.0207107789492461</v>
+        <v>0.0196248677431919</v>
       </c>
     </row>
     <row r="223">
@@ -5630,19 +5666,19 @@
         <v>227</v>
       </c>
       <c r="B223" t="n">
-        <v>1.91204149355097</v>
+        <v>2.34474304855584</v>
       </c>
       <c r="C223" t="n">
-        <v>1.89403891237119</v>
+        <v>2.31597034545692</v>
       </c>
       <c r="D223" t="n">
-        <v>2.14301480025409</v>
+        <v>2.22530928172586</v>
       </c>
       <c r="E223" t="n">
-        <v>0.165569436768231</v>
+        <v>0.14866227749998</v>
       </c>
       <c r="F223" t="n">
-        <v>0.0207107789492461</v>
+        <v>0.0196248677431919</v>
       </c>
     </row>
     <row r="224">
@@ -5650,19 +5686,19 @@
         <v>228</v>
       </c>
       <c r="B224" t="n">
-        <v>-12.3137879156804</v>
+        <v>-4.08795850644903</v>
       </c>
       <c r="C224" t="n">
-        <v>-12.3242296298785</v>
+        <v>-4.10596108762881</v>
       </c>
       <c r="D224" t="n">
-        <v>-12.7759066307065</v>
+        <v>-3.85698519974591</v>
       </c>
       <c r="E224" t="n">
-        <v>0.100743326516778</v>
+        <v>0.165569436768231</v>
       </c>
       <c r="F224" t="n">
-        <v>0.0161552800618765</v>
+        <v>0.0207107789492461</v>
       </c>
     </row>
     <row r="225">
@@ -5670,19 +5706,19 @@
         <v>229</v>
       </c>
       <c r="B225" t="n">
-        <v>-6.31378791568044</v>
+        <v>4.91204149355097</v>
       </c>
       <c r="C225" t="n">
-        <v>-6.32422962987851</v>
+        <v>4.89403891237119</v>
       </c>
       <c r="D225" t="n">
-        <v>-6.77590663070652</v>
+        <v>5.14301480025409</v>
       </c>
       <c r="E225" t="n">
-        <v>0.100743326516778</v>
+        <v>0.165569436768231</v>
       </c>
       <c r="F225" t="n">
-        <v>0.0161552800618765</v>
+        <v>0.0207107789492461</v>
       </c>
     </row>
     <row r="226">
@@ -5690,19 +5726,19 @@
         <v>230</v>
       </c>
       <c r="B226" t="n">
-        <v>-9.31378791568044</v>
+        <v>1.91204149355097</v>
       </c>
       <c r="C226" t="n">
-        <v>-9.32422962987851</v>
+        <v>1.89403891237119</v>
       </c>
       <c r="D226" t="n">
-        <v>-9.77590663070652</v>
+        <v>2.14301480025409</v>
       </c>
       <c r="E226" t="n">
-        <v>0.100743326516778</v>
+        <v>0.165569436768231</v>
       </c>
       <c r="F226" t="n">
-        <v>0.0161552800618765</v>
+        <v>0.0207107789492461</v>
       </c>
     </row>
     <row r="227">
@@ -5710,19 +5746,19 @@
         <v>231</v>
       </c>
       <c r="B227" t="n">
-        <v>-5.24105865023618</v>
+        <v>-12.3137879156804</v>
       </c>
       <c r="C227" t="n">
-        <v>-5.2300995592046</v>
+        <v>-12.3242296298785</v>
       </c>
       <c r="D227" t="n">
-        <v>-5.47443586370432</v>
+        <v>-12.7759066307065</v>
       </c>
       <c r="E227" t="n">
-        <v>0.126925019304733</v>
+        <v>0.100743326516778</v>
       </c>
       <c r="F227" t="n">
-        <v>0.0181334302749253</v>
+        <v>0.0161552800618765</v>
       </c>
     </row>
     <row r="228">
@@ -5730,19 +5766,19 @@
         <v>232</v>
       </c>
       <c r="B228" t="n">
-        <v>3.75894134976382</v>
+        <v>-6.31378791568044</v>
       </c>
       <c r="C228" t="n">
-        <v>3.7699004407954</v>
+        <v>-6.32422962987851</v>
       </c>
       <c r="D228" t="n">
-        <v>3.52556413629568</v>
+        <v>-6.77590663070652</v>
       </c>
       <c r="E228" t="n">
-        <v>0.126925019304733</v>
+        <v>0.100743326516778</v>
       </c>
       <c r="F228" t="n">
-        <v>0.0181334302749253</v>
+        <v>0.0161552800618765</v>
       </c>
     </row>
     <row r="229">
@@ -5750,19 +5786,19 @@
         <v>233</v>
       </c>
       <c r="B229" t="n">
-        <v>0.758941349763823</v>
+        <v>-9.31378791568044</v>
       </c>
       <c r="C229" t="n">
-        <v>0.769900440795398</v>
+        <v>-9.32422962987851</v>
       </c>
       <c r="D229" t="n">
-        <v>0.525564136295676</v>
+        <v>-9.77590663070652</v>
       </c>
       <c r="E229" t="n">
-        <v>0.126925019304733</v>
+        <v>0.100743326516778</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0181334302749253</v>
+        <v>0.0161552800618765</v>
       </c>
     </row>
     <row r="230">
@@ -5770,19 +5806,19 @@
         <v>234</v>
       </c>
       <c r="B230" t="n">
-        <v>-6.71936705589618</v>
+        <v>-5.24105865023618</v>
       </c>
       <c r="C230" t="n">
-        <v>-6.75113637641012</v>
+        <v>-5.2300995592046</v>
       </c>
       <c r="D230" t="n">
-        <v>-6.59308025306971</v>
+        <v>-5.47443586370432</v>
       </c>
       <c r="E230" t="n">
-        <v>0.195766615648459</v>
+        <v>0.126925019304733</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0225203773958831</v>
+        <v>0.0181334302749253</v>
       </c>
     </row>
     <row r="231">
@@ -5790,19 +5826,19 @@
         <v>235</v>
       </c>
       <c r="B231" t="n">
-        <v>2.28063294410382</v>
+        <v>3.75894134976382</v>
       </c>
       <c r="C231" t="n">
-        <v>2.24886362358988</v>
+        <v>3.7699004407954</v>
       </c>
       <c r="D231" t="n">
-        <v>2.40691974693029</v>
+        <v>3.52556413629568</v>
       </c>
       <c r="E231" t="n">
-        <v>0.195766615648459</v>
+        <v>0.126925019304733</v>
       </c>
       <c r="F231" t="n">
-        <v>0.0225203773958831</v>
+        <v>0.0181334302749253</v>
       </c>
     </row>
     <row r="232">
@@ -5810,19 +5846,19 @@
         <v>236</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.719367055896181</v>
+        <v>0.758941349763823</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.75113637641012</v>
+        <v>0.769900440795398</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.593080253069712</v>
+        <v>0.525564136295676</v>
       </c>
       <c r="E232" t="n">
-        <v>0.195766615648459</v>
+        <v>0.126925019304733</v>
       </c>
       <c r="F232" t="n">
-        <v>0.0225203773958831</v>
+        <v>0.0181334302749253</v>
       </c>
     </row>
     <row r="233">
@@ -5830,19 +5866,19 @@
         <v>237</v>
       </c>
       <c r="B233" t="n">
-        <v>-7.29780787608565</v>
+        <v>-6.71936705589618</v>
       </c>
       <c r="C233" t="n">
-        <v>-7.30088456249741</v>
+        <v>-6.75113637641012</v>
       </c>
       <c r="D233" t="n">
-        <v>-7.74488375097813</v>
+        <v>-6.59308025306971</v>
       </c>
       <c r="E233" t="n">
-        <v>0.282047080590764</v>
+        <v>0.195766615648459</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0270313136682057</v>
+        <v>0.0225203773958831</v>
       </c>
     </row>
     <row r="234">
@@ -5850,19 +5886,19 @@
         <v>238</v>
       </c>
       <c r="B234" t="n">
-        <v>1.70219212391435</v>
+        <v>2.28063294410382</v>
       </c>
       <c r="C234" t="n">
-        <v>1.69911543750259</v>
+        <v>2.24886362358988</v>
       </c>
       <c r="D234" t="n">
-        <v>1.25511624902187</v>
+        <v>2.40691974693029</v>
       </c>
       <c r="E234" t="n">
-        <v>0.282047080590764</v>
+        <v>0.195766615648459</v>
       </c>
       <c r="F234" t="n">
-        <v>0.0270313136682057</v>
+        <v>0.0225203773958831</v>
       </c>
     </row>
     <row r="235">
@@ -5870,19 +5906,19 @@
         <v>239</v>
       </c>
       <c r="B235" t="n">
-        <v>-1.29780787608565</v>
+        <v>-0.719367055896181</v>
       </c>
       <c r="C235" t="n">
-        <v>-1.30088456249741</v>
+        <v>-0.75113637641012</v>
       </c>
       <c r="D235" t="n">
-        <v>-1.74488375097813</v>
+        <v>-0.593080253069712</v>
       </c>
       <c r="E235" t="n">
-        <v>0.282047080590764</v>
+        <v>0.195766615648459</v>
       </c>
       <c r="F235" t="n">
-        <v>0.0270313136682057</v>
+        <v>0.0225203773958831</v>
       </c>
     </row>
     <row r="236">
@@ -5890,19 +5926,19 @@
         <v>240</v>
       </c>
       <c r="B236" t="n">
-        <v>-5.66835924651595</v>
+        <v>-7.29780787608565</v>
       </c>
       <c r="C236" t="n">
-        <v>-5.66258181576849</v>
+        <v>-7.30088456249741</v>
       </c>
       <c r="D236" t="n">
-        <v>-5.99651972783737</v>
+        <v>-7.74488375097813</v>
       </c>
       <c r="E236" t="n">
-        <v>0.0852470345732533</v>
+        <v>0.282047080590764</v>
       </c>
       <c r="F236" t="n">
-        <v>0.0148609299785404</v>
+        <v>0.0270313136682057</v>
       </c>
     </row>
     <row r="237">
@@ -5910,19 +5946,19 @@
         <v>241</v>
       </c>
       <c r="B237" t="n">
-        <v>3.33164075348405</v>
+        <v>1.70219212391435</v>
       </c>
       <c r="C237" t="n">
-        <v>3.33741818423151</v>
+        <v>1.69911543750259</v>
       </c>
       <c r="D237" t="n">
-        <v>3.00348027216263</v>
+        <v>1.25511624902187</v>
       </c>
       <c r="E237" t="n">
-        <v>0.0852470345732533</v>
+        <v>0.282047080590764</v>
       </c>
       <c r="F237" t="n">
-        <v>0.0148609299785404</v>
+        <v>0.0270313136682057</v>
       </c>
     </row>
     <row r="238">
@@ -5930,19 +5966,19 @@
         <v>242</v>
       </c>
       <c r="B238" t="n">
-        <v>0.331640753484046</v>
+        <v>-1.29780787608565</v>
       </c>
       <c r="C238" t="n">
-        <v>0.337418184231511</v>
+        <v>-1.30088456249741</v>
       </c>
       <c r="D238" t="n">
-        <v>0.00348027216263097</v>
+        <v>-1.74488375097813</v>
       </c>
       <c r="E238" t="n">
-        <v>0.0852470345732533</v>
+        <v>0.282047080590764</v>
       </c>
       <c r="F238" t="n">
-        <v>0.0148609299785404</v>
+        <v>0.0270313136682057</v>
       </c>
     </row>
     <row r="239">
@@ -5950,19 +5986,19 @@
         <v>243</v>
       </c>
       <c r="B239" t="n">
-        <v>-6.56298825801238</v>
+        <v>-5.66835924651595</v>
       </c>
       <c r="C239" t="n">
-        <v>-6.58754641809639</v>
+        <v>-5.66258181576849</v>
       </c>
       <c r="D239" t="n">
-        <v>-6.98674196473976</v>
+        <v>-5.99651972783737</v>
       </c>
       <c r="E239" t="n">
-        <v>0.2690323214326</v>
+        <v>0.0852470345732533</v>
       </c>
       <c r="F239" t="n">
-        <v>0.0264002826877136</v>
+        <v>0.0148609299785404</v>
       </c>
     </row>
     <row r="240">
@@ -5970,19 +6006,19 @@
         <v>244</v>
       </c>
       <c r="B240" t="n">
-        <v>2.43701174198762</v>
+        <v>3.33164075348405</v>
       </c>
       <c r="C240" t="n">
-        <v>2.41245358190361</v>
+        <v>3.33741818423151</v>
       </c>
       <c r="D240" t="n">
-        <v>2.01325803526024</v>
+        <v>3.00348027216263</v>
       </c>
       <c r="E240" t="n">
-        <v>0.2690323214326</v>
+        <v>0.0852470345732533</v>
       </c>
       <c r="F240" t="n">
-        <v>0.0264002826877136</v>
+        <v>0.0148609299785404</v>
       </c>
     </row>
     <row r="241">
@@ -5990,19 +6026,19 @@
         <v>245</v>
       </c>
       <c r="B241" t="n">
-        <v>-0.562988258012385</v>
+        <v>0.331640753484046</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.587546418096389</v>
+        <v>0.337418184231511</v>
       </c>
       <c r="D241" t="n">
-        <v>-0.986741964739757</v>
+        <v>0.00348027216263097</v>
       </c>
       <c r="E241" t="n">
-        <v>0.2690323214326</v>
+        <v>0.0852470345732533</v>
       </c>
       <c r="F241" t="n">
-        <v>0.0264002826877136</v>
+        <v>0.0148609299785404</v>
       </c>
     </row>
     <row r="242">
@@ -6010,19 +6046,19 @@
         <v>246</v>
       </c>
       <c r="B242" t="n">
-        <v>-7.44769008322978</v>
+        <v>-6.56298825801238</v>
       </c>
       <c r="C242" t="n">
-        <v>-7.47258465659123</v>
+        <v>-6.58754641809639</v>
       </c>
       <c r="D242" t="n">
-        <v>-8.22942662083826</v>
+        <v>-6.98674196473976</v>
       </c>
       <c r="E242" t="n">
-        <v>0.152788493102304</v>
+        <v>0.2690323214326</v>
       </c>
       <c r="F242" t="n">
-        <v>0.0198953540220827</v>
+        <v>0.0264002826877136</v>
       </c>
     </row>
     <row r="243">
@@ -6030,19 +6066,19 @@
         <v>247</v>
       </c>
       <c r="B243" t="n">
-        <v>1.55230991677022</v>
+        <v>2.43701174198762</v>
       </c>
       <c r="C243" t="n">
-        <v>1.52741534340877</v>
+        <v>2.41245358190361</v>
       </c>
       <c r="D243" t="n">
-        <v>0.77057337916174</v>
+        <v>2.01325803526024</v>
       </c>
       <c r="E243" t="n">
-        <v>0.152788493102304</v>
+        <v>0.2690323214326</v>
       </c>
       <c r="F243" t="n">
-        <v>0.0198953540220827</v>
+        <v>0.0264002826877136</v>
       </c>
     </row>
     <row r="244">
@@ -6050,19 +6086,19 @@
         <v>248</v>
       </c>
       <c r="B244" t="n">
-        <v>-1.44769008322978</v>
+        <v>-0.562988258012385</v>
       </c>
       <c r="C244" t="n">
-        <v>-1.47258465659123</v>
+        <v>-0.587546418096389</v>
       </c>
       <c r="D244" t="n">
-        <v>-2.22942662083826</v>
+        <v>-0.986741964739757</v>
       </c>
       <c r="E244" t="n">
-        <v>0.152788493102304</v>
+        <v>0.2690323214326</v>
       </c>
       <c r="F244" t="n">
-        <v>0.0198953540220827</v>
+        <v>0.0264002826877136</v>
       </c>
     </row>
     <row r="245">
@@ -6070,19 +6106,19 @@
         <v>249</v>
       </c>
       <c r="B245" t="n">
-        <v>1.17928162520831</v>
+        <v>-7.44769008322978</v>
       </c>
       <c r="C245" t="n">
-        <v>1.17897694729317</v>
+        <v>-7.47258465659123</v>
       </c>
       <c r="D245" t="n">
-        <v>1.35983548233989</v>
+        <v>-8.22942662083826</v>
       </c>
       <c r="E245" t="n">
-        <v>0.0239070328229495</v>
+        <v>0.152788493102304</v>
       </c>
       <c r="F245" t="n">
-        <v>0.0078698995034352</v>
+        <v>0.0198953540220827</v>
       </c>
     </row>
     <row r="246">
@@ -6090,19 +6126,19 @@
         <v>250</v>
       </c>
       <c r="B246" t="n">
-        <v>-0.387924893695415</v>
+        <v>1.55230991677022</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.214670164989233</v>
+        <v>1.52741534340877</v>
       </c>
       <c r="D246" t="n">
-        <v>-0.565431095965801</v>
+        <v>0.77057337916174</v>
       </c>
       <c r="E246" t="n">
-        <v>0.266895369325391</v>
+        <v>0.152788493102304</v>
       </c>
       <c r="F246" t="n">
-        <v>0.0308739007511309</v>
+        <v>0.0198953540220827</v>
       </c>
     </row>
     <row r="247">
@@ -6110,19 +6146,19 @@
         <v>251</v>
       </c>
       <c r="B247" t="n">
-        <v>-8.58532635347096</v>
+        <v>-1.44769008322978</v>
       </c>
       <c r="C247" t="n">
-        <v>-8.54545641624325</v>
+        <v>-1.47258465659123</v>
       </c>
       <c r="D247" t="n">
-        <v>-8.95712662644021</v>
+        <v>-2.22942662083826</v>
       </c>
       <c r="E247" t="n">
-        <v>0.286106788001192</v>
+        <v>0.152788493102304</v>
       </c>
       <c r="F247" t="n">
-        <v>0.0272251592344264</v>
+        <v>0.0198953540220827</v>
       </c>
     </row>
     <row r="248">
@@ -6130,19 +6166,19 @@
         <v>252</v>
       </c>
       <c r="B248" t="n">
-        <v>0.414673646529041</v>
+        <v>1.17928162520831</v>
       </c>
       <c r="C248" t="n">
-        <v>0.454543583756748</v>
+        <v>1.17897694729317</v>
       </c>
       <c r="D248" t="n">
-        <v>0.0428733735597898</v>
+        <v>1.35983548233989</v>
       </c>
       <c r="E248" t="n">
-        <v>0.286106788001192</v>
+        <v>0.0239070328229495</v>
       </c>
       <c r="F248" t="n">
-        <v>0.0272251592344264</v>
+        <v>0.0078698995034352</v>
       </c>
     </row>
     <row r="249">
@@ -6150,19 +6186,19 @@
         <v>253</v>
       </c>
       <c r="B249" t="n">
-        <v>-2.58532635347096</v>
+        <v>-0.387924893695415</v>
       </c>
       <c r="C249" t="n">
-        <v>-2.54545641624325</v>
+        <v>-0.214670164989233</v>
       </c>
       <c r="D249" t="n">
-        <v>-2.95712662644021</v>
+        <v>-0.565431095965801</v>
       </c>
       <c r="E249" t="n">
-        <v>0.286106788001192</v>
+        <v>0.266895369325391</v>
       </c>
       <c r="F249" t="n">
-        <v>0.0272251592344264</v>
+        <v>0.0308739007511309</v>
       </c>
     </row>
     <row r="250">
@@ -6170,19 +6206,19 @@
         <v>254</v>
       </c>
       <c r="B250" t="n">
-        <v>-11.1376754319643</v>
+        <v>-8.58532635347096</v>
       </c>
       <c r="C250" t="n">
-        <v>-11.0938235262643</v>
+        <v>-8.54545641624325</v>
       </c>
       <c r="D250" t="n">
-        <v>-11.4458240571519</v>
+        <v>-8.95712662644021</v>
       </c>
       <c r="E250" t="n">
-        <v>0.342127792431983</v>
+        <v>0.286106788001192</v>
       </c>
       <c r="F250" t="n">
-        <v>0.0297714868820981</v>
+        <v>0.0272251592344264</v>
       </c>
     </row>
     <row r="251">
@@ -6190,19 +6226,19 @@
         <v>255</v>
       </c>
       <c r="B251" t="n">
-        <v>-2.1376754319643</v>
+        <v>0.414673646529041</v>
       </c>
       <c r="C251" t="n">
-        <v>-2.09382352626426</v>
+        <v>0.454543583756748</v>
       </c>
       <c r="D251" t="n">
-        <v>-2.44582405715191</v>
+        <v>0.0428733735597898</v>
       </c>
       <c r="E251" t="n">
-        <v>0.342127792431983</v>
+        <v>0.286106788001192</v>
       </c>
       <c r="F251" t="n">
-        <v>0.0297714868820981</v>
+        <v>0.0272251592344264</v>
       </c>
     </row>
     <row r="252">
@@ -6210,19 +6246,19 @@
         <v>256</v>
       </c>
       <c r="B252" t="n">
-        <v>-5.1376754319643</v>
+        <v>-2.58532635347096</v>
       </c>
       <c r="C252" t="n">
-        <v>-5.09382352626426</v>
+        <v>-2.54545641624325</v>
       </c>
       <c r="D252" t="n">
-        <v>-5.44582405715191</v>
+        <v>-2.95712662644021</v>
       </c>
       <c r="E252" t="n">
-        <v>0.342127792431983</v>
+        <v>0.286106788001192</v>
       </c>
       <c r="F252" t="n">
-        <v>0.0297714868820981</v>
+        <v>0.0272251592344264</v>
       </c>
     </row>
     <row r="253">
@@ -6230,19 +6266,19 @@
         <v>257</v>
       </c>
       <c r="B253" t="n">
-        <v>-7.81039476957295</v>
+        <v>-11.1376754319643</v>
       </c>
       <c r="C253" t="n">
-        <v>-7.71514785095294</v>
+        <v>-11.0938235262643</v>
       </c>
       <c r="D253" t="n">
-        <v>-7.77116908592302</v>
+        <v>-11.4458240571519</v>
       </c>
       <c r="E253" t="n">
-        <v>0.16641007564819</v>
+        <v>0.342127792431983</v>
       </c>
       <c r="F253" t="n">
-        <v>0.0207632893737257</v>
+        <v>0.0297714868820981</v>
       </c>
     </row>
     <row r="254">
@@ -6250,19 +6286,19 @@
         <v>258</v>
       </c>
       <c r="B254" t="n">
-        <v>1.18960523042705</v>
+        <v>-2.1376754319643</v>
       </c>
       <c r="C254" t="n">
-        <v>1.28485214904706</v>
+        <v>-2.09382352626426</v>
       </c>
       <c r="D254" t="n">
-        <v>1.22883091407698</v>
+        <v>-2.44582405715191</v>
       </c>
       <c r="E254" t="n">
-        <v>0.16641007564819</v>
+        <v>0.342127792431983</v>
       </c>
       <c r="F254" t="n">
-        <v>0.0207632893737257</v>
+        <v>0.0297714868820981</v>
       </c>
     </row>
     <row r="255">
@@ -6270,19 +6306,19 @@
         <v>259</v>
       </c>
       <c r="B255" t="n">
-        <v>-1.81039476957295</v>
+        <v>-5.1376754319643</v>
       </c>
       <c r="C255" t="n">
-        <v>-1.71514785095294</v>
+        <v>-5.09382352626426</v>
       </c>
       <c r="D255" t="n">
-        <v>-1.77116908592302</v>
+        <v>-5.44582405715191</v>
       </c>
       <c r="E255" t="n">
-        <v>0.16641007564819</v>
+        <v>0.342127792431983</v>
       </c>
       <c r="F255" t="n">
-        <v>0.0207632893737257</v>
+        <v>0.0297714868820981</v>
       </c>
     </row>
     <row r="256">
@@ -6290,19 +6326,19 @@
         <v>260</v>
       </c>
       <c r="B256" t="n">
-        <v>-9.48234680236329</v>
+        <v>-7.81039476957295</v>
       </c>
       <c r="C256" t="n">
-        <v>-9.47325479550294</v>
+        <v>-7.71514785095294</v>
       </c>
       <c r="D256" t="n">
-        <v>-10.0659832147074</v>
+        <v>-7.77116908592302</v>
       </c>
       <c r="E256" t="n">
-        <v>0.192017860945023</v>
+        <v>0.16641007564819</v>
       </c>
       <c r="F256" t="n">
-        <v>0.0223037126573844</v>
+        <v>0.0207632893737257</v>
       </c>
     </row>
     <row r="257">
@@ -6310,19 +6346,19 @@
         <v>261</v>
       </c>
       <c r="B257" t="n">
-        <v>-0.482346802363294</v>
+        <v>1.18960523042705</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.47325479550294</v>
+        <v>1.28485214904706</v>
       </c>
       <c r="D257" t="n">
-        <v>-1.06598321470742</v>
+        <v>1.22883091407698</v>
       </c>
       <c r="E257" t="n">
-        <v>0.192017860945023</v>
+        <v>0.16641007564819</v>
       </c>
       <c r="F257" t="n">
-        <v>0.0223037126573844</v>
+        <v>0.0207632893737257</v>
       </c>
     </row>
     <row r="258">
@@ -6330,19 +6366,19 @@
         <v>262</v>
       </c>
       <c r="B258" t="n">
-        <v>-3.48234680236329</v>
+        <v>-1.81039476957295</v>
       </c>
       <c r="C258" t="n">
-        <v>-3.47325479550294</v>
+        <v>-1.71514785095294</v>
       </c>
       <c r="D258" t="n">
-        <v>-4.06598321470742</v>
+        <v>-1.77116908592302</v>
       </c>
       <c r="E258" t="n">
-        <v>0.192017860945023</v>
+        <v>0.16641007564819</v>
       </c>
       <c r="F258" t="n">
-        <v>0.0223037126573844</v>
+        <v>0.0207632893737257</v>
       </c>
     </row>
     <row r="259">
@@ -6350,19 +6386,19 @@
         <v>263</v>
       </c>
       <c r="B259" t="n">
-        <v>-9.78356888805875</v>
+        <v>-9.48234680236329</v>
       </c>
       <c r="C259" t="n">
-        <v>-9.80898619716051</v>
+        <v>-9.47325479550294</v>
       </c>
       <c r="D259" t="n">
-        <v>-10.3373956657658</v>
+        <v>-10.0659832147074</v>
       </c>
       <c r="E259" t="n">
-        <v>0.241671282988214</v>
+        <v>0.192017860945023</v>
       </c>
       <c r="F259" t="n">
-        <v>0.0250218186130668</v>
+        <v>0.0223037126573844</v>
       </c>
     </row>
     <row r="260">
@@ -6370,19 +6406,19 @@
         <v>264</v>
       </c>
       <c r="B260" t="n">
-        <v>-0.783568888058748</v>
+        <v>-0.482346802363294</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.808986197160512</v>
+        <v>-0.47325479550294</v>
       </c>
       <c r="D260" t="n">
-        <v>-1.33739566576581</v>
+        <v>-1.06598321470742</v>
       </c>
       <c r="E260" t="n">
-        <v>0.241671282988214</v>
+        <v>0.192017860945023</v>
       </c>
       <c r="F260" t="n">
-        <v>0.0250218186130668</v>
+        <v>0.0223037126573844</v>
       </c>
     </row>
     <row r="261">
@@ -6390,19 +6426,19 @@
         <v>265</v>
       </c>
       <c r="B261" t="n">
-        <v>-3.78356888805875</v>
+        <v>-3.48234680236329</v>
       </c>
       <c r="C261" t="n">
-        <v>-3.80898619716051</v>
+        <v>-3.47325479550294</v>
       </c>
       <c r="D261" t="n">
-        <v>-4.33739566576581</v>
+        <v>-4.06598321470742</v>
       </c>
       <c r="E261" t="n">
-        <v>0.241671282988214</v>
+        <v>0.192017860945023</v>
       </c>
       <c r="F261" t="n">
-        <v>0.0250218186130668</v>
+        <v>0.0223037126573844</v>
       </c>
     </row>
     <row r="262">
@@ -6410,19 +6446,19 @@
         <v>266</v>
       </c>
       <c r="B262" t="n">
-        <v>-16.0001688893144</v>
+        <v>-9.78356888805875</v>
       </c>
       <c r="C262" t="n">
-        <v>-16.0001144472419</v>
+        <v>-9.80898619716051</v>
       </c>
       <c r="D262" t="n">
-        <v>-16.0000953598044</v>
+        <v>-10.3373956657658</v>
       </c>
       <c r="E262" t="n">
-        <v>0.0000000962471936592136</v>
+        <v>0.241671282988214</v>
       </c>
       <c r="F262" t="n">
-        <v>0.0000157906637382125</v>
+        <v>0.0250218186130668</v>
       </c>
     </row>
     <row r="263">
@@ -6430,19 +6466,19 @@
         <v>267</v>
       </c>
       <c r="B263" t="n">
-        <v>-7.00016888931441</v>
+        <v>-0.783568888058748</v>
       </c>
       <c r="C263" t="n">
-        <v>-7.00011444724188</v>
+        <v>-0.808986197160512</v>
       </c>
       <c r="D263" t="n">
-        <v>-7.00009535980438</v>
+        <v>-1.33739566576581</v>
       </c>
       <c r="E263" t="n">
-        <v>0.0000000962471936592264</v>
+        <v>0.241671282988214</v>
       </c>
       <c r="F263" t="n">
-        <v>0.0000157906637382136</v>
+        <v>0.0250218186130668</v>
       </c>
     </row>
     <row r="264">
@@ -6450,19 +6486,19 @@
         <v>268</v>
       </c>
       <c r="B264" t="n">
-        <v>-10.0001688893144</v>
+        <v>-3.78356888805875</v>
       </c>
       <c r="C264" t="n">
-        <v>-10.0001144472419</v>
+        <v>-3.80898619716051</v>
       </c>
       <c r="D264" t="n">
-        <v>-10.0000953598044</v>
+        <v>-4.33739566576581</v>
       </c>
       <c r="E264" t="n">
-        <v>0.0000000962471936592294</v>
+        <v>0.241671282988214</v>
       </c>
       <c r="F264" t="n">
-        <v>0.0000157906637382138</v>
+        <v>0.0250218186130668</v>
       </c>
     </row>
     <row r="265">
@@ -6470,19 +6506,19 @@
         <v>269</v>
       </c>
       <c r="B265" t="n">
-        <v>-7.06909585835686</v>
+        <v>-16.0001688893144</v>
       </c>
       <c r="C265" t="n">
-        <v>-7.08671609823958</v>
+        <v>-16.0001144472419</v>
       </c>
       <c r="D265" t="n">
-        <v>-6.98296666070122</v>
+        <v>-16.0000953598044</v>
       </c>
       <c r="E265" t="n">
-        <v>0.0835980316493435</v>
+        <v>0.0000000962471936592136</v>
       </c>
       <c r="F265" t="n">
-        <v>0.0147164945393527</v>
+        <v>0.0000157906637382125</v>
       </c>
     </row>
     <row r="266">
@@ -6490,19 +6526,19 @@
         <v>270</v>
       </c>
       <c r="B266" t="n">
-        <v>-10.1525917761504</v>
+        <v>-7.00016888931441</v>
       </c>
       <c r="C266" t="n">
-        <v>-10.1219982998966</v>
+        <v>-7.00011444724188</v>
       </c>
       <c r="D266" t="n">
-        <v>-11.1261205536309</v>
+        <v>-7.00009535980438</v>
       </c>
       <c r="E266" t="n">
-        <v>0.71629861954669</v>
+        <v>0.0000000962471936592264</v>
       </c>
       <c r="F266" t="n">
-        <v>0.0430777890050241</v>
+        <v>0.0000157906637382136</v>
       </c>
     </row>
     <row r="267">
@@ -6510,19 +6546,19 @@
         <v>271</v>
       </c>
       <c r="B267" t="n">
-        <v>-1.15259177615043</v>
+        <v>-10.0001688893144</v>
       </c>
       <c r="C267" t="n">
-        <v>-1.12199829989665</v>
+        <v>-10.0001144472419</v>
       </c>
       <c r="D267" t="n">
-        <v>-2.12612055363087</v>
+        <v>-10.0000953598044</v>
       </c>
       <c r="E267" t="n">
-        <v>0.71629861954669</v>
+        <v>0.0000000962471936592294</v>
       </c>
       <c r="F267" t="n">
-        <v>0.0430777890050241</v>
+        <v>0.0000157906637382138</v>
       </c>
     </row>
     <row r="268">
@@ -6530,19 +6566,19 @@
         <v>272</v>
       </c>
       <c r="B268" t="n">
-        <v>-4.15259177615043</v>
+        <v>-7.06909585835686</v>
       </c>
       <c r="C268" t="n">
-        <v>-4.12199829989665</v>
+        <v>-7.08671609823958</v>
       </c>
       <c r="D268" t="n">
-        <v>-5.12612055363087</v>
+        <v>-6.98296666070122</v>
       </c>
       <c r="E268" t="n">
-        <v>0.71629861954669</v>
+        <v>0.0835980316493435</v>
       </c>
       <c r="F268" t="n">
-        <v>0.0430777890050241</v>
+        <v>0.0147164945393527</v>
       </c>
     </row>
     <row r="269">
@@ -6550,19 +6586,19 @@
         <v>273</v>
       </c>
       <c r="B269" t="n">
-        <v>-5.06463887066509</v>
+        <v>-10.1525917761504</v>
       </c>
       <c r="C269" t="n">
-        <v>-5.02087801373083</v>
+        <v>-10.1219982998966</v>
       </c>
       <c r="D269" t="n">
-        <v>-4.81565717426209</v>
+        <v>-11.1261205536309</v>
       </c>
       <c r="E269" t="n">
-        <v>0.0436346956879248</v>
+        <v>0.71629861954669</v>
       </c>
       <c r="F269" t="n">
-        <v>0.0106321800717221</v>
+        <v>0.0430777890050241</v>
       </c>
     </row>
     <row r="270">
@@ -6570,19 +6606,19 @@
         <v>274</v>
       </c>
       <c r="B270" t="n">
-        <v>3.93536112933491</v>
+        <v>-1.15259177615043</v>
       </c>
       <c r="C270" t="n">
-        <v>3.97912198626917</v>
+        <v>-1.12199829989665</v>
       </c>
       <c r="D270" t="n">
-        <v>4.18434282573791</v>
+        <v>-2.12612055363087</v>
       </c>
       <c r="E270" t="n">
-        <v>0.0436346956879248</v>
+        <v>0.71629861954669</v>
       </c>
       <c r="F270" t="n">
-        <v>0.0106321800717221</v>
+        <v>0.0430777890050241</v>
       </c>
     </row>
     <row r="271">
@@ -6590,19 +6626,19 @@
         <v>275</v>
       </c>
       <c r="B271" t="n">
-        <v>0.935361129334911</v>
+        <v>-4.15259177615043</v>
       </c>
       <c r="C271" t="n">
-        <v>0.979121986269174</v>
+        <v>-4.12199829989665</v>
       </c>
       <c r="D271" t="n">
-        <v>1.18434282573791</v>
+        <v>-5.12612055363087</v>
       </c>
       <c r="E271" t="n">
-        <v>0.0436346956879248</v>
+        <v>0.71629861954669</v>
       </c>
       <c r="F271" t="n">
-        <v>0.0106321800717221</v>
+        <v>0.0430777890050241</v>
       </c>
     </row>
     <row r="272">
@@ -6610,19 +6646,19 @@
         <v>276</v>
       </c>
       <c r="B272" t="n">
-        <v>1.93090414164314</v>
+        <v>-0.897178116393715</v>
       </c>
       <c r="C272" t="n">
-        <v>1.91328390176042</v>
+        <v>-0.854173804212698</v>
       </c>
       <c r="D272" t="n">
-        <v>2.01703333929878</v>
+        <v>-0.705801329509983</v>
       </c>
       <c r="E272" t="n">
-        <v>0.0835980316493435</v>
+        <v>0.0585983985335408</v>
       </c>
       <c r="F272" t="n">
-        <v>0.0147164945393527</v>
+        <v>0.0123210925905844</v>
       </c>
     </row>
     <row r="273">
@@ -6630,19 +6666,19 @@
         <v>277</v>
       </c>
       <c r="B273" t="n">
-        <v>-1.06909585835686</v>
+        <v>8.10282188360629</v>
       </c>
       <c r="C273" t="n">
-        <v>-1.08671609823958</v>
+        <v>8.1458261957873</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.98296666070122</v>
+        <v>8.29419867049002</v>
       </c>
       <c r="E273" t="n">
-        <v>0.0835980316493435</v>
+        <v>0.0585983985335408</v>
       </c>
       <c r="F273" t="n">
-        <v>0.0147164945393527</v>
+        <v>0.0123210925905844</v>
       </c>
     </row>
     <row r="274">
@@ -6650,19 +6686,19 @@
         <v>278</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.666611909893623</v>
+        <v>5.10282188360629</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.66059766321667</v>
+        <v>5.1458261957873</v>
       </c>
       <c r="D274" t="n">
-        <v>-0.47976307308921</v>
+        <v>5.29419867049002</v>
       </c>
       <c r="E274" t="n">
-        <v>0.0529478407200874</v>
+        <v>0.0585983985335408</v>
       </c>
       <c r="F274" t="n">
-        <v>0.0117119841108882</v>
+        <v>0.0123210925905844</v>
       </c>
     </row>
     <row r="275">
@@ -6670,19 +6706,19 @@
         <v>279</v>
       </c>
       <c r="B275" t="n">
-        <v>7.61722797927461</v>
+        <v>-6.02946975900035</v>
       </c>
       <c r="C275" t="n">
-        <v>7.63</v>
+        <v>-6.00358816209828</v>
       </c>
       <c r="D275" t="n">
-        <v>7.63</v>
+        <v>-5.89392262610087</v>
       </c>
       <c r="E275" t="n">
-        <v>0.184809179059283</v>
+        <v>0.0435381854662681</v>
       </c>
       <c r="F275" t="n">
-        <v>0.0218810478869333</v>
+        <v>0.010620415556679</v>
       </c>
     </row>
     <row r="276">
@@ -6690,18 +6726,138 @@
         <v>280</v>
       </c>
       <c r="B276" t="n">
+        <v>2.97053024099965</v>
+      </c>
+      <c r="C276" t="n">
+        <v>2.99641183790172</v>
+      </c>
+      <c r="D276" t="n">
+        <v>3.10607737389913</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.0435381854662681</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.010620415556679</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>281</v>
+      </c>
+      <c r="B277" t="n">
+        <v>-0.0294697590003481</v>
+      </c>
+      <c r="C277" t="n">
+        <v>-0.00358816209827762</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.106077373899131</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.0435381854662681</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.010620415556679</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>282</v>
+      </c>
+      <c r="B278" t="n">
+        <v>1.93090414164314</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1.91328390176042</v>
+      </c>
+      <c r="D278" t="n">
+        <v>2.01703333929878</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.0835980316493435</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0.0147164945393527</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>283</v>
+      </c>
+      <c r="B279" t="n">
+        <v>-1.06909585835686</v>
+      </c>
+      <c r="C279" t="n">
+        <v>-1.08671609823958</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-0.98296666070122</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.0835980316493435</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0.0147164945393527</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>284</v>
+      </c>
+      <c r="B280" t="n">
+        <v>-0.666611909893623</v>
+      </c>
+      <c r="C280" t="n">
+        <v>-0.66059766321667</v>
+      </c>
+      <c r="D280" t="n">
+        <v>-0.47976307308921</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.0529478407200874</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0.0117119841108882</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>285</v>
+      </c>
+      <c r="B281" t="n">
+        <v>7.61722797927461</v>
+      </c>
+      <c r="C281" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="D281" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.184809179059283</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0.0218810478869333</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>286</v>
+      </c>
+      <c r="B282" t="n">
         <v>0.243462866770415</v>
       </c>
-      <c r="C276" t="n">
+      <c r="C282" t="n">
         <v>0.218475296387963</v>
       </c>
-      <c r="D276" t="n">
+      <c r="D282" t="n">
         <v>0.331311817486975</v>
       </c>
-      <c r="E276" t="n">
+      <c r="E282" t="n">
         <v>0.0134185743271285</v>
       </c>
-      <c r="F276" t="n">
+      <c r="F282" t="n">
         <v>0.00589602797866525</v>
       </c>
     </row>
@@ -9358,7 +9514,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>287</v>
       </c>
       <c r="B133" t="n">
         <v>0.00000649233111218818</v>
@@ -9378,7 +9534,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>139</v>
+        <v>288</v>
       </c>
       <c r="B134" t="n">
         <v>6492.33111218818</v>
@@ -9398,7 +9554,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>140</v>
+        <v>289</v>
       </c>
       <c r="B135" t="n">
         <v>6.49233111218818</v>
@@ -9418,7 +9574,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B136" t="n">
         <v>104.099137305699</v>
@@ -9438,7 +9594,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B137" t="n">
         <v>0.104099137305699</v>
@@ -9458,7 +9614,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B138" t="n">
         <v>-9.42930793778969</v>
@@ -9478,7 +9634,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B139" t="n">
         <v>-3.42930793778969</v>
@@ -9498,7 +9654,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B140" t="n">
         <v>-0.429307937789685</v>
@@ -9518,7 +9674,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B141" t="n">
         <v>-6.42930793778969</v>
@@ -9538,7 +9694,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B142" t="n">
         <v>-11.3244265835902</v>
@@ -9558,7 +9714,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B143" t="n">
         <v>-5.32442658359016</v>
@@ -9578,7 +9734,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B144" t="n">
         <v>-2.32442658359016</v>
@@ -9598,7 +9754,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B145" t="n">
         <v>-8.32442658359016</v>
@@ -9618,7 +9774,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B146" t="n">
         <v>-10.3570835604135</v>
@@ -9638,7 +9794,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B147" t="n">
         <v>-4.35708356041347</v>
@@ -9658,7 +9814,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B148" t="n">
         <v>-1.35708356041347</v>
@@ -9678,7 +9834,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B149" t="n">
         <v>-7.35708356041347</v>
@@ -9698,7 +9854,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B150" t="n">
         <v>-11.1926925697674</v>
@@ -9718,7 +9874,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B151" t="n">
         <v>-5.19269256976736</v>
@@ -9738,7 +9894,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B152" t="n">
         <v>-2.19269256976736</v>
@@ -9758,7 +9914,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B153" t="n">
         <v>-8.19269256976736</v>
@@ -9778,7 +9934,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B154" t="n">
         <v>-12.669384729144</v>
@@ -9798,7 +9954,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B155" t="n">
         <v>-6.66938472914396</v>
@@ -9818,7 +9974,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B156" t="n">
         <v>-3.66938472914396</v>
@@ -9838,7 +9994,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B157" t="n">
         <v>-9.66938472914396</v>
@@ -9858,7 +10014,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B158" t="n">
         <v>-12.4898499471774</v>
@@ -9878,7 +10034,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B159" t="n">
         <v>-6.48984994717738</v>
@@ -9898,7 +10054,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B160" t="n">
         <v>-3.48984994717737</v>
@@ -9918,7 +10074,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B161" t="n">
         <v>-9.48984994717737</v>
@@ -9938,7 +10094,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B162" t="n">
         <v>-6.11598684803654</v>
@@ -9958,7 +10114,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B163" t="n">
         <v>2.88401315196346</v>
@@ -9978,7 +10134,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B164" t="n">
         <v>-0.115986848036539</v>
@@ -9998,7 +10154,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B165" t="n">
         <v>-5.37902517824316</v>
@@ -10018,7 +10174,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B166" t="n">
         <v>3.62097482175684</v>
@@ -10038,7 +10194,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B167" t="n">
         <v>0.620974821756843</v>
@@ -10058,7 +10214,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B168" t="n">
         <v>-5.11091690555914</v>
@@ -10078,7 +10234,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B169" t="n">
         <v>3.88908309444086</v>
@@ -10098,7 +10254,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B170" t="n">
         <v>0.889083094440858</v>
@@ -10118,7 +10274,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B171" t="n">
         <v>-2.97800662468358</v>
@@ -10138,7 +10294,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B172" t="n">
         <v>6.02199337531642</v>
@@ -10158,7 +10314,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B173" t="n">
         <v>3.02199337531642</v>
@@ -10178,7 +10334,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B174" t="n">
         <v>-3.65101105730638</v>
@@ -10198,7 +10354,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B175" t="n">
         <v>5.34898894269362</v>
@@ -10218,7 +10374,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B176" t="n">
         <v>2.34898894269362</v>
@@ -10238,7 +10394,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B177" t="n">
         <v>-8.03306989879472</v>
@@ -10258,7 +10414,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B178" t="n">
         <v>0.966930101205278</v>
@@ -10278,7 +10434,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B179" t="n">
         <v>-2.03306989879472</v>
@@ -10298,7 +10454,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B180" t="n">
         <v>-2.61618579484238</v>
@@ -10318,7 +10474,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B181" t="n">
         <v>6.38381420515762</v>
@@ -10338,7 +10494,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B182" t="n">
         <v>3.38381420515762</v>
@@ -10358,7 +10514,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B183" t="n">
         <v>-3.8624318393549</v>
@@ -10378,7 +10534,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B184" t="n">
         <v>5.1375681606451</v>
@@ -10398,7 +10554,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B185" t="n">
         <v>2.1375681606451</v>
@@ -10418,7 +10574,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B186" t="n">
         <v>-7.64404785956147</v>
@@ -10438,7 +10594,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B187" t="n">
         <v>1.35595214043853</v>
@@ -10458,7 +10614,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B188" t="n">
         <v>-1.64404785956147</v>
@@ -10478,7 +10634,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B189" t="n">
         <v>-20.8685301204301</v>
@@ -10498,7 +10654,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B190" t="n">
         <v>-11.8685301204301</v>
@@ -10518,7 +10674,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B191" t="n">
         <v>-14.8685301204301</v>
@@ -10538,7 +10694,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B192" t="n">
         <v>-4.56438170024587</v>
@@ -10558,7 +10714,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B193" t="n">
         <v>4.43561829975413</v>
@@ -10578,7 +10734,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B194" t="n">
         <v>1.43561829975413</v>
@@ -10598,7 +10754,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B195" t="n">
         <v>-3.3208835525604</v>
@@ -10618,7 +10774,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B196" t="n">
         <v>5.6791164474396</v>
@@ -10638,7 +10794,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B197" t="n">
         <v>2.6791164474396</v>
@@ -10658,7 +10814,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B198" t="n">
         <v>-20.221579061294</v>
@@ -10678,7 +10834,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B199" t="n">
         <v>-11.221579061294</v>
@@ -10698,7 +10854,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B200" t="n">
         <v>-14.221579061294</v>
@@ -10718,7 +10874,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B201" t="n">
         <v>-4.39006948872305</v>
@@ -10738,7 +10894,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B202" t="n">
         <v>4.60993051127695</v>
@@ -10758,7 +10914,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B203" t="n">
         <v>1.60993051127695</v>
@@ -10778,7 +10934,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B204" t="n">
         <v>-6.753908979177</v>
@@ -10798,7 +10954,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B205" t="n">
         <v>2.246091020823</v>
@@ -10818,7 +10974,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B206" t="n">
         <v>-0.753908979176996</v>
@@ -10838,7 +10994,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B207" t="n">
         <v>-5.79189417065519</v>
@@ -10858,7 +11014,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B208" t="n">
         <v>3.20810582934481</v>
@@ -10878,7 +11034,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B209" t="n">
         <v>0.208105829344813</v>
@@ -10898,7 +11054,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B210" t="n">
         <v>-5.52723431891734</v>
@@ -10918,7 +11074,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B211" t="n">
         <v>3.47276568108266</v>
@@ -10938,7 +11094,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B212" t="n">
         <v>0.472765681082662</v>
@@ -10958,7 +11114,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B213" t="n">
         <v>-3.39728011553017</v>
@@ -10978,7 +11134,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B214" t="n">
         <v>5.60271988446983</v>
@@ -10998,7 +11154,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B215" t="n">
         <v>2.60271988446983</v>
@@ -11018,7 +11174,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B216" t="n">
         <v>-3.65525695144415</v>
@@ -11038,7 +11194,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B217" t="n">
         <v>5.34474304855584</v>
@@ -11058,7 +11214,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B218" t="n">
         <v>2.34474304855584</v>
@@ -11078,7 +11234,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B219" t="n">
         <v>-4.08795850644903</v>
@@ -11098,7 +11254,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B220" t="n">
         <v>4.91204149355097</v>
@@ -11118,7 +11274,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B221" t="n">
         <v>1.91204149355097</v>
@@ -11138,7 +11294,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B222" t="n">
         <v>-12.2246831891206</v>
@@ -11158,7 +11314,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B223" t="n">
         <v>-6.22468318912056</v>
@@ -11178,7 +11334,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B224" t="n">
         <v>-9.22468318912055</v>
@@ -11198,7 +11354,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B225" t="n">
         <v>-5.24304035875144</v>
@@ -11218,7 +11374,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B226" t="n">
         <v>3.75695964124856</v>
@@ -11238,7 +11394,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B227" t="n">
         <v>0.756959641248558</v>
@@ -11258,7 +11414,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B228" t="n">
         <v>-7.28982370054765</v>
@@ -11278,7 +11434,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B229" t="n">
         <v>1.71017629945235</v>
@@ -11298,7 +11454,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B230" t="n">
         <v>-1.28982370054765</v>
@@ -11318,7 +11474,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B231" t="n">
         <v>-7.25783337325316</v>
@@ -11338,7 +11494,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B232" t="n">
         <v>1.74216662674684</v>
@@ -11358,7 +11514,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B233" t="n">
         <v>-1.25783337325316</v>
@@ -11378,7 +11534,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B234" t="n">
         <v>-5.6700664262043</v>
@@ -11398,7 +11554,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B235" t="n">
         <v>3.3299335737957</v>
@@ -11418,7 +11574,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B236" t="n">
         <v>0.329933573795699</v>
@@ -11438,7 +11594,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B237" t="n">
         <v>-6.52301375406182</v>
@@ -11458,7 +11614,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B238" t="n">
         <v>2.47698624593818</v>
@@ -11478,7 +11634,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B239" t="n">
         <v>-0.523013754061816</v>
@@ -11498,7 +11654,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B240" t="n">
         <v>-7.3475245713113</v>
@@ -11518,7 +11674,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B241" t="n">
         <v>1.6524754286887</v>
@@ -11538,7 +11694,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B242" t="n">
         <v>-1.3475245713113</v>
@@ -11558,7 +11714,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B243" t="n">
         <v>1.17928162520831</v>
@@ -11578,7 +11734,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B244" t="n">
         <v>-0.387924893695415</v>
@@ -11598,7 +11754,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B245" t="n">
         <v>-9.14262398806834</v>
@@ -11618,7 +11774,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B246" t="n">
         <v>-0.142623988068339</v>
@@ -11638,7 +11794,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B247" t="n">
         <v>-3.14262398806834</v>
@@ -11658,7 +11814,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B248" t="n">
         <v>-11.0372472512135</v>
@@ -11678,7 +11834,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B249" t="n">
         <v>-2.03724725121349</v>
@@ -11698,7 +11854,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B250" t="n">
         <v>-5.03724725121349</v>
@@ -11718,7 +11874,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B251" t="n">
         <v>-8.37012933920423</v>
@@ -11738,7 +11894,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B252" t="n">
         <v>0.62987066079577</v>
@@ -11758,7 +11914,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B253" t="n">
         <v>-2.37012933920423</v>
@@ -11778,7 +11934,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B254" t="n">
         <v>-9.38444313617553</v>
@@ -11798,7 +11954,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B255" t="n">
         <v>-0.384443136175533</v>
@@ -11818,7 +11974,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B256" t="n">
         <v>-3.38444313617553</v>
@@ -11838,7 +11994,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B257" t="n">
         <v>-9.67791337129567</v>
@@ -11858,7 +12014,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B258" t="n">
         <v>-0.67791337129567</v>
@@ -11878,7 +12034,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B259" t="n">
         <v>-3.67791337129567</v>
@@ -11898,7 +12054,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B260" t="n">
         <v>-16.0001534369502</v>
@@ -11918,7 +12074,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B261" t="n">
         <v>-7.00015343695019</v>
@@ -11938,7 +12094,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B262" t="n">
         <v>-10.0001534369502</v>
@@ -11958,7 +12114,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B263" t="n">
         <v>-7.06909585835686</v>
@@ -11978,7 +12134,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B264" t="n">
         <v>-10.0522512110379</v>
@@ -11998,7 +12154,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B265" t="n">
         <v>-1.05225121103792</v>
@@ -12018,7 +12174,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B266" t="n">
         <v>-4.05225121103792</v>
@@ -12038,7 +12194,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B267" t="n">
         <v>-5.2136790078794</v>
@@ -12058,7 +12214,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="B268" t="n">
         <v>3.7863209921206</v>
@@ -12078,7 +12234,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B269" t="n">
         <v>0.786320992120599</v>
@@ -12098,7 +12254,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B270" t="n">
         <v>1.93090414164314</v>
@@ -12118,7 +12274,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B271" t="n">
         <v>-1.06909585835686</v>
@@ -12138,7 +12294,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B272" t="n">
         <v>-0.574952001204607</v>
@@ -12158,7 +12314,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B273" t="n">
         <v>7.61722797927461</v>
@@ -12178,7 +12334,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B274" t="n">
         <v>0.32572981231456</v>
@@ -14849,7 +15005,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>287</v>
       </c>
       <c r="B133" t="n">
         <v>0.0000103839211758947</v>
@@ -14869,7 +15025,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>139</v>
+        <v>288</v>
       </c>
       <c r="B134" t="n">
         <v>10383.9211758947</v>
@@ -14889,7 +15045,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>140</v>
+        <v>289</v>
       </c>
       <c r="B135" t="n">
         <v>10.3839211758947</v>
@@ -14909,7 +15065,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B136" t="n">
         <v>104.099137305699</v>
@@ -14929,7 +15085,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B137" t="n">
         <v>0.104099137305699</v>
@@ -14949,7 +15105,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B138" t="n">
         <v>-9.43047625453963</v>
@@ -14969,7 +15125,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B139" t="n">
         <v>-3.43047625453963</v>
@@ -14989,7 +15145,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B140" t="n">
         <v>-0.430476254539628</v>
@@ -15009,7 +15165,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B141" t="n">
         <v>-6.43047625453963</v>
@@ -15029,7 +15185,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B142" t="n">
         <v>-11.3148794599625</v>
@@ -15049,7 +15205,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B143" t="n">
         <v>-5.3148794599625</v>
@@ -15069,7 +15225,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B144" t="n">
         <v>-2.3148794599625</v>
@@ -15089,7 +15245,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B145" t="n">
         <v>-8.3148794599625</v>
@@ -15109,7 +15265,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B146" t="n">
         <v>-10.3580837016221</v>
@@ -15129,7 +15285,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B147" t="n">
         <v>-4.35808370162213</v>
@@ -15149,7 +15305,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B148" t="n">
         <v>-1.35808370162213</v>
@@ -15169,7 +15325,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B149" t="n">
         <v>-7.35808370162213</v>
@@ -15189,7 +15345,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B150" t="n">
         <v>-11.1853448402758</v>
@@ -15209,7 +15365,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B151" t="n">
         <v>-5.18534484027584</v>
@@ -15229,7 +15385,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B152" t="n">
         <v>-2.18534484027584</v>
@@ -15249,7 +15405,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B153" t="n">
         <v>-8.18534484027584</v>
@@ -15269,7 +15425,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B154" t="n">
         <v>-12.8532844067397</v>
@@ -15289,7 +15445,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B155" t="n">
         <v>-6.85328440673965</v>
@@ -15309,7 +15465,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B156" t="n">
         <v>-3.85328440673965</v>
@@ -15329,7 +15485,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B157" t="n">
         <v>-9.85328440673965</v>
@@ -15349,7 +15505,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B158" t="n">
         <v>-12.6727739851647</v>
@@ -15369,7 +15525,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B159" t="n">
         <v>-6.67277398516467</v>
@@ -15389,7 +15545,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B160" t="n">
         <v>-3.67277398516467</v>
@@ -15409,7 +15565,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B161" t="n">
         <v>-9.67277398516467</v>
@@ -15429,7 +15585,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B162" t="n">
         <v>-5.47123491574122</v>
@@ -15449,7 +15605,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B163" t="n">
         <v>3.52876508425878</v>
@@ -15469,7 +15625,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B164" t="n">
         <v>0.528765084258778</v>
@@ -15489,7 +15645,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B165" t="n">
         <v>-4.73183121055391</v>
@@ -15509,7 +15665,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B166" t="n">
         <v>4.26816878944609</v>
@@ -15529,7 +15685,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B167" t="n">
         <v>1.26816878944609</v>
@@ -15549,7 +15705,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B168" t="n">
         <v>-5.1291843939392</v>
@@ -15569,7 +15725,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B169" t="n">
         <v>3.8708156060608</v>
@@ -15589,7 +15745,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B170" t="n">
         <v>0.8708156060608</v>
@@ -15609,7 +15765,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B171" t="n">
         <v>-2.97800662468358</v>
@@ -15629,7 +15785,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B172" t="n">
         <v>6.02199337531642</v>
@@ -15649,7 +15805,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B173" t="n">
         <v>3.02199337531642</v>
@@ -15669,7 +15825,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B174" t="n">
         <v>-3.65101105730638</v>
@@ -15689,7 +15845,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B175" t="n">
         <v>5.34898894269362</v>
@@ -15709,7 +15865,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B176" t="n">
         <v>2.34898894269362</v>
@@ -15729,7 +15885,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B177" t="n">
         <v>-8.03306989879472</v>
@@ -15749,7 +15905,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B178" t="n">
         <v>0.966930101205278</v>
@@ -15769,7 +15925,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B179" t="n">
         <v>-2.03306989879472</v>
@@ -15789,7 +15945,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B180" t="n">
         <v>-2.61618579484238</v>
@@ -15809,7 +15965,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B181" t="n">
         <v>6.38381420515762</v>
@@ -15829,7 +15985,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B182" t="n">
         <v>3.38381420515762</v>
@@ -15849,7 +16005,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B183" t="n">
         <v>-3.8624318393549</v>
@@ -15869,7 +16025,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B184" t="n">
         <v>5.1375681606451</v>
@@ -15889,7 +16045,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B185" t="n">
         <v>2.1375681606451</v>
@@ -15909,7 +16065,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B186" t="n">
         <v>-7.8296777202845</v>
@@ -15929,7 +16085,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B187" t="n">
         <v>1.1703222797155</v>
@@ -15949,7 +16105,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B188" t="n">
         <v>-1.8296777202845</v>
@@ -15969,7 +16125,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B189" t="n">
         <v>-20.674237558062</v>
@@ -15989,7 +16145,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B190" t="n">
         <v>-11.674237558062</v>
@@ -16009,7 +16165,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B191" t="n">
         <v>-14.674237558062</v>
@@ -16029,7 +16185,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B192" t="n">
         <v>-3.90705667964021</v>
@@ -16049,7 +16205,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B193" t="n">
         <v>5.09294332035979</v>
@@ -16069,7 +16225,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B194" t="n">
         <v>2.09294332035979</v>
@@ -16089,7 +16245,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B195" t="n">
         <v>-2.66111647332121</v>
@@ -16109,7 +16265,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B196" t="n">
         <v>6.33888352667879</v>
@@ -16129,7 +16285,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B197" t="n">
         <v>3.33888352667879</v>
@@ -16149,7 +16305,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B198" t="n">
         <v>-20.0248445228654</v>
@@ -16169,7 +16325,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B199" t="n">
         <v>-11.0248445228654</v>
@@ -16189,7 +16345,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B200" t="n">
         <v>-14.0248445228654</v>
@@ -16209,7 +16365,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B201" t="n">
         <v>-4.39006948872305</v>
@@ -16229,7 +16385,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B202" t="n">
         <v>4.60993051127695</v>
@@ -16249,7 +16405,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B203" t="n">
         <v>1.60993051127695</v>
@@ -16269,7 +16425,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B204" t="n">
         <v>-6.10898888729648</v>
@@ -16289,7 +16445,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B205" t="n">
         <v>2.89101111270352</v>
@@ -16309,7 +16465,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B206" t="n">
         <v>-0.108988887296483</v>
@@ -16329,7 +16485,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B207" t="n">
         <v>-5.14453203903624</v>
@@ -16349,7 +16505,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B208" t="n">
         <v>3.85546796096376</v>
@@ -16369,7 +16525,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B209" t="n">
         <v>0.855467960963761</v>
@@ -16389,7 +16545,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B210" t="n">
         <v>-5.5453336356715</v>
@@ -16409,7 +16565,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B211" t="n">
         <v>3.4546663643285</v>
@@ -16429,7 +16585,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B212" t="n">
         <v>0.454666364328496</v>
@@ -16449,7 +16605,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B213" t="n">
         <v>-3.39728011553017</v>
@@ -16469,7 +16625,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B214" t="n">
         <v>5.60271988446983</v>
@@ -16489,7 +16645,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B215" t="n">
         <v>2.60271988446983</v>
@@ -16509,7 +16665,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B216" t="n">
         <v>-3.65525695144415</v>
@@ -16529,7 +16685,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B217" t="n">
         <v>5.34474304855584</v>
@@ -16549,7 +16705,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B218" t="n">
         <v>2.34474304855584</v>
@@ -16569,7 +16725,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B219" t="n">
         <v>-4.08795850644903</v>
@@ -16589,7 +16745,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B220" t="n">
         <v>4.91204149355097</v>
@@ -16609,7 +16765,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B221" t="n">
         <v>1.91204149355097</v>
@@ -16629,7 +16785,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B222" t="n">
         <v>-12.4079053588964</v>
@@ -16649,7 +16805,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B223" t="n">
         <v>-6.40790535889639</v>
@@ -16669,7 +16825,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B224" t="n">
         <v>-9.40790535889639</v>
@@ -16689,7 +16845,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B225" t="n">
         <v>-5.30458917856027</v>
@@ -16709,7 +16865,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B226" t="n">
         <v>3.69541082143973</v>
@@ -16729,7 +16885,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B227" t="n">
         <v>0.695410821439727</v>
@@ -16749,7 +16905,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B228" t="n">
         <v>-7.17699095098957</v>
@@ -16769,7 +16925,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B229" t="n">
         <v>1.82300904901043</v>
@@ -16789,7 +16945,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B230" t="n">
         <v>-1.17699095098957</v>
@@ -16809,7 +16965,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B231" t="n">
         <v>-7.66980963620123</v>
@@ -16829,7 +16985,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B232" t="n">
         <v>1.33019036379877</v>
@@ -16849,7 +17005,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B233" t="n">
         <v>-1.66980963620123</v>
@@ -16869,7 +17025,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B234" t="n">
         <v>-5.81436078399953</v>
@@ -16889,7 +17045,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B235" t="n">
         <v>3.18563921600047</v>
@@ -16909,7 +17065,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B236" t="n">
         <v>0.185639216000467</v>
@@ -16929,7 +17085,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B237" t="n">
         <v>-6.93499001470425</v>
@@ -16949,7 +17105,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B238" t="n">
         <v>2.06500998529575</v>
@@ -16969,7 +17125,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B239" t="n">
         <v>-0.934990014704251</v>
@@ -16989,7 +17145,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B240" t="n">
         <v>-7.35726832169801</v>
@@ -17009,7 +17165,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B241" t="n">
         <v>1.64273167830199</v>
@@ -17029,7 +17185,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B242" t="n">
         <v>-1.35726832169801</v>
@@ -17049,7 +17205,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B243" t="n">
         <v>1.17928162520831</v>
@@ -17069,7 +17225,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B244" t="n">
         <v>-0.387924893695415</v>
@@ -17089,7 +17245,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B245" t="n">
         <v>-8.67962781924752</v>
@@ -17109,7 +17265,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B246" t="n">
         <v>0.320372180752477</v>
@@ -17129,7 +17285,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B247" t="n">
         <v>-2.67962781924752</v>
@@ -17149,7 +17305,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B248" t="n">
         <v>-11.232014783183</v>
@@ -17169,7 +17325,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B249" t="n">
         <v>-2.23201478318303</v>
@@ -17189,7 +17345,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B250" t="n">
         <v>-5.23201478318303</v>
@@ -17209,7 +17365,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B251" t="n">
         <v>-7.90469107790376</v>
@@ -17229,7 +17385,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B252" t="n">
         <v>1.09530892209624</v>
@@ -17249,7 +17405,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B253" t="n">
         <v>-1.90469107790376</v>
@@ -17269,7 +17425,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B254" t="n">
         <v>-9.5763299430752</v>
@@ -17289,7 +17445,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B255" t="n">
         <v>-0.576329943075197</v>
@@ -17309,7 +17465,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B256" t="n">
         <v>-3.5763299430752</v>
@@ -17329,7 +17485,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B257" t="n">
         <v>-9.87793658574158</v>
@@ -17349,7 +17505,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B258" t="n">
         <v>-0.87793658574158</v>
@@ -17369,7 +17525,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B259" t="n">
         <v>-3.87793658574158</v>
@@ -17389,7 +17545,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B260" t="n">
         <v>-16.00018976568</v>
@@ -17409,7 +17565,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B261" t="n">
         <v>-7.00018976568003</v>
@@ -17429,7 +17585,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B262" t="n">
         <v>-10.00018976568</v>
@@ -17449,7 +17605,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B263" t="n">
         <v>-7.06909585835686</v>
@@ -17469,7 +17625,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B264" t="n">
         <v>-10.2465800565038</v>
@@ -17489,7 +17645,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B265" t="n">
         <v>-1.24658005650378</v>
@@ -17509,7 +17665,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B266" t="n">
         <v>-4.24658005650378</v>
@@ -17529,7 +17685,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B267" t="n">
         <v>-5.02570310306523</v>
@@ -17549,7 +17705,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="B268" t="n">
         <v>3.97429689693477</v>
@@ -17569,7 +17725,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B269" t="n">
         <v>0.974296896934769</v>
@@ -17589,7 +17745,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B270" t="n">
         <v>1.93090414164314</v>
@@ -17609,7 +17765,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B271" t="n">
         <v>-1.06909585835686</v>
@@ -17629,7 +17785,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B272" t="n">
         <v>-0.760581861927642</v>
@@ -17649,7 +17805,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B273" t="n">
         <v>7.61722797927461</v>
@@ -17669,7 +17825,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B274" t="n">
         <v>0.200069140767506</v>
